--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="309">
   <si>
     <t>workstream</t>
   </si>
@@ -338,19 +338,289 @@
     <t>Stabilize roll-up gate determinism across staged/unstaged/untracked diff states</t>
   </si>
   <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:committed]</t>
+  </si>
+  <si>
+    <t>Define transient-artifact hygiene policy for local/generated files without hiding governed outputs</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:committed]</t>
+  </si>
+  <si>
+    <t>Split migration changes into deterministic policy/management/product slices with per-slice gate evidence</t>
+  </si>
+  <si>
+    <t>Executed deterministic slice commits (`policy`, `management`, `product`) from generated manifest files and captured closure evidence under `management/pm/reports/workstream-j-slice-evidence.json`. [github:committed]</t>
+  </si>
+  <si>
+    <t>Reconcile project plan/progress/decision artifacts so open actions are reflected in next-step guidance</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:committed]</t>
+  </si>
+  <si>
+    <t>Re-run qualityGate plus PM refresh/report cycle and publish stabilization closure evidence</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` and executed PM refresh/report cycles to regenerate governance outputs after slice commits and issue-log synchronization. [github:committed]</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
     <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
   </si>
   <si>
-    <t>Define transient-artifact hygiene policy for local/generated files without hiding governed outputs</t>
-  </si>
-  <si>
     <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
   </si>
   <si>
-    <t>Split migration changes into deterministic policy/management/product slices with per-slice gate evidence</t>
-  </si>
-  <si>
-    <t>In Progress</t>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:26:23Z</t>
   </si>
   <si>
     <t>80</t>
@@ -359,259 +629,7 @@
     <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
   </si>
   <si>
-    <t>Reconcile project plan/progress/decision artifacts so open actions are reflected in next-step guidance</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Re-run qualityGate plus PM refresh/report cycle and publish stabilization closure evidence</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:26:23Z</t>
+    <t>2026-02-23T22:33:37Z</t>
   </si>
   <si>
     <t>iteration</t>
@@ -749,6 +767,36 @@
     <t xml:space="preserve"> -+#</t>
   </si>
   <si>
+    <t>10,100,100,100</t>
+  </si>
+  <si>
+    <t>.@@@</t>
+  </si>
+  <si>
+    <t>0,100,100,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @@@</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0,30,55,80,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -+#@</t>
+  </si>
+  <si>
+    <t>0,60,100,100,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +@@@</t>
+  </si>
+  <si>
     <t>Workstream A | complete graphics object rendering beyond placeholders (rules, boxes, strokes/fills)</t>
   </si>
   <si>
@@ -887,16 +935,16 @@
     <t>latest_percent</t>
   </si>
   <si>
-    <t>@@@@</t>
-  </si>
-  <si>
-    <t>+@@@</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> @@@</t>
-  </si>
-  <si>
-    <t>.@@@</t>
+    <t>@@@@@</t>
+  </si>
+  <si>
+    <t>+@@@@</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @@@@</t>
+  </si>
+  <si>
+    <t>.@@@@</t>
   </si>
 </sst>
 </file>
@@ -1944,16 +1992,16 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45">
@@ -1961,7 +2009,7 @@
         <v>104</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>9</v>
@@ -1976,7 +2024,7 @@
         <v>98</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
@@ -1984,7 +2032,7 @@
         <v>104</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>9</v>
@@ -1999,7 +2047,7 @@
         <v>98</v>
       </c>
       <c r="G46" t="s" s="0">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2010,12 +2058,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2024,25 +2072,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>122</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>124</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2050,7 +2098,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2059,19 +2107,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2080,12 +2128,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2094,19 +2142,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2115,12 +2163,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2129,19 +2177,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2150,12 +2198,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2164,19 +2212,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2185,12 +2233,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2199,19 +2247,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2220,12 +2268,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2234,19 +2282,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2255,12 +2303,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2269,19 +2317,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2290,12 +2338,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2304,19 +2352,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2325,12 +2373,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2339,19 +2387,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2360,12 +2408,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2374,19 +2422,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2395,12 +2443,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2409,19 +2457,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2430,12 +2478,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2444,19 +2492,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2465,12 +2513,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2479,19 +2527,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2500,12 +2548,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2514,19 +2562,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2535,12 +2583,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2549,19 +2597,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2570,12 +2618,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2584,19 +2632,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2605,12 +2653,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2619,19 +2667,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2640,12 +2688,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -2654,19 +2702,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -2675,12 +2723,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -2689,19 +2737,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -2710,12 +2758,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -2724,19 +2772,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -2745,12 +2793,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -2759,19 +2807,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -2780,12 +2828,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -2794,19 +2842,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -2815,12 +2863,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -2829,19 +2877,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -2850,12 +2898,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -2864,19 +2912,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -2885,12 +2933,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -2899,19 +2947,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -2920,12 +2968,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -2934,19 +2982,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -2955,12 +3003,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -2969,19 +3017,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -2990,12 +3038,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3004,19 +3052,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3025,12 +3073,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3039,19 +3087,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3060,12 +3108,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3074,19 +3122,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3095,12 +3143,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3109,19 +3157,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3130,12 +3178,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3144,19 +3192,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3165,12 +3213,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3179,19 +3227,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3200,12 +3248,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3214,19 +3262,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3235,12 +3283,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3249,19 +3297,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3270,12 +3318,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3284,19 +3332,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3305,12 +3353,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3319,19 +3367,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3340,12 +3388,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3354,33 +3402,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3389,33 +3437,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I40" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F40" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G40" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H40" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I40" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3424,33 +3472,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I41" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F41" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G41" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I41" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3480,12 +3528,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -3515,12 +3563,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -3550,12 +3598,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -3564,7 +3612,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3576,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3585,12 +3633,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -3599,19 +3647,19 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H46" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="E46" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H46" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3620,12 +3668,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -3634,19 +3682,19 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H47" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="E47" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G47" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H47" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3655,12 +3703,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -3669,33 +3717,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -3704,33 +3752,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E49" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I49" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F49" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G49" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H49" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I49" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -3739,103 +3787,103 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I50" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F50" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G50" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H50" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I50" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E51" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I51" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F51" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G51" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H51" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I51" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E52" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I52" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="F52" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="G52" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H52" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="I52" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -3844,7 +3892,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -3856,7 +3904,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -3865,12 +3913,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -3879,19 +3927,19 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H54" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="E54" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G54" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H54" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -3900,12 +3948,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -3914,89 +3962,89 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H55" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="E55" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="F55" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G55" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H55" t="s" s="0">
-        <v>168</v>
-      </c>
       <c r="I55" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H56" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="E56" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="F56" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G56" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H56" t="s" s="0">
-        <v>168</v>
-      </c>
       <c r="I56" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H57" t="s" s="0">
         <v>167</v>
-      </c>
-      <c r="E57" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G57" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H57" t="s" s="0">
-        <v>168</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4005,12 +4053,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4019,10 +4067,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4031,30 +4079,30 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4066,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4075,12 +4123,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4115,7 +4163,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4150,7 +4198,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4185,7 +4233,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4220,7 +4268,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4255,7 +4303,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4290,7 +4338,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4325,7 +4373,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4360,7 +4408,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4395,7 +4443,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4430,7 +4478,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4465,7 +4513,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4500,7 +4548,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -4535,7 +4583,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -4570,7 +4618,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -4605,7 +4653,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -4640,7 +4688,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -4675,7 +4723,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -4710,7 +4758,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -4745,7 +4793,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -4780,7 +4828,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -4815,7 +4863,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -4850,7 +4898,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -4885,7 +4933,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -4920,7 +4968,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -4955,7 +5003,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -4990,7 +5038,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5025,7 +5073,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5060,7 +5108,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5095,7 +5143,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5130,7 +5178,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5165,7 +5213,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5200,7 +5248,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5235,7 +5283,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5270,7 +5318,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5305,7 +5353,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5340,7 +5388,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5375,7 +5423,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5410,7 +5458,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5445,7 +5493,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5480,7 +5528,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5510,12 +5558,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>106</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -5545,18 +5593,18 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>108</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D102" t="s" s="0">
         <v>10</v>
@@ -5580,18 +5628,18 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>114</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D103" t="s" s="0">
         <v>10</v>
@@ -5615,12 +5663,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>116</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -5629,10 +5677,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5641,16 +5689,191 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H105" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I105" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J105" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K105" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="D106" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E106" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H106" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I106" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J106" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K106" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="D107" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="E107" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H107" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="I107" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J107" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K107" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D108" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E108" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H108" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I108" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J108" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K108" t="s" s="0">
         <v>112</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="D109" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H109" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I109" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J109" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K109" t="s" s="0">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -5660,7 +5883,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5674,25 +5897,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2">
@@ -5706,7 +5929,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -5715,13 +5938,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
@@ -5735,7 +5958,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -5744,13 +5967,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
@@ -5764,7 +5987,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -5773,13 +5996,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
@@ -5793,7 +6016,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -5802,13 +6025,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -5822,7 +6045,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -5831,13 +6054,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -5851,7 +6074,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -5860,13 +6083,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8">
@@ -5880,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -5889,13 +6112,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -5909,7 +6132,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -5918,13 +6141,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -5938,7 +6161,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -5947,13 +6170,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -5967,7 +6190,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -5976,13 +6199,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -5996,7 +6219,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6005,13 +6228,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13">
@@ -6025,7 +6248,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6034,13 +6257,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
@@ -6054,7 +6277,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6063,13 +6286,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -6083,7 +6306,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6092,13 +6315,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16">
@@ -6112,7 +6335,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6121,13 +6344,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
@@ -6141,7 +6364,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6150,13 +6373,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -6170,7 +6393,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6179,13 +6402,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19">
@@ -6199,7 +6422,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6208,13 +6431,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
@@ -6228,7 +6451,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6237,13 +6460,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
@@ -6257,7 +6480,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -6266,13 +6489,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22">
@@ -6286,7 +6509,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -6295,13 +6518,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23">
@@ -6315,7 +6538,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -6324,13 +6547,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24">
@@ -6344,7 +6567,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -6353,13 +6576,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25">
@@ -6373,7 +6596,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -6382,13 +6605,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26">
@@ -6402,7 +6625,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -6411,13 +6634,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -6431,7 +6654,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -6440,13 +6663,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
@@ -6460,7 +6683,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -6469,13 +6692,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29">
@@ -6489,7 +6712,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -6498,13 +6721,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30">
@@ -6518,7 +6741,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -6527,13 +6750,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31">
@@ -6547,7 +6770,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -6556,13 +6779,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
@@ -6576,7 +6799,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -6585,13 +6808,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
@@ -6605,7 +6828,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -6614,13 +6837,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -6634,7 +6857,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -6643,13 +6866,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35">
@@ -6663,7 +6886,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -6672,13 +6895,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36">
@@ -6692,7 +6915,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -6701,13 +6924,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37">
@@ -6721,7 +6944,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -6730,13 +6953,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38">
@@ -6750,7 +6973,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -6759,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39">
@@ -6779,22 +7002,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40">
@@ -6808,22 +7031,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
@@ -6837,22 +7060,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42">
@@ -6866,7 +7089,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -6875,13 +7098,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43">
@@ -6895,7 +7118,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -6904,13 +7127,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44">
@@ -6924,7 +7147,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -6933,13 +7156,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
@@ -6953,7 +7176,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -6962,13 +7185,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
@@ -6982,7 +7205,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -6994,10 +7217,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47">
@@ -7011,7 +7234,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7023,10 +7246,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48">
@@ -7040,22 +7263,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49">
@@ -7069,22 +7292,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
@@ -7098,22 +7321,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51">
@@ -7121,28 +7344,28 @@
         <v>104</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52">
@@ -7150,28 +7373,28 @@
         <v>104</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53">
@@ -7185,7 +7408,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7194,13 +7417,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54">
@@ -7214,7 +7437,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7226,10 +7449,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55">
@@ -7243,22 +7466,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56">
@@ -7266,28 +7489,28 @@
         <v>104</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57">
@@ -7295,13 +7518,13 @@
         <v>104</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -7313,10 +7536,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58">
@@ -7330,22 +7553,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59">
@@ -7353,13 +7576,13 @@
         <v>104</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -7368,13 +7591,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60">
@@ -7388,7 +7611,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -7397,13 +7620,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61">
@@ -7417,7 +7640,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -7426,13 +7649,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62">
@@ -7446,7 +7669,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -7455,13 +7678,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63">
@@ -7475,7 +7698,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -7484,13 +7707,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64">
@@ -7504,7 +7727,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -7513,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65">
@@ -7533,7 +7756,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -7542,13 +7765,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66">
@@ -7562,7 +7785,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -7571,13 +7794,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67">
@@ -7591,7 +7814,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -7600,13 +7823,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68">
@@ -7620,7 +7843,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -7629,13 +7852,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69">
@@ -7649,7 +7872,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -7658,13 +7881,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70">
@@ -7678,7 +7901,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -7687,13 +7910,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71">
@@ -7707,7 +7930,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -7716,13 +7939,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72">
@@ -7736,7 +7959,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -7745,13 +7968,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73">
@@ -7765,7 +7988,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -7774,13 +7997,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74">
@@ -7794,7 +8017,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -7803,13 +8026,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75">
@@ -7823,7 +8046,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -7832,13 +8055,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76">
@@ -7852,7 +8075,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -7861,13 +8084,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77">
@@ -7881,7 +8104,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -7890,13 +8113,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78">
@@ -7910,7 +8133,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -7919,13 +8142,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79">
@@ -7939,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -7948,13 +8171,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80">
@@ -7968,7 +8191,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -7977,13 +8200,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81">
@@ -7997,7 +8220,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8006,13 +8229,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82">
@@ -8026,7 +8249,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8035,13 +8258,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83">
@@ -8055,7 +8278,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8064,13 +8287,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84">
@@ -8084,7 +8307,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8093,13 +8316,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85">
@@ -8113,7 +8336,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8122,13 +8345,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86">
@@ -8142,7 +8365,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8151,13 +8374,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87">
@@ -8171,7 +8394,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8180,13 +8403,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88">
@@ -8200,7 +8423,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8209,13 +8432,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89">
@@ -8229,7 +8452,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8238,13 +8461,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90">
@@ -8258,7 +8481,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -8267,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91">
@@ -8287,7 +8510,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -8296,13 +8519,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92">
@@ -8316,7 +8539,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -8325,13 +8548,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93">
@@ -8345,7 +8568,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -8354,13 +8577,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94">
@@ -8374,7 +8597,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -8383,13 +8606,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95">
@@ -8403,7 +8626,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -8412,13 +8635,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96">
@@ -8432,7 +8655,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -8441,13 +8664,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97">
@@ -8461,7 +8684,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -8470,13 +8693,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98">
@@ -8490,7 +8713,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -8499,13 +8722,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99">
@@ -8519,7 +8742,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -8528,13 +8751,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="100">
@@ -8548,7 +8771,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -8557,13 +8780,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101">
@@ -8577,7 +8800,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -8586,13 +8809,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102">
@@ -8600,13 +8823,13 @@
         <v>104</v>
       </c>
       <c r="B102" t="s" s="0">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C102" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -8615,13 +8838,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103">
@@ -8629,13 +8852,13 @@
         <v>104</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C103" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -8644,13 +8867,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="104">
@@ -8664,22 +8887,167 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="G104" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="H104" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="I104" t="s" s="0">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F105" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G105" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H105" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="I105" t="s" s="0">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D106" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="E106" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F106" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G106" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H106" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="I106" t="s" s="0">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D107" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E107" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F107" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G107" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="H107" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="I107" t="s" s="0">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B108" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="G104" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="H104" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="I104" t="s" s="0">
-        <v>242</v>
+      <c r="C108" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D108" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E108" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F108" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G108" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H108" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="I108" t="s" s="0">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D109" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F109" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G109" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H109" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="I109" t="s" s="0">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -8689,152 +9057,152 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT53"/>
+  <dimension ref="A1:AT54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>287</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>11</v>
@@ -8948,33 +9316,33 @@
         <v>11</v>
       </c>
       <c r="AM2" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AO2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AP2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>11</v>
@@ -9103,10 +9471,10 @@
         <v>11</v>
       </c>
       <c r="AR3" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AS3" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AT3" t="s" s="0">
         <v>11</v>
@@ -9114,118 +9482,118 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="U4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AB4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AM4" t="s" s="0">
         <v>11</v>
@@ -9246,7 +9614,7 @@
         <v>11</v>
       </c>
       <c r="AS4" t="s" s="0">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AT4" t="s" s="0">
         <v>11</v>
@@ -9254,172 +9622,301 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="AT5" t="s" s="0">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>288</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="O6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="P6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="Q6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="R6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="S6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="T6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="U6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="V6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="W6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="X6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="Y6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="Z6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AA6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AB6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AC6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AD6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AE6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AF6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AG6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AH6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AI6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AJ6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AK6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AL6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AM6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AN6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AO6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AP6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AQ6" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="AR6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="s" s="0">
+        <v>124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>243</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>289</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>11</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -9427,10 +9924,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -9438,10 +9935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -9449,10 +9946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -9460,10 +9957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -9471,10 +9968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -9482,10 +9979,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -9493,10 +9990,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -9504,10 +10001,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -9515,10 +10012,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -9526,10 +10023,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -9537,10 +10034,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -9548,10 +10045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -9559,10 +10056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -9570,10 +10067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -9581,10 +10078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -9592,10 +10089,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -9603,10 +10100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -9614,10 +10111,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -9625,10 +10122,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -9636,10 +10133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -9647,10 +10144,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -9658,10 +10155,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -9669,10 +10166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -9680,10 +10177,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -9691,10 +10188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -9702,10 +10199,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -9713,10 +10210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -9724,10 +10221,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -9735,10 +10232,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -9746,10 +10243,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -9757,10 +10254,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -9768,10 +10265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -9779,10 +10276,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -9790,10 +10287,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -9801,10 +10298,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -9812,10 +10309,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -9823,10 +10320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -9834,10 +10331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -9845,10 +10342,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -9856,10 +10353,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -9867,10 +10364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -9878,23 +10375,34 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>111</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="C53" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="C54" t="s" s="0">
         <v>11</v>
       </c>
     </row>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2977" uniqueCount="315">
   <si>
     <t>workstream</t>
   </si>
@@ -317,297 +317,306 @@
     <t>2026-02-23</t>
   </si>
   <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:committed]</t>
+  </si>
+  <si>
+    <t>Stage 2 - Tooling governance refactor</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:committed]</t>
+  </si>
+  <si>
+    <t>Stage 3 - Enforcement and closure validation</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:committed]</t>
+  </si>
+  <si>
+    <t>Workstream J</t>
+  </si>
+  <si>
+    <t>Stabilize roll-up gate determinism across staged/unstaged/untracked diff states</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:committed]</t>
+  </si>
+  <si>
+    <t>Define transient-artifact hygiene policy for local/generated files without hiding governed outputs</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:committed]</t>
+  </si>
+  <si>
+    <t>Split migration changes into deterministic policy/management/product slices with per-slice gate evidence</t>
+  </si>
+  <si>
+    <t>Executed deterministic slice commits (`policy`, `management`, `product`) from generated manifest files and captured closure evidence under `management/pm/reports/workstream-j-slice-evidence.json`. [github:committed]</t>
+  </si>
+  <si>
+    <t>Reconcile project plan/progress/decision artifacts so open actions are reflected in next-step guidance</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:committed]</t>
+  </si>
+  <si>
+    <t>Re-run qualityGate plus PM refresh/report cycle and publish stabilization closure evidence</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` and executed PM refresh/report cycles to regenerate governance outputs after slice commits and issue-log synchronization. [github:committed]</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
     <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
   </si>
   <si>
-    <t>Stage 2 - Tooling governance refactor</t>
-  </si>
-  <si>
     <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
   </si>
   <si>
-    <t>Stage 3 - Enforcement and closure validation</t>
-  </si>
-  <si>
     <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
   </si>
   <si>
-    <t>Workstream J</t>
-  </si>
-  <si>
-    <t>Stabilize roll-up gate determinism across staged/unstaged/untracked diff states</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:committed]</t>
-  </si>
-  <si>
-    <t>Define transient-artifact hygiene policy for local/generated files without hiding governed outputs</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:committed]</t>
-  </si>
-  <si>
-    <t>Split migration changes into deterministic policy/management/product slices with per-slice gate evidence</t>
-  </si>
-  <si>
-    <t>Executed deterministic slice commits (`policy`, `management`, `product`) from generated manifest files and captured closure evidence under `management/pm/reports/workstream-j-slice-evidence.json`. [github:committed]</t>
-  </si>
-  <si>
-    <t>Reconcile project plan/progress/decision artifacts so open actions are reflected in next-step guidance</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:committed]</t>
-  </si>
-  <si>
-    <t>Re-run qualityGate plus PM refresh/report cycle and publish stabilization closure evidence</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` and executed PM refresh/report cycles to regenerate governance outputs after slice commits and issue-log synchronization. [github:committed]</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
     <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
   </si>
   <si>
@@ -632,6 +641,9 @@
     <t>2026-02-23T22:33:37Z</t>
   </si>
   <si>
+    <t>2026-02-23T22:39:03Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -795,6 +807,12 @@
   </si>
   <si>
     <t xml:space="preserve"> +@@@</t>
+  </si>
+  <si>
+    <t>55,100,100,100</t>
+  </si>
+  <si>
+    <t>+@@@</t>
   </si>
   <si>
     <t>Workstream A | complete graphics object rendering beyond placeholders (rules, boxes, strokes/fills)</t>
@@ -2058,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5453,7 +5471,7 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>99</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98">
@@ -5488,7 +5506,7 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>101</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99">
@@ -5523,7 +5541,7 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>103</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100">
@@ -5558,7 +5576,7 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="101">
@@ -5593,7 +5611,7 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102">
@@ -5628,7 +5646,7 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="103">
@@ -5663,12 +5681,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -5692,18 +5710,18 @@
         <v>164</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -5738,7 +5756,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -5773,7 +5791,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -5794,7 +5812,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -5808,7 +5826,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -5843,7 +5861,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -5874,6 +5892,111 @@
       </c>
       <c r="K109" t="s" s="0">
         <v>114</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="D110" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E110" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H110" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I110" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J110" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K110" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="D111" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E111" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H111" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I111" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J111" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K111" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D112" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E112" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H112" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I112" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J112" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K112" t="s" s="0">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -5883,7 +6006,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5897,7 +6020,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s" s="0">
         <v>115</v>
@@ -5906,16 +6029,16 @@
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
@@ -5929,7 +6052,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -5944,7 +6067,7 @@
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -5958,7 +6081,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -5973,7 +6096,7 @@
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -5987,7 +6110,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6002,7 +6125,7 @@
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -6016,7 +6139,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6031,7 +6154,7 @@
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
@@ -6045,7 +6168,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6060,7 +6183,7 @@
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
@@ -6074,7 +6197,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6089,7 +6212,7 @@
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -6103,7 +6226,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6118,7 +6241,7 @@
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
@@ -6132,7 +6255,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6147,7 +6270,7 @@
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -6161,7 +6284,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6176,7 +6299,7 @@
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -6190,7 +6313,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6205,7 +6328,7 @@
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -6219,7 +6342,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6234,7 +6357,7 @@
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13">
@@ -6248,7 +6371,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6263,7 +6386,7 @@
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
@@ -6277,7 +6400,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6292,7 +6415,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
@@ -6306,7 +6429,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6321,7 +6444,7 @@
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
@@ -6335,7 +6458,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6350,7 +6473,7 @@
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
@@ -6364,7 +6487,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6379,7 +6502,7 @@
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
@@ -6393,7 +6516,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6408,7 +6531,7 @@
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
@@ -6422,7 +6545,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6437,7 +6560,7 @@
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
@@ -6451,7 +6574,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6466,7 +6589,7 @@
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
@@ -6480,7 +6603,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -6495,7 +6618,7 @@
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22">
@@ -6509,7 +6632,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -6524,7 +6647,7 @@
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
@@ -6538,7 +6661,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -6553,7 +6676,7 @@
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24">
@@ -6567,7 +6690,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -6582,7 +6705,7 @@
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25">
@@ -6596,7 +6719,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -6611,7 +6734,7 @@
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
@@ -6625,7 +6748,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -6640,7 +6763,7 @@
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27">
@@ -6654,7 +6777,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -6669,7 +6792,7 @@
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
@@ -6683,7 +6806,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -6698,7 +6821,7 @@
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
@@ -6712,7 +6835,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -6727,7 +6850,7 @@
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30">
@@ -6741,7 +6864,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -6756,7 +6879,7 @@
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
@@ -6770,7 +6893,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -6785,7 +6908,7 @@
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32">
@@ -6799,7 +6922,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -6814,7 +6937,7 @@
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33">
@@ -6828,7 +6951,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -6843,7 +6966,7 @@
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34">
@@ -6857,7 +6980,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -6872,7 +6995,7 @@
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35">
@@ -6886,7 +7009,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -6901,7 +7024,7 @@
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -6915,7 +7038,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -6930,7 +7053,7 @@
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37">
@@ -6944,7 +7067,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -6959,7 +7082,7 @@
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38">
@@ -6973,7 +7096,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -6988,7 +7111,7 @@
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39">
@@ -7002,7 +7125,7 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
@@ -7017,7 +7140,7 @@
         <v>164</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40">
@@ -7031,7 +7154,7 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
@@ -7046,7 +7169,7 @@
         <v>167</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41">
@@ -7060,7 +7183,7 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
@@ -7075,7 +7198,7 @@
         <v>167</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42">
@@ -7089,7 +7212,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7101,10 +7224,10 @@
         <v>167</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43">
@@ -7118,7 +7241,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7130,10 +7253,10 @@
         <v>167</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44">
@@ -7147,7 +7270,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7159,10 +7282,10 @@
         <v>167</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45">
@@ -7176,7 +7299,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7185,13 +7308,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46">
@@ -7205,7 +7328,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7217,10 +7340,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47">
@@ -7234,7 +7357,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7246,10 +7369,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48">
@@ -7263,7 +7386,7 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
@@ -7278,7 +7401,7 @@
         <v>178</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49">
@@ -7292,7 +7415,7 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
@@ -7307,7 +7430,7 @@
         <v>167</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50">
@@ -7321,7 +7444,7 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
@@ -7336,7 +7459,7 @@
         <v>167</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51">
@@ -7350,7 +7473,7 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
@@ -7365,7 +7488,7 @@
         <v>167</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52">
@@ -7379,7 +7502,7 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
@@ -7394,7 +7517,7 @@
         <v>167</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53">
@@ -7408,7 +7531,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7417,13 +7540,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54">
@@ -7437,7 +7560,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7449,10 +7572,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55">
@@ -7466,7 +7589,7 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
@@ -7478,10 +7601,10 @@
         <v>187</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="56">
@@ -7495,7 +7618,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
@@ -7507,10 +7630,10 @@
         <v>189</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57">
@@ -7524,7 +7647,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -7536,10 +7659,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58">
@@ -7553,7 +7676,7 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
@@ -7562,13 +7685,13 @@
         <v>164</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59">
@@ -7582,7 +7705,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -7591,13 +7714,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60">
@@ -7611,7 +7734,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -7623,10 +7746,10 @@
         <v>167</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61">
@@ -7640,7 +7763,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -7652,10 +7775,10 @@
         <v>167</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62">
@@ -7669,7 +7792,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -7681,10 +7804,10 @@
         <v>167</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63">
@@ -7698,7 +7821,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -7710,10 +7833,10 @@
         <v>167</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64">
@@ -7727,7 +7850,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -7739,10 +7862,10 @@
         <v>167</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65">
@@ -7756,7 +7879,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -7768,10 +7891,10 @@
         <v>167</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66">
@@ -7785,7 +7908,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -7797,10 +7920,10 @@
         <v>167</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67">
@@ -7814,7 +7937,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -7826,10 +7949,10 @@
         <v>167</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68">
@@ -7843,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -7855,10 +7978,10 @@
         <v>167</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69">
@@ -7872,7 +7995,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -7884,10 +8007,10 @@
         <v>167</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70">
@@ -7901,7 +8024,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -7913,10 +8036,10 @@
         <v>167</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71">
@@ -7930,7 +8053,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -7942,10 +8065,10 @@
         <v>167</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72">
@@ -7959,7 +8082,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -7971,10 +8094,10 @@
         <v>167</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73">
@@ -7988,7 +8111,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8000,10 +8123,10 @@
         <v>167</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74">
@@ -8017,7 +8140,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8029,10 +8152,10 @@
         <v>167</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75">
@@ -8046,7 +8169,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8058,10 +8181,10 @@
         <v>167</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76">
@@ -8075,7 +8198,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8087,10 +8210,10 @@
         <v>167</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77">
@@ -8104,7 +8227,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8116,10 +8239,10 @@
         <v>167</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78">
@@ -8133,7 +8256,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8145,10 +8268,10 @@
         <v>167</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79">
@@ -8162,7 +8285,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8174,10 +8297,10 @@
         <v>167</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80">
@@ -8191,7 +8314,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8203,10 +8326,10 @@
         <v>167</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81">
@@ -8220,7 +8343,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8232,10 +8355,10 @@
         <v>167</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82">
@@ -8249,7 +8372,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8261,10 +8384,10 @@
         <v>167</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83">
@@ -8278,7 +8401,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8290,10 +8413,10 @@
         <v>167</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84">
@@ -8307,7 +8430,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8319,10 +8442,10 @@
         <v>167</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85">
@@ -8336,7 +8459,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8348,10 +8471,10 @@
         <v>167</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86">
@@ -8365,7 +8488,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8377,10 +8500,10 @@
         <v>167</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="87">
@@ -8394,7 +8517,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8406,10 +8529,10 @@
         <v>167</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88">
@@ -8423,7 +8546,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8435,10 +8558,10 @@
         <v>167</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89">
@@ -8452,7 +8575,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8464,10 +8587,10 @@
         <v>167</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90">
@@ -8481,7 +8604,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -8493,10 +8616,10 @@
         <v>167</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91">
@@ -8510,7 +8633,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -8522,10 +8645,10 @@
         <v>167</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92">
@@ -8539,7 +8662,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -8551,10 +8674,10 @@
         <v>167</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93">
@@ -8568,7 +8691,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -8580,10 +8703,10 @@
         <v>167</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94">
@@ -8597,7 +8720,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -8609,10 +8732,10 @@
         <v>167</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95">
@@ -8626,7 +8749,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -8638,10 +8761,10 @@
         <v>167</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="96">
@@ -8655,7 +8778,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -8667,10 +8790,10 @@
         <v>167</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97">
@@ -8684,7 +8807,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -8696,10 +8819,10 @@
         <v>167</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98">
@@ -8713,7 +8836,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -8725,10 +8848,10 @@
         <v>167</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99">
@@ -8742,7 +8865,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -8754,10 +8877,10 @@
         <v>167</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100">
@@ -8771,7 +8894,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -8783,10 +8906,10 @@
         <v>167</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101">
@@ -8800,7 +8923,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -8812,10 +8935,10 @@
         <v>167</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102">
@@ -8829,7 +8952,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -8841,10 +8964,10 @@
         <v>167</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103">
@@ -8858,7 +8981,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -8870,10 +8993,10 @@
         <v>167</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104">
@@ -8887,22 +9010,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105">
@@ -8916,7 +9039,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -8928,10 +9051,10 @@
         <v>167</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="106">
@@ -8945,7 +9068,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -8957,10 +9080,10 @@
         <v>167</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107">
@@ -8974,7 +9097,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -8983,13 +9106,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108">
@@ -9003,7 +9126,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9015,10 +9138,10 @@
         <v>167</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109">
@@ -9032,7 +9155,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9044,10 +9167,97 @@
         <v>167</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>252</v>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D110" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="E110" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F110" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G110" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H110" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="I110" t="s" s="0">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D111" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="E111" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F111" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G111" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H111" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="I111" t="s" s="0">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D112" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="E112" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F112" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G112" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="H112" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="I112" t="s" s="0">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -9062,147 +9272,147 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>11</v>
@@ -9342,7 +9552,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>11</v>
@@ -9482,7 +9692,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>124</v>
@@ -9622,7 +9832,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>124</v>
@@ -9736,13 +9946,13 @@
         <v>124</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="s" s="0">
         <v>11</v>
@@ -9754,7 +9964,7 @@
         <v>11</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AT5" t="s" s="0">
         <v>11</v>
@@ -9762,7 +9972,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>124</v>
@@ -9905,18 +10115,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -9924,10 +10134,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -9935,10 +10145,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -9946,10 +10156,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -9957,10 +10167,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -9968,10 +10178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -9979,10 +10189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -9990,10 +10200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10001,10 +10211,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10012,10 +10222,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10023,10 +10233,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10034,10 +10244,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10045,10 +10255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10056,10 +10266,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -10067,10 +10277,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -10078,10 +10288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -10089,10 +10299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -10100,10 +10310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -10111,10 +10321,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -10122,10 +10332,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -10133,10 +10343,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -10144,10 +10354,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -10155,10 +10365,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -10166,10 +10376,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -10177,10 +10387,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -10188,10 +10398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -10199,10 +10409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -10210,10 +10420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -10221,10 +10431,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -10232,10 +10442,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -10243,10 +10453,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -10254,10 +10464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -10265,10 +10475,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -10276,10 +10486,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -10287,10 +10497,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -10298,10 +10508,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -10309,10 +10519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -10320,10 +10530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -10331,10 +10541,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -10342,10 +10552,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -10353,10 +10563,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -10364,10 +10574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -10375,10 +10585,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -10386,10 +10596,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -10397,10 +10607,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Progress Graph" r:id="rId6" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2977" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="329">
   <si>
     <t>workstream</t>
   </si>
@@ -365,6 +365,39 @@
     <t>Ran `qualityGate` and executed PM refresh/report cycles to regenerate governance outputs after slice commits and issue-log synchronization. [github:committed]</t>
   </si>
   <si>
+    <t>Renderer Continuation 2026-02-23</t>
+  </si>
+  <si>
+    <t>Implement structured-field scope graph baseline for renderer continuation</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
+  </si>
+  <si>
+    <t>Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Pending implementation after scope graph baseline.</t>
+  </si>
+  <si>
+    <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
+  </si>
+  <si>
+    <t>Planned closeout task for first continuation slice.</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
@@ -509,21 +542,12 @@
     <t>2026-02-23T20:57:10Z</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>55</t>
   </si>
   <si>
     <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
   </si>
   <si>
@@ -644,6 +668,9 @@
     <t>2026-02-23T22:39:03Z</t>
   </si>
   <si>
+    <t>2026-02-23T23:01:31Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -815,6 +842,15 @@
     <t>+@@@</t>
   </si>
   <si>
+    <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
+  </si>
+  <si>
+    <t>Renderer Continuation 2026-02-23 | Implement structured-field scope graph baseline for renderer continuation</t>
+  </si>
+  <si>
+    <t>Renderer Continuation 2026-02-23 | Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
+  </si>
+  <si>
     <t>Workstream A | complete graphics object rendering beyond placeholders (rules, boxes, strokes/fills)</t>
   </si>
   <si>
@@ -951,6 +987,12 @@
   </si>
   <si>
     <t>latest_percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>.....</t>
   </si>
   <si>
     <t>@@@@@</t>
@@ -1007,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2068,20 +2110,89 @@
         <v>114</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="F48" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G46"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2090,25 +2201,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2116,7 +2227,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2125,19 +2236,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2146,12 +2257,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2160,19 +2271,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2181,12 +2292,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2195,19 +2306,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2216,12 +2327,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2230,19 +2341,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2251,12 +2362,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2265,19 +2376,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2286,12 +2397,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2300,19 +2411,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2321,12 +2432,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2335,19 +2446,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2356,12 +2467,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2370,19 +2481,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2391,12 +2502,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2405,19 +2516,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2426,12 +2537,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2440,19 +2551,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2461,12 +2572,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2475,19 +2586,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2496,12 +2607,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2510,19 +2621,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2531,12 +2642,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2545,19 +2656,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2566,12 +2677,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>137</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2580,19 +2691,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2601,12 +2712,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2615,19 +2726,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2636,12 +2747,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2650,19 +2761,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2671,12 +2782,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2685,19 +2796,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2706,12 +2817,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -2720,19 +2831,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -2741,12 +2852,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -2755,19 +2866,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -2776,12 +2887,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -2790,19 +2901,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -2811,12 +2922,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -2825,19 +2936,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -2846,12 +2957,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -2860,19 +2971,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -2881,12 +2992,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -2895,19 +3006,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -2916,12 +3027,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -2930,19 +3041,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -2951,12 +3062,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -2965,19 +3076,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -2986,12 +3097,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3000,19 +3111,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3021,12 +3132,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3035,19 +3146,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3056,12 +3167,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3070,19 +3181,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3091,12 +3202,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3105,19 +3216,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3126,12 +3237,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3140,19 +3251,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3161,12 +3272,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3175,19 +3286,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3196,12 +3307,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3210,19 +3321,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3231,12 +3342,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3245,19 +3356,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3266,12 +3377,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3280,19 +3391,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3301,12 +3412,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3315,19 +3426,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3336,12 +3447,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3350,19 +3461,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3371,12 +3482,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3385,19 +3496,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3406,12 +3517,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3420,33 +3531,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3455,33 +3566,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3490,33 +3601,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3546,12 +3657,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -3581,12 +3692,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -3616,12 +3727,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -3630,7 +3741,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3642,7 +3753,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3651,12 +3762,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -3665,7 +3776,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3677,7 +3788,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3686,12 +3797,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -3700,7 +3811,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -3712,7 +3823,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3721,12 +3832,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -3735,33 +3846,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -3770,33 +3881,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -3805,33 +3916,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -3840,33 +3951,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -3875,33 +3986,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -3910,7 +4021,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -3922,7 +4033,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -3931,12 +4042,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -3945,7 +4056,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -3957,7 +4068,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -3966,12 +4077,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -3980,10 +4091,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -3992,21 +4103,21 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4015,10 +4126,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4027,21 +4138,21 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4050,7 +4161,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4062,7 +4173,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4071,12 +4182,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4085,10 +4196,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4097,21 +4208,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4120,7 +4231,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4132,7 +4243,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4141,12 +4252,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4181,7 +4292,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4216,7 +4327,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4251,7 +4362,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4286,7 +4397,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4321,7 +4432,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4356,7 +4467,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4391,7 +4502,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4426,7 +4537,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4461,7 +4572,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4496,7 +4607,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4531,7 +4642,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4566,7 +4677,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -4601,7 +4712,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -4636,7 +4747,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -4671,7 +4782,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -4706,7 +4817,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -4741,7 +4852,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -4776,7 +4887,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -4811,7 +4922,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -4846,7 +4957,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -4881,7 +4992,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -4916,7 +5027,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -4951,7 +5062,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -4986,7 +5097,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5021,7 +5132,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5056,7 +5167,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5091,7 +5202,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5126,7 +5237,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5161,7 +5272,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5196,7 +5307,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5231,7 +5342,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5266,7 +5377,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5301,7 +5412,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5336,7 +5447,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5371,7 +5482,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5406,7 +5517,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5441,7 +5552,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5471,12 +5582,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5506,12 +5617,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5541,12 +5652,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5576,12 +5687,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -5611,12 +5722,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -5646,12 +5757,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -5681,12 +5792,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -5695,10 +5806,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5707,21 +5818,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -5756,7 +5867,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -5791,7 +5902,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -5800,7 +5911,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -5812,7 +5923,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -5826,7 +5937,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -5861,7 +5972,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -5896,7 +6007,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -5931,7 +6042,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -5966,7 +6077,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -5997,6 +6108,111 @@
       </c>
       <c r="K112" t="s" s="0">
         <v>103</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="D113" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F113" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="G113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H113" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="I113" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="J113" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K113" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D114" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="E114" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F114" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="G114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H114" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="I114" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="J114" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K114" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="D115" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F115" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="G115" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H115" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="I115" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="J115" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K115" t="s" s="0">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -6006,7 +6222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6020,25 +6236,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
@@ -6052,7 +6268,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6061,13 +6277,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
@@ -6081,7 +6297,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6090,13 +6306,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
@@ -6110,7 +6326,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6119,13 +6335,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5">
@@ -6139,7 +6355,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6148,13 +6364,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
@@ -6168,7 +6384,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6177,13 +6393,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
@@ -6197,7 +6413,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6206,13 +6422,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
@@ -6226,7 +6442,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6235,13 +6451,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
@@ -6255,7 +6471,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6264,13 +6480,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -6284,7 +6500,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6293,13 +6509,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -6313,7 +6529,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6322,13 +6538,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12">
@@ -6342,7 +6558,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6351,13 +6567,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
@@ -6371,7 +6587,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6380,13 +6596,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14">
@@ -6400,7 +6616,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6409,13 +6625,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15">
@@ -6429,7 +6645,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6438,13 +6654,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16">
@@ -6458,7 +6674,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6467,13 +6683,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -6487,7 +6703,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6496,13 +6712,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18">
@@ -6516,7 +6732,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6525,13 +6741,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19">
@@ -6545,7 +6761,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6554,13 +6770,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
@@ -6574,7 +6790,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6583,13 +6799,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21">
@@ -6603,7 +6819,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -6612,13 +6828,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22">
@@ -6632,7 +6848,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -6641,13 +6857,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23">
@@ -6661,7 +6877,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -6670,13 +6886,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24">
@@ -6690,7 +6906,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -6699,13 +6915,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25">
@@ -6719,7 +6935,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -6728,13 +6944,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26">
@@ -6748,7 +6964,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -6757,13 +6973,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27">
@@ -6777,7 +6993,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -6786,13 +7002,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28">
@@ -6806,7 +7022,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -6815,13 +7031,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29">
@@ -6835,7 +7051,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -6844,13 +7060,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
@@ -6864,7 +7080,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -6873,13 +7089,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31">
@@ -6893,7 +7109,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -6902,13 +7118,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32">
@@ -6922,7 +7138,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -6931,13 +7147,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33">
@@ -6951,7 +7167,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -6960,13 +7176,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34">
@@ -6980,7 +7196,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -6989,13 +7205,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35">
@@ -7009,7 +7225,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7018,13 +7234,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36">
@@ -7038,7 +7254,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7047,13 +7263,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37">
@@ -7067,7 +7283,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7076,13 +7292,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38">
@@ -7096,7 +7312,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7105,13 +7321,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
@@ -7125,22 +7341,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40">
@@ -7154,22 +7370,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41">
@@ -7183,22 +7399,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42">
@@ -7212,7 +7428,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7221,13 +7437,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43">
@@ -7241,7 +7457,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7250,13 +7466,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44">
@@ -7270,7 +7486,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7279,13 +7495,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45">
@@ -7299,7 +7515,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7308,13 +7524,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46">
@@ -7328,7 +7544,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7340,10 +7556,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47">
@@ -7357,7 +7573,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7369,10 +7585,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48">
@@ -7386,22 +7602,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49">
@@ -7415,22 +7631,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50">
@@ -7444,22 +7660,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51">
@@ -7473,22 +7689,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52">
@@ -7502,22 +7718,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53">
@@ -7531,7 +7747,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7540,13 +7756,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54">
@@ -7560,7 +7776,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7572,10 +7788,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55">
@@ -7589,22 +7805,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56">
@@ -7618,22 +7834,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57">
@@ -7647,7 +7863,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -7659,10 +7875,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58">
@@ -7676,22 +7892,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59">
@@ -7705,7 +7921,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -7714,13 +7930,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60">
@@ -7734,7 +7950,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -7743,13 +7959,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61">
@@ -7763,7 +7979,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -7772,13 +7988,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62">
@@ -7792,7 +8008,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -7801,13 +8017,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63">
@@ -7821,7 +8037,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -7830,13 +8046,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64">
@@ -7850,7 +8066,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -7859,13 +8075,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65">
@@ -7879,7 +8095,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -7888,13 +8104,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66">
@@ -7908,7 +8124,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -7917,13 +8133,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67">
@@ -7937,7 +8153,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -7946,13 +8162,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68">
@@ -7966,7 +8182,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -7975,13 +8191,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69">
@@ -7995,7 +8211,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8004,13 +8220,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70">
@@ -8024,7 +8240,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8033,13 +8249,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71">
@@ -8053,7 +8269,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8062,13 +8278,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72">
@@ -8082,7 +8298,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8091,13 +8307,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73">
@@ -8111,7 +8327,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8120,13 +8336,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="74">
@@ -8140,7 +8356,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8149,13 +8365,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75">
@@ -8169,7 +8385,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8178,13 +8394,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76">
@@ -8198,7 +8414,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8207,13 +8423,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="77">
@@ -8227,7 +8443,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8236,13 +8452,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78">
@@ -8256,7 +8472,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8265,13 +8481,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79">
@@ -8285,7 +8501,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8294,13 +8510,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80">
@@ -8314,7 +8530,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8323,13 +8539,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81">
@@ -8343,7 +8559,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8352,13 +8568,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82">
@@ -8372,7 +8588,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8381,13 +8597,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="83">
@@ -8401,7 +8617,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8410,13 +8626,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="84">
@@ -8430,7 +8646,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8439,13 +8655,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85">
@@ -8459,7 +8675,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8468,13 +8684,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86">
@@ -8488,7 +8704,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8497,13 +8713,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87">
@@ -8517,7 +8733,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8526,13 +8742,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88">
@@ -8546,7 +8762,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8555,13 +8771,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89">
@@ -8575,7 +8791,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8584,13 +8800,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="90">
@@ -8604,7 +8820,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -8613,13 +8829,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91">
@@ -8633,7 +8849,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -8642,13 +8858,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92">
@@ -8662,7 +8878,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -8671,13 +8887,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93">
@@ -8691,7 +8907,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -8700,13 +8916,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94">
@@ -8720,7 +8936,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -8729,13 +8945,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95">
@@ -8749,7 +8965,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -8758,13 +8974,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96">
@@ -8778,7 +8994,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -8787,13 +9003,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97">
@@ -8807,7 +9023,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -8816,13 +9032,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98">
@@ -8836,7 +9052,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -8845,13 +9061,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99">
@@ -8865,7 +9081,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -8874,13 +9090,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100">
@@ -8894,7 +9110,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -8903,13 +9119,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101">
@@ -8923,7 +9139,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -8932,13 +9148,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102">
@@ -8952,7 +9168,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -8961,13 +9177,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103">
@@ -8981,7 +9197,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -8990,13 +9206,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104">
@@ -9010,22 +9226,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105">
@@ -9039,7 +9255,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9048,13 +9264,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="106">
@@ -9068,7 +9284,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9077,13 +9293,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107">
@@ -9097,7 +9313,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9106,13 +9322,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108">
@@ -9126,7 +9342,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9135,13 +9351,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109">
@@ -9155,7 +9371,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9164,13 +9380,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110">
@@ -9184,7 +9400,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9193,13 +9409,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111">
@@ -9213,7 +9429,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9222,13 +9438,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112">
@@ -9242,7 +9458,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9251,13 +9467,100 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>256</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D113" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F113" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="G113" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="H113" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I113" t="s" s="0">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D114" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="E114" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F114" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="G114" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="H114" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I114" t="s" s="0">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D115" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F115" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="G115" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="H115" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I115" t="s" s="0">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -9267,161 +9570,170 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT54"/>
+  <dimension ref="A1:AW57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>309</v>
+        <v>318</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>321</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
@@ -9526,42 +9838,51 @@
         <v>11</v>
       </c>
       <c r="AM2" t="s" s="0">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="AN2" t="s" s="0">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="s" s="0">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="s" s="0">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>178</v>
+        <v>122</v>
+      </c>
+      <c r="AU2" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="AV2" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="AW2" t="s" s="0">
+        <v>186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>11</v>
@@ -9681,138 +10002,147 @@
         <v>11</v>
       </c>
       <c r="AR3" t="s" s="0">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="s" s="0">
-        <v>187</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="AV3" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="AW3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AP4" t="s" s="0">
         <v>11</v>
@@ -9824,135 +10154,144 @@
         <v>11</v>
       </c>
       <c r="AS4" t="s" s="0">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AU4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="AW4" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AP5" t="s" s="0">
         <v>11</v>
@@ -9964,150 +10303,168 @@
         <v>11</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>204</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AV5" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="AW5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>124</v>
+        <v>135</v>
+      </c>
+      <c r="AU6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AV6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="s" s="0">
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -10115,51 +10472,51 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>11</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>11</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -10167,10 +10524,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -10178,10 +10535,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -10189,10 +10546,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -10200,10 +10557,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10211,10 +10568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10222,10 +10579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10233,10 +10590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10244,10 +10601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10255,10 +10612,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10266,10 +10623,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -10277,10 +10634,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -10288,10 +10645,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -10299,10 +10656,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -10310,10 +10667,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -10321,10 +10678,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -10332,10 +10689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -10343,10 +10700,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -10354,10 +10711,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -10365,10 +10722,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -10376,10 +10733,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -10387,10 +10744,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -10398,10 +10755,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -10409,10 +10766,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -10420,10 +10777,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -10431,10 +10788,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -10442,10 +10799,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -10453,10 +10810,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -10464,10 +10821,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -10475,10 +10832,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -10486,10 +10843,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -10497,10 +10854,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -10508,10 +10865,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -10519,10 +10876,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -10530,10 +10887,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -10541,10 +10898,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -10552,10 +10909,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -10563,10 +10920,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -10574,10 +10931,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -10585,10 +10942,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -10596,10 +10953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -10607,12 +10964,45 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C54" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="C57" t="s" s="0">
         <v>11</v>
       </c>
     </row>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="336">
   <si>
     <t>workstream</t>
   </si>
@@ -371,304 +371,316 @@
     <t>Implement structured-field scope graph baseline for renderer continuation</t>
   </si>
   <si>
+    <t>Implemented `AfpScopeGraph` baseline analyzer and integrated scope-graph warnings/summary into interpreter diagnostics with dedicated unit coverage. [github:committed]</t>
+  </si>
+  <si>
+    <t>Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
+  </si>
+  <si>
     <t>In Progress</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
+  </si>
+  <si>
+    <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Planned closeout task for first continuation slice.</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:26:23Z</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:33:37Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:39:03Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:01:31Z</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
     <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
   </si>
   <si>
-    <t>Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Pending implementation after scope graph baseline.</t>
   </si>
   <si>
-    <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
-  </si>
-  <si>
-    <t>Planned closeout task for first continuation slice.</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:26:23Z</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:33:37Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:39:03Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:01:31Z</t>
+    <t>2026-02-23T23:07:45Z</t>
   </si>
   <si>
     <t>iteration</t>
@@ -821,9 +833,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>0,30,55,80,100</t>
   </si>
   <si>
@@ -842,6 +851,18 @@
     <t>+@@@</t>
   </si>
   <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>15,100</t>
+  </si>
+  <si>
+    <t>0,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> :</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -989,12 +1010,15 @@
     <t>latest_percent</t>
   </si>
   <si>
+    <t xml:space="preserve"> ::::</t>
+  </si>
+  <si>
+    <t>.@@@@</t>
+  </si>
+  <si>
     <t xml:space="preserve">     </t>
   </si>
   <si>
-    <t>.....</t>
-  </si>
-  <si>
     <t>@@@@@</t>
   </si>
   <si>
@@ -1002,9 +1026,6 @@
   </si>
   <si>
     <t xml:space="preserve"> @@@@</t>
-  </si>
-  <si>
-    <t>.@@@@</t>
   </si>
 </sst>
 </file>
@@ -2121,16 +2142,16 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s" s="0">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="F47" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G47" t="s" s="0">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48">
@@ -2138,22 +2159,22 @@
         <v>115</v>
       </c>
       <c r="B48" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E48" t="s" s="0">
         <v>120</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="E48" t="s" s="0">
-        <v>122</v>
       </c>
       <c r="F48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
@@ -2161,16 +2182,16 @@
         <v>115</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s" s="0">
         <v>98</v>
@@ -2187,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3534,7 +3555,7 @@
         <v>135</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F39" t="s" s="0">
         <v>135</v>
@@ -3569,7 +3590,7 @@
         <v>135</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F40" t="s" s="0">
         <v>135</v>
@@ -3581,7 +3602,7 @@
         <v>135</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
@@ -3604,7 +3625,7 @@
         <v>135</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F41" t="s" s="0">
         <v>135</v>
@@ -3616,7 +3637,7 @@
         <v>135</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
@@ -3741,7 +3762,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3776,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3788,7 +3809,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3811,7 +3832,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -3823,7 +3844,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3849,7 +3870,7 @@
         <v>135</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s" s="0">
         <v>135</v>
@@ -3884,7 +3905,7 @@
         <v>135</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F49" t="s" s="0">
         <v>135</v>
@@ -3896,7 +3917,7 @@
         <v>135</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
@@ -3919,7 +3940,7 @@
         <v>135</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s" s="0">
         <v>135</v>
@@ -3931,7 +3952,7 @@
         <v>135</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
@@ -3954,7 +3975,7 @@
         <v>135</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F51" t="s" s="0">
         <v>135</v>
@@ -3966,7 +3987,7 @@
         <v>135</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
@@ -3989,7 +4010,7 @@
         <v>135</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s" s="0">
         <v>135</v>
@@ -4001,7 +4022,7 @@
         <v>135</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
@@ -4021,7 +4042,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4056,7 +4077,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4068,7 +4089,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4091,10 +4112,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4103,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I55" t="s" s="0">
         <v>195</v>
@@ -4126,10 +4147,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4138,7 +4159,7 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I56" t="s" s="0">
         <v>197</v>
@@ -4161,7 +4182,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4173,7 +4194,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4196,10 +4217,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4231,7 +4252,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -5806,10 +5827,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5911,7 +5932,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6124,7 +6145,7 @@
         <v>135</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F113" t="s" s="0">
         <v>135</v>
@@ -6136,13 +6157,13 @@
         <v>135</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>119</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114">
@@ -6153,13 +6174,13 @@
         <v>115</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
         <v>135</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F114" t="s" s="0">
         <v>135</v>
@@ -6171,13 +6192,13 @@
         <v>135</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>123</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115">
@@ -6188,13 +6209,13 @@
         <v>115</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D115" t="s" s="0">
         <v>135</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F115" t="s" s="0">
         <v>135</v>
@@ -6206,13 +6227,83 @@
         <v>135</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
         <v>125</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="D116" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="E116" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H116" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="I116" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J116" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K116" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="J117" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K117" t="s" s="0">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6222,7 +6313,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6236,7 +6327,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E1" t="s" s="0">
         <v>126</v>
@@ -6245,16 +6336,16 @@
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2">
@@ -6268,7 +6359,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6283,7 +6374,7 @@
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3">
@@ -6297,7 +6388,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6312,7 +6403,7 @@
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
@@ -6326,7 +6417,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6341,7 +6432,7 @@
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
@@ -6355,7 +6446,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6370,7 +6461,7 @@
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
@@ -6384,7 +6475,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6399,7 +6490,7 @@
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
@@ -6413,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6428,7 +6519,7 @@
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -6442,7 +6533,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6457,7 +6548,7 @@
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
@@ -6471,7 +6562,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6486,7 +6577,7 @@
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -6500,7 +6591,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6515,7 +6606,7 @@
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -6529,7 +6620,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6544,7 +6635,7 @@
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
@@ -6558,7 +6649,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6573,7 +6664,7 @@
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
@@ -6587,7 +6678,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6602,7 +6693,7 @@
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
@@ -6616,7 +6707,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6631,7 +6722,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
@@ -6645,7 +6736,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6660,7 +6751,7 @@
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16">
@@ -6674,7 +6765,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6689,7 +6780,7 @@
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17">
@@ -6703,7 +6794,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6718,7 +6809,7 @@
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
@@ -6732,7 +6823,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6747,7 +6838,7 @@
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19">
@@ -6761,7 +6852,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6776,7 +6867,7 @@
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
@@ -6790,7 +6881,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6805,7 +6896,7 @@
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
@@ -6819,7 +6910,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -6834,7 +6925,7 @@
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22">
@@ -6848,7 +6939,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -6863,7 +6954,7 @@
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23">
@@ -6877,7 +6968,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -6892,7 +6983,7 @@
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
@@ -6906,7 +6997,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -6921,7 +7012,7 @@
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25">
@@ -6935,7 +7026,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -6950,7 +7041,7 @@
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26">
@@ -6964,7 +7055,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -6979,7 +7070,7 @@
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
@@ -6993,7 +7084,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7008,7 +7099,7 @@
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28">
@@ -7022,7 +7113,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7037,7 +7128,7 @@
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
@@ -7051,7 +7142,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7066,7 +7157,7 @@
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30">
@@ -7080,7 +7171,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7095,7 +7186,7 @@
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31">
@@ -7109,7 +7200,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7124,7 +7215,7 @@
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32">
@@ -7138,7 +7229,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7153,7 +7244,7 @@
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33">
@@ -7167,7 +7258,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7182,7 +7273,7 @@
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34">
@@ -7196,7 +7287,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7211,7 +7302,7 @@
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35">
@@ -7225,7 +7316,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7240,7 +7331,7 @@
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36">
@@ -7254,7 +7345,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7269,7 +7360,7 @@
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37">
@@ -7283,7 +7374,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7298,7 +7389,7 @@
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
@@ -7312,7 +7403,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7327,7 +7418,7 @@
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39">
@@ -7341,7 +7432,7 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
@@ -7356,7 +7447,7 @@
         <v>174</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40">
@@ -7370,22 +7461,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41">
@@ -7399,22 +7490,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42">
@@ -7428,7 +7519,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7437,13 +7528,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43">
@@ -7457,7 +7548,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7466,13 +7557,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44">
@@ -7486,7 +7577,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7495,13 +7586,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45">
@@ -7515,7 +7606,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7524,13 +7615,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46">
@@ -7544,7 +7635,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7556,10 +7647,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47">
@@ -7573,7 +7664,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7585,10 +7676,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48">
@@ -7602,7 +7693,7 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
@@ -7617,7 +7708,7 @@
         <v>186</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49">
@@ -7631,22 +7722,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50">
@@ -7660,22 +7751,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51">
@@ -7689,22 +7780,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52">
@@ -7718,22 +7809,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53">
@@ -7747,7 +7838,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7756,13 +7847,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54">
@@ -7776,7 +7867,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7788,10 +7879,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55">
@@ -7805,7 +7896,7 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
@@ -7817,10 +7908,10 @@
         <v>195</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56">
@@ -7834,7 +7925,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
@@ -7846,10 +7937,10 @@
         <v>197</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57">
@@ -7863,7 +7954,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -7875,10 +7966,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58">
@@ -7892,7 +7983,7 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
@@ -7901,13 +7992,13 @@
         <v>174</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59">
@@ -7921,7 +8012,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -7930,13 +8021,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -7950,7 +8041,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -7959,13 +8050,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61">
@@ -7979,7 +8070,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -7988,13 +8079,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62">
@@ -8008,7 +8099,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8017,13 +8108,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63">
@@ -8037,7 +8128,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8046,13 +8137,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64">
@@ -8066,7 +8157,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8075,13 +8166,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65">
@@ -8095,7 +8186,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8104,13 +8195,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66">
@@ -8124,7 +8215,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8133,13 +8224,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67">
@@ -8153,7 +8244,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8162,13 +8253,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68">
@@ -8182,7 +8273,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8191,13 +8282,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69">
@@ -8211,7 +8302,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8220,13 +8311,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70">
@@ -8240,7 +8331,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8249,13 +8340,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71">
@@ -8269,7 +8360,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8278,13 +8369,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72">
@@ -8298,7 +8389,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8307,13 +8398,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73">
@@ -8327,7 +8418,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8336,13 +8427,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74">
@@ -8356,7 +8447,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8365,13 +8456,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75">
@@ -8385,7 +8476,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8394,13 +8485,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76">
@@ -8414,7 +8505,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8423,13 +8514,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77">
@@ -8443,7 +8534,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8452,13 +8543,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78">
@@ -8472,7 +8563,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8481,13 +8572,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79">
@@ -8501,7 +8592,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8510,13 +8601,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80">
@@ -8530,7 +8621,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8539,13 +8630,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81">
@@ -8559,7 +8650,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8568,13 +8659,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82">
@@ -8588,7 +8679,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8597,13 +8688,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83">
@@ -8617,7 +8708,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8626,13 +8717,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84">
@@ -8646,7 +8737,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8655,13 +8746,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85">
@@ -8675,7 +8766,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8684,13 +8775,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86">
@@ -8704,7 +8795,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8713,13 +8804,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87">
@@ -8733,7 +8824,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8742,13 +8833,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88">
@@ -8762,7 +8853,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8771,13 +8862,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89">
@@ -8791,7 +8882,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8800,13 +8891,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90">
@@ -8820,7 +8911,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -8829,13 +8920,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91">
@@ -8849,7 +8940,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -8858,13 +8949,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92">
@@ -8878,7 +8969,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -8887,13 +8978,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93">
@@ -8907,7 +8998,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -8916,13 +9007,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94">
@@ -8936,7 +9027,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -8945,13 +9036,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95">
@@ -8965,7 +9056,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -8974,13 +9065,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96">
@@ -8994,7 +9085,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9003,13 +9094,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97">
@@ -9023,7 +9114,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9032,13 +9123,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98">
@@ -9052,7 +9143,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9061,13 +9152,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99">
@@ -9081,7 +9172,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9090,13 +9181,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="100">
@@ -9110,7 +9201,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9119,13 +9210,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101">
@@ -9139,7 +9230,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9148,13 +9239,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102">
@@ -9168,7 +9259,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9177,13 +9268,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103">
@@ -9197,7 +9288,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9206,13 +9297,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104">
@@ -9226,7 +9317,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
@@ -9235,13 +9326,13 @@
         <v>212</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105">
@@ -9255,7 +9346,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9264,13 +9355,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106">
@@ -9284,7 +9375,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9293,13 +9384,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="107">
@@ -9313,7 +9404,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9322,13 +9413,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108">
@@ -9342,7 +9433,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9351,13 +9442,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109">
@@ -9371,7 +9462,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9380,13 +9471,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -9400,7 +9491,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9409,13 +9500,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111">
@@ -9429,7 +9520,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9438,13 +9529,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112">
@@ -9458,7 +9549,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9467,13 +9558,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113">
@@ -9487,22 +9578,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114">
@@ -9510,28 +9601,28 @@
         <v>115</v>
       </c>
       <c r="B114" t="s" s="0">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115">
@@ -9539,28 +9630,86 @@
         <v>115</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>135</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>225</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D116" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="E116" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F116" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G116" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="H116" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="I116" t="s" s="0">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -9575,165 +9724,165 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
@@ -9850,22 +9999,22 @@
         <v>174</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AW2" t="s" s="0">
         <v>186</v>
@@ -9873,13 +10022,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>135</v>
@@ -10022,7 +10171,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>135</v>
@@ -10171,7 +10320,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>135</v>
@@ -10320,7 +10469,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>135</v>
@@ -10472,51 +10621,51 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>118</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -10524,10 +10673,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -10535,10 +10684,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -10546,10 +10695,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -10557,10 +10706,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10568,10 +10717,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10579,10 +10728,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10590,10 +10739,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10601,10 +10750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10612,10 +10761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10623,10 +10772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -10634,10 +10783,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -10645,10 +10794,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -10656,10 +10805,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -10667,10 +10816,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -10678,10 +10827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -10689,10 +10838,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -10700,10 +10849,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -10711,10 +10860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -10722,10 +10871,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -10733,10 +10882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -10744,10 +10893,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -10755,10 +10904,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -10766,10 +10915,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -10777,10 +10926,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -10788,10 +10937,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -10799,10 +10948,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -10810,10 +10959,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -10821,10 +10970,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -10832,10 +10981,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -10843,10 +10992,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -10854,10 +11003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -10865,10 +11014,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -10876,10 +11025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -10887,10 +11036,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -10898,10 +11047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -10909,10 +11058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -10920,10 +11069,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -10931,10 +11080,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -10942,10 +11091,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -10953,10 +11102,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -10964,10 +11113,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -10975,10 +11124,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -10986,10 +11135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -10997,10 +11146,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="341">
   <si>
     <t>workstream</t>
   </si>
@@ -377,310 +377,319 @@
     <t>Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
+    <t>Added deterministic paint-order assertion coverage in `AfpNativePdfRendererTest` using explicit signature probes for overlay/text/image interleave ordering. [github:committed]</t>
+  </si>
+  <si>
+    <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
+  </si>
+  <si>
     <t>In Progress</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Active closeout task: publish continuation diagnostics and updated next-step deltas after slice-2 commit.</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:26:23Z</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:33:37Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:39:03Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:01:31Z</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
+  </si>
+  <si>
+    <t>Pending implementation after scope graph baseline.</t>
+  </si>
+  <si>
+    <t>Planned closeout task for first continuation slice.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:07:45Z</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
     <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
   </si>
   <si>
-    <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Planned closeout task for first continuation slice.</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:26:23Z</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:33:37Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:39:03Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:01:31Z</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
-  </si>
-  <si>
-    <t>Pending implementation after scope graph baseline.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:07:45Z</t>
+    <t>2026-02-23T23:13:28Z</t>
   </si>
   <si>
     <t>iteration</t>
@@ -863,6 +872,12 @@
     <t xml:space="preserve"> :</t>
   </si>
   <si>
+    <t>0,20,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> :@</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -1010,13 +1025,13 @@
     <t>latest_percent</t>
   </si>
   <si>
-    <t xml:space="preserve"> ::::</t>
+    <t xml:space="preserve"> :@@@</t>
   </si>
   <si>
     <t>.@@@@</t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
+    <t xml:space="preserve"> ----</t>
   </si>
   <si>
     <t>@@@@@</t>
@@ -2165,16 +2180,16 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="F48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49">
@@ -2182,22 +2197,22 @@
         <v>115</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2208,12 +2223,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2222,25 +2237,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>131</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>133</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2248,7 +2263,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2257,19 +2272,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2278,12 +2293,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2292,19 +2307,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2313,12 +2328,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2327,19 +2342,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2348,12 +2363,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2362,19 +2377,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2383,12 +2398,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2397,19 +2412,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2418,12 +2433,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2432,19 +2447,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2453,12 +2468,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2467,19 +2482,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2488,12 +2503,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2502,19 +2517,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2523,12 +2538,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2537,19 +2552,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2558,12 +2573,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2572,19 +2587,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2593,12 +2608,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2607,19 +2622,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2628,12 +2643,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2642,19 +2657,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2663,12 +2678,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2677,19 +2692,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2698,12 +2713,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2712,19 +2727,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2733,12 +2748,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2747,19 +2762,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2768,12 +2783,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2782,19 +2797,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2803,12 +2818,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2817,19 +2832,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2838,12 +2853,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -2852,19 +2867,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -2873,12 +2888,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -2887,19 +2902,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -2908,12 +2923,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -2922,19 +2937,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -2943,12 +2958,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -2957,19 +2972,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -2978,12 +2993,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -2992,19 +3007,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3013,12 +3028,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3027,19 +3042,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3048,12 +3063,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3062,19 +3077,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3083,12 +3098,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3097,19 +3112,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3118,12 +3133,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3132,19 +3147,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3153,12 +3168,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3167,19 +3182,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3188,12 +3203,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3202,19 +3217,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3223,12 +3238,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3237,19 +3252,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3258,12 +3273,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3272,19 +3287,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3293,12 +3308,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3307,19 +3322,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3328,12 +3343,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3342,19 +3357,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3363,12 +3378,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3377,19 +3392,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3398,12 +3413,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3412,19 +3427,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3433,12 +3448,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3447,19 +3462,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3468,12 +3483,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3482,19 +3497,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3503,12 +3518,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3517,19 +3532,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3538,12 +3553,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3552,33 +3567,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3587,22 +3602,22 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
@@ -3613,7 +3628,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3622,22 +3637,22 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
@@ -3762,7 +3777,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3774,7 +3789,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3797,7 +3812,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3809,7 +3824,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3832,7 +3847,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -3844,7 +3859,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3867,19 +3882,19 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I48" t="s" s="0">
         <v>186</v>
@@ -3902,22 +3917,22 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
@@ -3937,22 +3952,22 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
@@ -3972,22 +3987,22 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
@@ -4007,22 +4022,22 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
@@ -4042,7 +4057,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4077,7 +4092,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4089,7 +4104,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4112,10 +4127,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4124,16 +4139,16 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56">
@@ -4147,10 +4162,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4159,16 +4174,16 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57">
@@ -4182,7 +4197,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4194,7 +4209,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4203,12 +4218,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4217,10 +4232,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4229,21 +4244,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4252,7 +4267,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4264,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4273,12 +4288,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4313,7 +4328,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4348,7 +4363,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4383,7 +4398,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4418,7 +4433,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4453,7 +4468,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4488,7 +4503,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4523,7 +4538,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4558,7 +4573,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4593,7 +4608,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4628,7 +4643,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4663,7 +4678,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4698,7 +4713,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -4733,7 +4748,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -4768,7 +4783,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -4803,7 +4818,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -4838,7 +4853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -4873,7 +4888,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -4908,7 +4923,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -4943,7 +4958,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -4978,7 +4993,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -5013,7 +5028,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -5048,7 +5063,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -5083,7 +5098,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -5118,7 +5133,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5153,7 +5168,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5188,7 +5203,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5223,7 +5238,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5258,7 +5273,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5293,7 +5308,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5328,7 +5343,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5363,7 +5378,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5398,7 +5413,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5433,7 +5448,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5468,7 +5483,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5503,7 +5518,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5538,7 +5553,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5573,7 +5588,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5603,12 +5618,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5638,12 +5653,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5673,12 +5688,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5708,12 +5723,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -5743,12 +5758,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -5778,12 +5793,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -5813,12 +5828,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -5827,10 +5842,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5839,21 +5854,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -5888,7 +5903,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -5923,7 +5938,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -5932,7 +5947,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -5944,7 +5959,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -5958,7 +5973,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -5993,7 +6008,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -6028,7 +6043,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -6063,7 +6078,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -6098,7 +6113,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -6133,7 +6148,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>115</v>
@@ -6142,33 +6157,33 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>115</v>
@@ -6177,63 +6192,63 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>115</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>125</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116">
@@ -6247,7 +6262,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6259,7 +6274,7 @@
         <v>9</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I116" t="s" s="0">
         <v>11</v>
@@ -6282,10 +6297,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6294,16 +6309,86 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="J117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K117" t="s" s="0">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="D118" t="s" s="0">
         <v>121</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H118" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="I118" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J118" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K118" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F119" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G119" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H119" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="I119" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="J119" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K119" t="s" s="0">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6313,7 +6398,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6327,25 +6412,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
@@ -6359,7 +6444,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6368,13 +6453,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
@@ -6388,7 +6473,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6397,13 +6482,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
@@ -6417,7 +6502,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6426,13 +6511,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
@@ -6446,7 +6531,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6455,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
@@ -6475,7 +6560,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6484,13 +6569,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
@@ -6504,7 +6589,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6513,13 +6598,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
@@ -6533,7 +6618,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6542,13 +6627,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -6562,7 +6647,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6571,13 +6656,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -6591,7 +6676,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6600,13 +6685,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -6620,7 +6705,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6629,13 +6714,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12">
@@ -6649,7 +6734,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6658,13 +6743,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
@@ -6678,7 +6763,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6687,13 +6772,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -6707,7 +6792,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6716,13 +6801,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15">
@@ -6736,7 +6821,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6745,13 +6830,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">
@@ -6765,7 +6850,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6774,13 +6859,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17">
@@ -6794,7 +6879,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6803,13 +6888,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18">
@@ -6823,7 +6908,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6832,13 +6917,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19">
@@ -6852,7 +6937,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6861,13 +6946,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
@@ -6881,7 +6966,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6890,13 +6975,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21">
@@ -6910,7 +6995,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -6919,13 +7004,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22">
@@ -6939,7 +7024,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -6948,13 +7033,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
@@ -6968,7 +7053,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -6977,13 +7062,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24">
@@ -6997,7 +7082,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7006,13 +7091,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
@@ -7026,7 +7111,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7035,13 +7120,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26">
@@ -7055,7 +7140,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7064,13 +7149,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27">
@@ -7084,7 +7169,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7093,13 +7178,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28">
@@ -7113,7 +7198,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7122,13 +7207,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29">
@@ -7142,7 +7227,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7151,13 +7236,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30">
@@ -7171,7 +7256,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7180,13 +7265,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31">
@@ -7200,7 +7285,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7209,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32">
@@ -7229,7 +7314,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7238,13 +7323,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33">
@@ -7258,7 +7343,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7267,13 +7352,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34">
@@ -7287,7 +7372,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7296,13 +7381,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35">
@@ -7316,7 +7401,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7325,13 +7410,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36">
@@ -7345,7 +7430,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7354,13 +7439,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37">
@@ -7374,7 +7459,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7383,13 +7468,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38">
@@ -7403,7 +7488,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7412,13 +7497,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
@@ -7432,22 +7517,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40">
@@ -7461,22 +7546,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41">
@@ -7490,22 +7575,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42">
@@ -7519,7 +7604,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7528,13 +7613,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="43">
@@ -7548,7 +7633,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7557,13 +7642,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44">
@@ -7577,7 +7662,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7586,13 +7671,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45">
@@ -7606,7 +7691,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7615,13 +7700,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46">
@@ -7635,7 +7720,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7647,10 +7732,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47">
@@ -7664,7 +7749,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7676,10 +7761,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48">
@@ -7693,7 +7778,7 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
@@ -7702,13 +7787,13 @@
         <v>186</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H48" t="s" s="0">
         <v>186</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49">
@@ -7722,22 +7807,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50">
@@ -7751,22 +7836,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51">
@@ -7780,22 +7865,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52">
@@ -7809,22 +7894,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53">
@@ -7838,7 +7923,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7847,13 +7932,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54">
@@ -7867,7 +7952,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7879,10 +7964,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55">
@@ -7896,22 +7981,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56">
@@ -7925,22 +8010,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57">
@@ -7954,7 +8039,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -7966,10 +8051,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58">
@@ -7983,22 +8068,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59">
@@ -8012,7 +8097,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8021,13 +8106,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60">
@@ -8041,7 +8126,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8050,13 +8135,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61">
@@ -8070,7 +8155,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8079,13 +8164,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62">
@@ -8099,7 +8184,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8108,13 +8193,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63">
@@ -8128,7 +8213,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8137,13 +8222,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="64">
@@ -8157,7 +8242,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8166,13 +8251,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65">
@@ -8186,7 +8271,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8195,13 +8280,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="66">
@@ -8215,7 +8300,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8224,13 +8309,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="67">
@@ -8244,7 +8329,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8253,13 +8338,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68">
@@ -8273,7 +8358,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8282,13 +8367,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69">
@@ -8302,7 +8387,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8311,13 +8396,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70">
@@ -8331,7 +8416,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8340,13 +8425,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71">
@@ -8360,7 +8445,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8369,13 +8454,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72">
@@ -8389,7 +8474,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8398,13 +8483,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73">
@@ -8418,7 +8503,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8427,13 +8512,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74">
@@ -8447,7 +8532,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8456,13 +8541,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75">
@@ -8476,7 +8561,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8485,13 +8570,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="76">
@@ -8505,7 +8590,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8514,13 +8599,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77">
@@ -8534,7 +8619,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8543,13 +8628,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78">
@@ -8563,7 +8648,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8572,13 +8657,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79">
@@ -8592,7 +8677,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8601,13 +8686,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80">
@@ -8621,7 +8706,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8630,13 +8715,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="81">
@@ -8650,7 +8735,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8659,13 +8744,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82">
@@ -8679,7 +8764,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8688,13 +8773,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="83">
@@ -8708,7 +8793,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8717,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84">
@@ -8737,7 +8822,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8746,13 +8831,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="85">
@@ -8766,7 +8851,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8775,13 +8860,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="86">
@@ -8795,7 +8880,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8804,13 +8889,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="87">
@@ -8824,7 +8909,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8833,13 +8918,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88">
@@ -8853,7 +8938,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8862,13 +8947,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="89">
@@ -8882,7 +8967,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8891,13 +8976,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="90">
@@ -8911,7 +8996,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -8920,13 +9005,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91">
@@ -8940,7 +9025,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -8949,13 +9034,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92">
@@ -8969,7 +9054,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -8978,13 +9063,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93">
@@ -8998,7 +9083,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9007,13 +9092,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94">
@@ -9027,7 +9112,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9036,13 +9121,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95">
@@ -9056,7 +9141,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9065,13 +9150,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96">
@@ -9085,7 +9170,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9094,13 +9179,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97">
@@ -9114,7 +9199,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9123,13 +9208,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98">
@@ -9143,7 +9228,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9152,13 +9237,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99">
@@ -9172,7 +9257,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9181,13 +9266,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100">
@@ -9201,7 +9286,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9210,13 +9295,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101">
@@ -9230,7 +9315,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9239,13 +9324,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102">
@@ -9259,7 +9344,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9268,13 +9353,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103">
@@ -9288,7 +9373,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9297,13 +9382,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104">
@@ -9317,22 +9402,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="105">
@@ -9346,7 +9431,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9355,13 +9440,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106">
@@ -9375,7 +9460,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9384,13 +9469,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107">
@@ -9404,7 +9489,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9413,13 +9498,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="108">
@@ -9433,7 +9518,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9442,13 +9527,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109">
@@ -9462,7 +9547,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9471,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110">
@@ -9491,7 +9576,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9500,13 +9585,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="111">
@@ -9520,7 +9605,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9529,13 +9614,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112">
@@ -9549,7 +9634,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9558,13 +9643,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113">
@@ -9578,22 +9663,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114">
@@ -9607,22 +9692,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115">
@@ -9630,28 +9715,28 @@
         <v>115</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116">
@@ -9665,7 +9750,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -9674,13 +9759,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117">
@@ -9694,22 +9779,80 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F117" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="H117" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="I117" t="s" s="0">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D118" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F118" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G118" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="H118" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="I118" t="s" s="0">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B119" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="G117" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="H117" t="s" s="0">
-        <v>279</v>
-      </c>
-      <c r="I117" t="s" s="0">
-        <v>280</v>
+      <c r="C119" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F119" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="G119" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="H119" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="I119" t="s" s="0">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -9724,165 +9867,165 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
@@ -9996,25 +10139,25 @@
         <v>11</v>
       </c>
       <c r="AP2" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="AW2" t="s" s="0">
         <v>186</v>
@@ -10022,16 +10165,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>11</v>
@@ -10160,10 +10303,10 @@
         <v>11</v>
       </c>
       <c r="AU3" t="s" s="0">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AV3" t="s" s="0">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="AW3" t="s" s="0">
         <v>11</v>
@@ -10171,127 +10314,127 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="X4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AE4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AP4" t="s" s="0">
         <v>11</v>
@@ -10312,7 +10455,7 @@
         <v>11</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AW4" t="s" s="0">
         <v>11</v>
@@ -10320,127 +10463,127 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AP5" t="s" s="0">
         <v>11</v>
@@ -10461,7 +10604,7 @@
         <v>11</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AW5" t="s" s="0">
         <v>11</v>
@@ -10469,142 +10612,142 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AU6" t="s" s="0">
         <v>11</v>
@@ -10613,7 +10756,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
@@ -10621,29 +10764,29 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>120</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -10651,21 +10794,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -10673,10 +10816,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -10684,10 +10827,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -10695,10 +10838,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -10706,10 +10849,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10717,10 +10860,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10728,10 +10871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10739,10 +10882,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10750,10 +10893,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10761,10 +10904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10772,10 +10915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -10783,10 +10926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -10794,10 +10937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -10805,10 +10948,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -10816,10 +10959,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -10827,10 +10970,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -10838,10 +10981,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -10849,10 +10992,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -10860,10 +11003,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -10871,10 +11014,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -10882,10 +11025,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -10893,10 +11036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -10904,10 +11047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -10915,10 +11058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -10926,10 +11069,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -10937,10 +11080,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -10948,10 +11091,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -10959,10 +11102,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -10970,10 +11113,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -10981,10 +11124,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -10992,10 +11135,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -11003,10 +11146,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -11014,10 +11157,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -11025,10 +11168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -11036,10 +11179,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -11047,10 +11190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -11058,10 +11201,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -11069,10 +11212,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -11080,10 +11223,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -11091,10 +11234,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -11102,10 +11245,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -11113,10 +11256,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -11124,10 +11267,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -11135,10 +11278,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -11146,10 +11289,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="346">
   <si>
     <t>workstream</t>
   </si>
@@ -383,313 +383,319 @@
     <t>Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
   </si>
   <si>
+    <t>Published continuation diagnostics and refreshed next-step/report deltas after slice-2 validation cycle. [github:committed]</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
     <t>In Progress</t>
   </si>
   <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:26:23Z</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:33:37Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:39:03Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:01:31Z</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
+  </si>
+  <si>
+    <t>Pending implementation after scope graph baseline.</t>
+  </si>
+  <si>
+    <t>Planned closeout task for first continuation slice.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:07:45Z</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:13:28Z</t>
+  </si>
+  <si>
     <t>Active closeout task: publish continuation diagnostics and updated next-step deltas after slice-2 commit.</t>
   </si>
   <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:26:23Z</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:33:37Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:39:03Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:01:31Z</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
-  </si>
-  <si>
-    <t>Pending implementation after scope graph baseline.</t>
-  </si>
-  <si>
-    <t>Planned closeout task for first continuation slice.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:07:45Z</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:13:28Z</t>
+    <t>2026-02-23T23:22:39Z</t>
   </si>
   <si>
     <t>iteration</t>
@@ -878,6 +884,15 @@
     <t xml:space="preserve"> :@</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>0,30,100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -@</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -1031,7 +1046,7 @@
     <t>.@@@@</t>
   </si>
   <si>
-    <t xml:space="preserve"> ----</t>
+    <t xml:space="preserve"> -@@@</t>
   </si>
   <si>
     <t>@@@@@</t>
@@ -2203,16 +2218,16 @@
         <v>33</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2223,12 +2238,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2237,25 +2252,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>129</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>131</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2263,7 +2278,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2272,19 +2287,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2293,12 +2308,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2307,19 +2322,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2328,12 +2343,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2342,19 +2357,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2363,12 +2378,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2377,19 +2392,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2398,12 +2413,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2412,19 +2427,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2433,12 +2448,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2447,19 +2462,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2468,12 +2483,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2482,19 +2497,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2503,12 +2518,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2517,19 +2532,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2538,12 +2553,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2552,19 +2567,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2573,12 +2588,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2587,19 +2602,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2608,12 +2623,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2622,19 +2637,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2643,12 +2658,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2657,19 +2672,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2678,12 +2693,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2692,19 +2707,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2713,12 +2728,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2727,19 +2742,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2748,12 +2763,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2762,19 +2777,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2783,12 +2798,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2797,19 +2812,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2818,12 +2833,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2832,19 +2847,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2853,12 +2868,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -2867,19 +2882,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -2888,12 +2903,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -2902,19 +2917,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -2923,12 +2938,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -2937,19 +2952,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -2958,12 +2973,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -2972,19 +2987,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -2993,12 +3008,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3007,19 +3022,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3028,12 +3043,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3042,19 +3057,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3063,12 +3078,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3077,19 +3092,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3098,12 +3113,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3112,19 +3127,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3133,12 +3148,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3147,19 +3162,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3168,12 +3183,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3182,19 +3197,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3203,12 +3218,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3217,19 +3232,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3238,12 +3253,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3252,19 +3267,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3273,12 +3288,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3287,19 +3302,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3308,12 +3323,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3322,19 +3337,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3343,12 +3358,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3357,19 +3372,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3378,12 +3393,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3392,19 +3407,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3413,12 +3428,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3427,19 +3442,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3448,12 +3463,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3462,19 +3477,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3483,12 +3498,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3497,19 +3512,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3518,12 +3533,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3532,19 +3547,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3553,12 +3568,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3567,33 +3582,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3602,33 +3617,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E40" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I40" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F40" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G40" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H40" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I40" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3637,33 +3652,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I41" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F41" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G41" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I41" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3693,12 +3708,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -3728,12 +3743,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -3763,12 +3778,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -3777,7 +3792,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3789,7 +3804,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3798,12 +3813,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -3812,19 +3827,19 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H46" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E46" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G46" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H46" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3833,12 +3848,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -3847,19 +3862,19 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H47" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E47" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G47" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H47" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3868,12 +3883,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -3882,33 +3897,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -3917,33 +3932,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E49" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H49" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I49" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F49" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G49" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H49" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I49" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -3952,33 +3967,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E50" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H50" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I50" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F50" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G50" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H50" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I50" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -3987,33 +4002,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E51" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H51" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I51" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F51" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G51" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H51" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I51" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -4022,33 +4037,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E52" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H52" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I52" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F52" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G52" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H52" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I52" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -4057,7 +4072,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4069,7 +4084,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -4078,12 +4093,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -4092,19 +4107,19 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H54" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E54" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G54" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H54" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4113,12 +4128,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -4127,22 +4142,22 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H55" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="E55" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="F55" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G55" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H55" t="s" s="0">
-        <v>175</v>
-      </c>
       <c r="I55" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
@@ -4153,7 +4168,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4162,19 +4177,19 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H56" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E56" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="F56" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G56" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H56" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I56" t="s" s="0">
         <v>196</v>
@@ -4188,7 +4203,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4197,19 +4212,19 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H57" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E57" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G57" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H57" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4232,10 +4247,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4244,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
@@ -4267,7 +4282,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -5842,10 +5857,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5854,7 +5869,7 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I104" t="s" s="0">
         <v>211</v>
@@ -5947,7 +5962,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6157,19 +6172,19 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I113" t="s" s="0">
         <v>216</v>
@@ -6192,22 +6207,22 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E114" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F114" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G114" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H114" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I114" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="F114" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="G114" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H114" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="I114" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
@@ -6227,22 +6242,22 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
@@ -6262,7 +6277,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6297,19 +6312,19 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="F117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H117" t="s" s="0">
         <v>174</v>
-      </c>
-      <c r="E117" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="F117" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="G117" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="H117" t="s" s="0">
-        <v>175</v>
       </c>
       <c r="I117" t="s" s="0">
         <v>221</v>
@@ -6332,7 +6347,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6367,10 +6382,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6379,16 +6394,51 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="J119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>123</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G120" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H120" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="I120" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J120" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K120" t="s" s="0">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6398,7 +6448,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6412,25 +6462,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2">
@@ -6444,7 +6494,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6453,13 +6503,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
@@ -6473,7 +6523,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6482,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
@@ -6502,7 +6552,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6511,13 +6561,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -6531,7 +6581,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6540,13 +6590,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6">
@@ -6560,7 +6610,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6569,13 +6619,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7">
@@ -6589,7 +6639,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6598,13 +6648,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -6618,7 +6668,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6627,13 +6677,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
@@ -6647,7 +6697,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6656,13 +6706,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -6676,7 +6726,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6685,13 +6735,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -6705,7 +6755,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6714,13 +6764,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12">
@@ -6734,7 +6784,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6743,13 +6793,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
@@ -6763,7 +6813,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6772,13 +6822,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -6792,7 +6842,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6801,13 +6851,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15">
@@ -6821,7 +6871,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6830,13 +6880,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
@@ -6850,7 +6900,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6859,13 +6909,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
@@ -6879,7 +6929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6888,13 +6938,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
@@ -6908,7 +6958,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6917,13 +6967,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19">
@@ -6937,7 +6987,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6946,13 +6996,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20">
@@ -6966,7 +7016,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -6975,13 +7025,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
@@ -6995,7 +7045,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -7004,13 +7054,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22">
@@ -7024,7 +7074,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -7033,13 +7083,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23">
@@ -7053,7 +7103,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -7062,13 +7112,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24">
@@ -7082,7 +7132,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7091,13 +7141,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25">
@@ -7111,7 +7161,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7120,13 +7170,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26">
@@ -7140,7 +7190,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7149,13 +7199,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27">
@@ -7169,7 +7219,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7178,13 +7228,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28">
@@ -7198,7 +7248,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7207,13 +7257,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29">
@@ -7227,7 +7277,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7236,13 +7286,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30">
@@ -7256,7 +7306,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7265,13 +7315,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31">
@@ -7285,7 +7335,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7294,13 +7344,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32">
@@ -7314,7 +7364,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7323,13 +7373,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
@@ -7343,7 +7393,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7352,13 +7402,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34">
@@ -7372,7 +7422,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7381,13 +7431,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35">
@@ -7401,7 +7451,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7410,13 +7460,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36">
@@ -7430,7 +7480,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7439,13 +7489,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37">
@@ -7459,7 +7509,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7468,13 +7518,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38">
@@ -7488,7 +7538,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7497,13 +7547,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39">
@@ -7517,22 +7567,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40">
@@ -7546,22 +7596,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41">
@@ -7575,22 +7625,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42">
@@ -7604,7 +7654,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7613,13 +7663,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43">
@@ -7633,7 +7683,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7642,13 +7692,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44">
@@ -7662,7 +7712,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7671,13 +7721,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45">
@@ -7691,7 +7741,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7700,13 +7750,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46">
@@ -7720,7 +7770,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7732,10 +7782,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47">
@@ -7749,7 +7799,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7761,10 +7811,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48">
@@ -7778,22 +7828,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49">
@@ -7807,22 +7857,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50">
@@ -7836,22 +7886,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51">
@@ -7865,22 +7915,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52">
@@ -7894,22 +7944,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53">
@@ -7923,7 +7973,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7932,13 +7982,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54">
@@ -7952,7 +8002,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -7964,10 +8014,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55">
@@ -7981,22 +8031,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56">
@@ -8010,7 +8060,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
@@ -8022,10 +8072,10 @@
         <v>196</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57">
@@ -8039,7 +8089,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -8051,10 +8101,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58">
@@ -8068,22 +8118,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="59">
@@ -8097,7 +8147,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8106,13 +8156,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60">
@@ -8126,7 +8176,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8135,13 +8185,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61">
@@ -8155,7 +8205,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8164,13 +8214,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62">
@@ -8184,7 +8234,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8193,13 +8243,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63">
@@ -8213,7 +8263,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8222,13 +8272,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64">
@@ -8242,7 +8292,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8251,13 +8301,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65">
@@ -8271,7 +8321,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8280,13 +8330,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66">
@@ -8300,7 +8350,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8309,13 +8359,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67">
@@ -8329,7 +8379,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8338,13 +8388,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68">
@@ -8358,7 +8408,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8367,13 +8417,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69">
@@ -8387,7 +8437,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8396,13 +8446,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70">
@@ -8416,7 +8466,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8425,13 +8475,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71">
@@ -8445,7 +8495,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8454,13 +8504,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72">
@@ -8474,7 +8524,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8483,13 +8533,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73">
@@ -8503,7 +8553,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8512,13 +8562,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74">
@@ -8532,7 +8582,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8541,13 +8591,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75">
@@ -8561,7 +8611,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8570,13 +8620,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76">
@@ -8590,7 +8640,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8599,13 +8649,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77">
@@ -8619,7 +8669,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8628,13 +8678,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78">
@@ -8648,7 +8698,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8657,13 +8707,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79">
@@ -8677,7 +8727,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8686,13 +8736,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80">
@@ -8706,7 +8756,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8715,13 +8765,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81">
@@ -8735,7 +8785,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8744,13 +8794,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82">
@@ -8764,7 +8814,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8773,13 +8823,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83">
@@ -8793,7 +8843,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8802,13 +8852,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84">
@@ -8822,7 +8872,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8831,13 +8881,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85">
@@ -8851,7 +8901,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8860,13 +8910,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86">
@@ -8880,7 +8930,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8889,13 +8939,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87">
@@ -8909,7 +8959,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8918,13 +8968,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88">
@@ -8938,7 +8988,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8947,13 +8997,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89">
@@ -8967,7 +9017,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -8976,13 +9026,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90">
@@ -8996,7 +9046,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -9005,13 +9055,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91">
@@ -9025,7 +9075,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -9034,13 +9084,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92">
@@ -9054,7 +9104,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -9063,13 +9113,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93">
@@ -9083,7 +9133,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9092,13 +9142,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94">
@@ -9112,7 +9162,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9121,13 +9171,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95">
@@ -9141,7 +9191,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9150,13 +9200,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96">
@@ -9170,7 +9220,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9179,13 +9229,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97">
@@ -9199,7 +9249,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9208,13 +9258,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98">
@@ -9228,7 +9278,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9237,13 +9287,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99">
@@ -9257,7 +9307,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9266,13 +9316,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100">
@@ -9286,7 +9336,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9295,13 +9345,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="101">
@@ -9315,7 +9365,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9324,13 +9374,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102">
@@ -9344,7 +9394,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9353,13 +9403,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103">
@@ -9373,7 +9423,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9382,13 +9432,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104">
@@ -9402,7 +9452,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
@@ -9411,13 +9461,13 @@
         <v>211</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105">
@@ -9431,7 +9481,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9440,13 +9490,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106">
@@ -9460,7 +9510,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9469,13 +9519,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="107">
@@ -9489,7 +9539,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9501,10 +9551,10 @@
         <v>221</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108">
@@ -9518,7 +9568,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9527,13 +9577,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109">
@@ -9547,7 +9597,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9556,13 +9606,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="110">
@@ -9576,7 +9626,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9585,13 +9635,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111">
@@ -9605,7 +9655,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9614,13 +9664,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="112">
@@ -9634,7 +9684,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9643,13 +9693,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113">
@@ -9663,7 +9713,7 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
@@ -9672,13 +9722,13 @@
         <v>216</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H113" t="s" s="0">
         <v>216</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114">
@@ -9692,22 +9742,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115">
@@ -9721,22 +9771,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116">
@@ -9750,7 +9800,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -9759,13 +9809,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117">
@@ -9779,7 +9829,7 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
@@ -9791,10 +9841,10 @@
         <v>221</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="118">
@@ -9808,7 +9858,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -9820,10 +9870,10 @@
         <v>211</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119">
@@ -9837,22 +9887,51 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>246</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F120" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G120" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="H120" t="s" s="0">
+        <v>289</v>
+      </c>
+      <c r="I120" t="s" s="0">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -9867,165 +9946,165 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>216</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
@@ -10139,33 +10218,33 @@
         <v>11</v>
       </c>
       <c r="AP2" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AW2" t="s" s="0">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>221</v>
@@ -10174,7 +10253,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>11</v>
@@ -10306,7 +10385,7 @@
         <v>196</v>
       </c>
       <c r="AV3" t="s" s="0">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="AW3" t="s" s="0">
         <v>11</v>
@@ -10314,127 +10393,127 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AE4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AP4" t="s" s="0">
         <v>11</v>
@@ -10455,7 +10534,7 @@
         <v>11</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AW4" t="s" s="0">
         <v>11</v>
@@ -10463,127 +10542,127 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AP5" t="s" s="0">
         <v>11</v>
@@ -10612,142 +10691,142 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AU6" t="s" s="0">
         <v>11</v>
@@ -10756,7 +10835,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9">
@@ -10764,18 +10843,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -10783,10 +10862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -10794,21 +10873,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>122</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -10816,10 +10895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -10827,10 +10906,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -10838,10 +10917,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -10849,10 +10928,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10860,10 +10939,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10871,10 +10950,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10882,10 +10961,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10893,10 +10972,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10904,10 +10983,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10915,10 +10994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -10926,10 +11005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -10937,10 +11016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -10948,10 +11027,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -10959,10 +11038,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -10970,10 +11049,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -10981,10 +11060,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -10992,10 +11071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -11003,10 +11082,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -11014,10 +11093,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -11025,10 +11104,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -11036,10 +11115,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -11047,10 +11126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -11058,10 +11137,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -11069,10 +11148,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -11080,10 +11159,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -11091,10 +11170,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -11102,10 +11181,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -11113,10 +11192,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -11124,10 +11203,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -11135,10 +11214,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -11146,10 +11225,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -11157,10 +11236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -11168,10 +11247,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -11179,10 +11258,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -11190,10 +11269,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -11201,10 +11280,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -11212,10 +11291,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -11223,10 +11302,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -11234,10 +11313,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -11245,10 +11324,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -11256,10 +11335,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -11267,10 +11346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -11278,10 +11357,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -11289,10 +11368,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Progress Graph" r:id="rId6" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$52</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="366">
   <si>
     <t>workstream</t>
   </si>
@@ -386,6 +386,33 @@
     <t>Published continuation diagnostics and refreshed next-step/report deltas after slice-2 validation cycle. [github:committed]</t>
   </si>
   <si>
+    <t>Renderer Continuation 2026-02-23-B</t>
+  </si>
+  <si>
+    <t>Add scope-graph transition diagnostics breakdown for continuation triage</t>
+  </si>
+  <si>
+    <t>Implemented scope-graph transition breakdown diagnostics (begin/end/underflow/final depth per scope) and validated interpreter coverage in unit tests. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Add deterministic ordering assertions for resource-depth tie cases across paint kinds</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Pending after scope-graph diagnostics slice.</t>
+  </si>
+  <si>
+    <t>Publish continuation diagnostics and next-step delta after slice validations</t>
+  </si>
+  <si>
+    <t>Closeout task for WS-2026-002.</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
@@ -539,12 +566,6 @@
     <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
   </si>
   <si>
@@ -698,6 +719,18 @@
     <t>2026-02-23T23:22:39Z</t>
   </si>
   <si>
+    <t>2026-02-23T23:29:45Z</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Slice 1 implementation underway to enrich scope-graph diagnostics for faster render-scope triage.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:30:47Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -893,6 +926,18 @@
     <t xml:space="preserve"> -@</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>35,100</t>
+  </si>
+  <si>
+    <t>-@</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -902,6 +947,15 @@
     <t>Renderer Continuation 2026-02-23 | Publish updated fidelity diagnostics and next-step deltas for continuation slice</t>
   </si>
   <si>
+    <t>Renderer Continuation 2026-02-23-B | Add deterministic ordering assertions for resource-depth tie cases across paint kinds</t>
+  </si>
+  <si>
+    <t>Renderer Continuation 2026-02-23-B | Add scope-graph transition diagnostics breakdown for continuation triage</t>
+  </si>
+  <si>
+    <t>Renderer Continuation 2026-02-23-B | Publish continuation diagnostics and next-step delta after slice validations</t>
+  </si>
+  <si>
     <t>Workstream A | complete graphics object rendering beyond placeholders (rules, boxes, strokes/fills)</t>
   </si>
   <si>
@@ -1047,6 +1101,12 @@
   </si>
   <si>
     <t xml:space="preserve"> -@@@</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t>-@@@@</t>
   </si>
   <si>
     <t>@@@@@</t>
@@ -1100,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2230,20 +2290,89 @@
         <v>121</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2252,25 +2381,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2278,7 +2407,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2287,19 +2416,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2308,12 +2437,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2322,19 +2451,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2343,12 +2472,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2357,19 +2486,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2378,12 +2507,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2392,19 +2521,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2413,12 +2542,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2427,19 +2556,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2448,12 +2577,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2462,19 +2591,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2483,12 +2612,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2497,19 +2626,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2518,12 +2647,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2532,19 +2661,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2553,12 +2682,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2567,19 +2696,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2588,12 +2717,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2602,19 +2731,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2623,12 +2752,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2637,19 +2766,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2658,12 +2787,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2672,19 +2801,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2693,12 +2822,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2707,19 +2836,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2728,12 +2857,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2742,19 +2871,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2763,12 +2892,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2777,19 +2906,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2798,12 +2927,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2812,19 +2941,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2833,12 +2962,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2847,19 +2976,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2868,12 +2997,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -2882,19 +3011,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -2903,12 +3032,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -2917,19 +3046,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -2938,12 +3067,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -2952,19 +3081,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -2973,12 +3102,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -2987,19 +3116,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -3008,12 +3137,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3022,19 +3151,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3043,12 +3172,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3057,19 +3186,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3078,12 +3207,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3092,19 +3221,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3113,12 +3242,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3127,19 +3256,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3148,12 +3277,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3162,19 +3291,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3183,12 +3312,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3197,19 +3326,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3218,12 +3347,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3232,19 +3361,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3253,12 +3382,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3267,19 +3396,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3288,12 +3417,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3302,19 +3431,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3323,12 +3452,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3337,19 +3466,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3358,12 +3487,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3372,19 +3501,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3393,12 +3522,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3407,19 +3536,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3428,12 +3557,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3442,19 +3571,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3463,12 +3592,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3477,19 +3606,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3498,12 +3627,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3512,19 +3641,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3533,12 +3662,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3547,19 +3676,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3568,12 +3697,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3582,33 +3711,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3617,33 +3746,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3652,33 +3781,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3708,12 +3837,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -3743,12 +3872,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -3778,12 +3907,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -3792,7 +3921,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3804,7 +3933,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3813,12 +3942,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -3827,7 +3956,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3839,7 +3968,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3848,12 +3977,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -3862,7 +3991,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -3874,7 +4003,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -3883,12 +4012,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -3897,33 +4026,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -3932,33 +4061,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -3967,33 +4096,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -4002,33 +4131,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -4037,33 +4166,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -4072,7 +4201,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4084,7 +4213,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -4093,12 +4222,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -4107,7 +4236,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4119,7 +4248,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4128,12 +4257,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -4142,10 +4271,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4154,21 +4283,21 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4177,10 +4306,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4189,21 +4318,21 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4212,7 +4341,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4224,7 +4353,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4233,12 +4362,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4247,10 +4376,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4259,21 +4388,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4282,7 +4411,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4294,7 +4423,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4303,12 +4432,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4343,7 +4472,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4378,7 +4507,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4413,7 +4542,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4448,7 +4577,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4483,7 +4612,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4518,7 +4647,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4553,7 +4682,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4588,7 +4717,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4623,7 +4752,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4658,7 +4787,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4693,7 +4822,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4728,7 +4857,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -4763,7 +4892,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -4798,7 +4927,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -4833,7 +4962,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -4868,7 +4997,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -4903,7 +5032,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -4938,7 +5067,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -4973,7 +5102,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -5008,7 +5137,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -5043,7 +5172,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -5078,7 +5207,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -5113,7 +5242,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -5148,7 +5277,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5183,7 +5312,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5218,7 +5347,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5253,7 +5382,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5288,7 +5417,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5323,7 +5452,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5358,7 +5487,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5393,7 +5522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5428,7 +5557,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5463,7 +5592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5498,7 +5627,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5533,7 +5662,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5568,7 +5697,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5603,7 +5732,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5633,12 +5762,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5668,12 +5797,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5703,12 +5832,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5738,12 +5867,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -5773,12 +5902,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -5808,12 +5937,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -5843,12 +5972,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -5857,10 +5986,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5869,21 +5998,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -5918,7 +6047,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -5953,7 +6082,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -5962,7 +6091,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -5974,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -5988,7 +6117,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -6023,7 +6152,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -6058,7 +6187,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -6093,7 +6222,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -6128,7 +6257,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -6163,7 +6292,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>115</v>
@@ -6172,33 +6301,33 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>115</v>
@@ -6207,33 +6336,33 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>115</v>
@@ -6242,33 +6371,33 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>115</v>
@@ -6277,7 +6406,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6289,7 +6418,7 @@
         <v>9</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I116" t="s" s="0">
         <v>11</v>
@@ -6303,7 +6432,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B117" t="s" s="0">
         <v>115</v>
@@ -6312,10 +6441,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6324,21 +6453,21 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="J117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K117" t="s" s="0">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>115</v>
@@ -6347,7 +6476,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6359,7 +6488,7 @@
         <v>9</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I118" t="s" s="0">
         <v>11</v>
@@ -6373,7 +6502,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B119" t="s" s="0">
         <v>115</v>
@@ -6382,10 +6511,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6394,21 +6523,21 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="J119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>115</v>
@@ -6417,7 +6546,7 @@
         <v>120</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>10</v>
@@ -6429,7 +6558,7 @@
         <v>33</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="I120" t="s" s="0">
         <v>11</v>
@@ -6439,6 +6568,146 @@
       </c>
       <c r="K120" t="s" s="0">
         <v>121</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="G121" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H121" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="I121" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="J121" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K121" t="s" s="0">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F122" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="G122" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H122" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="I122" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="J122" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K122" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F123" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="G123" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H123" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="I123" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="J123" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K123" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H124" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="I124" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J124" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K124" t="s" s="0">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6448,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6462,25 +6731,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2">
@@ -6494,7 +6763,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6503,13 +6772,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -6523,7 +6792,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6532,13 +6801,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -6552,7 +6821,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6561,13 +6830,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
@@ -6581,7 +6850,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6590,13 +6859,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
@@ -6610,7 +6879,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6619,13 +6888,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
@@ -6639,7 +6908,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6648,13 +6917,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -6668,7 +6937,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6677,13 +6946,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9">
@@ -6697,7 +6966,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6706,13 +6975,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -6726,7 +6995,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -6735,13 +7004,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -6755,7 +7024,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -6764,13 +7033,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -6784,7 +7053,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -6793,13 +7062,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13">
@@ -6813,7 +7082,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -6822,13 +7091,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
@@ -6842,7 +7111,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -6851,13 +7120,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15">
@@ -6871,7 +7140,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -6880,13 +7149,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
@@ -6900,7 +7169,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -6909,13 +7178,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17">
@@ -6929,7 +7198,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -6938,13 +7207,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18">
@@ -6958,7 +7227,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -6967,13 +7236,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19">
@@ -6987,7 +7256,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -6996,13 +7265,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20">
@@ -7016,7 +7285,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -7025,13 +7294,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21">
@@ -7045,7 +7314,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -7054,13 +7323,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22">
@@ -7074,7 +7343,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -7083,13 +7352,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23">
@@ -7103,7 +7372,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -7112,13 +7381,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
@@ -7132,7 +7401,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7141,13 +7410,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25">
@@ -7161,7 +7430,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7170,13 +7439,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26">
@@ -7190,7 +7459,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7199,13 +7468,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27">
@@ -7219,7 +7488,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7228,13 +7497,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28">
@@ -7248,7 +7517,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7257,13 +7526,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29">
@@ -7277,7 +7546,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7286,13 +7555,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30">
@@ -7306,7 +7575,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7315,13 +7584,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31">
@@ -7335,7 +7604,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7344,13 +7613,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32">
@@ -7364,7 +7633,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7373,13 +7642,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33">
@@ -7393,7 +7662,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7402,13 +7671,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34">
@@ -7422,7 +7691,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7431,13 +7700,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35">
@@ -7451,7 +7720,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7460,13 +7729,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36">
@@ -7480,7 +7749,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7489,13 +7758,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37">
@@ -7509,7 +7778,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7518,13 +7787,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38">
@@ -7538,7 +7807,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7547,13 +7816,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39">
@@ -7567,22 +7836,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40">
@@ -7596,22 +7865,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41">
@@ -7625,22 +7894,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42">
@@ -7654,7 +7923,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7663,13 +7932,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43">
@@ -7683,7 +7952,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7692,13 +7961,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44">
@@ -7712,7 +7981,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7721,13 +7990,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45">
@@ -7741,7 +8010,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -7750,13 +8019,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46">
@@ -7770,7 +8039,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -7782,10 +8051,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47">
@@ -7799,7 +8068,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -7811,10 +8080,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48">
@@ -7828,22 +8097,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49">
@@ -7857,22 +8126,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50">
@@ -7886,22 +8155,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51">
@@ -7915,22 +8184,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52">
@@ -7944,22 +8213,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53">
@@ -7973,7 +8242,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -7982,13 +8251,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54">
@@ -8002,7 +8271,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -8014,10 +8283,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55">
@@ -8031,22 +8300,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56">
@@ -8060,22 +8329,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57">
@@ -8089,7 +8358,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -8101,10 +8370,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="58">
@@ -8118,22 +8387,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59">
@@ -8147,7 +8416,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8156,13 +8425,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60">
@@ -8176,7 +8445,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8185,13 +8454,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61">
@@ -8205,7 +8474,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8214,13 +8483,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62">
@@ -8234,7 +8503,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8243,13 +8512,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63">
@@ -8263,7 +8532,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8272,13 +8541,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64">
@@ -8292,7 +8561,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8301,13 +8570,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65">
@@ -8321,7 +8590,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8330,13 +8599,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="66">
@@ -8350,7 +8619,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8359,13 +8628,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67">
@@ -8379,7 +8648,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8388,13 +8657,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68">
@@ -8408,7 +8677,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8417,13 +8686,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69">
@@ -8437,7 +8706,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8446,13 +8715,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70">
@@ -8466,7 +8735,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8475,13 +8744,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71">
@@ -8495,7 +8764,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8504,13 +8773,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72">
@@ -8524,7 +8793,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8533,13 +8802,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73">
@@ -8553,7 +8822,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8562,13 +8831,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74">
@@ -8582,7 +8851,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8591,13 +8860,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75">
@@ -8611,7 +8880,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8620,13 +8889,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76">
@@ -8640,7 +8909,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8649,13 +8918,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77">
@@ -8669,7 +8938,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8678,13 +8947,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78">
@@ -8698,7 +8967,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8707,13 +8976,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79">
@@ -8727,7 +8996,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -8736,13 +9005,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80">
@@ -8756,7 +9025,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -8765,13 +9034,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81">
@@ -8785,7 +9054,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -8794,13 +9063,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82">
@@ -8814,7 +9083,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -8823,13 +9092,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83">
@@ -8843,7 +9112,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -8852,13 +9121,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84">
@@ -8872,7 +9141,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -8881,13 +9150,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85">
@@ -8901,7 +9170,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -8910,13 +9179,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86">
@@ -8930,7 +9199,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -8939,13 +9208,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87">
@@ -8959,7 +9228,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -8968,13 +9237,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="88">
@@ -8988,7 +9257,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -8997,13 +9266,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="89">
@@ -9017,7 +9286,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -9026,13 +9295,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90">
@@ -9046,7 +9315,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -9055,13 +9324,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91">
@@ -9075,7 +9344,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -9084,13 +9353,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92">
@@ -9104,7 +9373,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -9113,13 +9382,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93">
@@ -9133,7 +9402,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9142,13 +9411,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94">
@@ -9162,7 +9431,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9171,13 +9440,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95">
@@ -9191,7 +9460,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9200,13 +9469,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96">
@@ -9220,7 +9489,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9229,13 +9498,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97">
@@ -9249,7 +9518,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9258,13 +9527,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98">
@@ -9278,7 +9547,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9287,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="99">
@@ -9307,7 +9576,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9316,13 +9585,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100">
@@ -9336,7 +9605,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9345,13 +9614,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101">
@@ -9365,7 +9634,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9374,13 +9643,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102">
@@ -9394,7 +9663,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9403,13 +9672,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="103">
@@ -9423,7 +9692,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9432,13 +9701,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="104">
@@ -9452,22 +9721,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="105">
@@ -9481,7 +9750,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9490,13 +9759,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="106">
@@ -9510,7 +9779,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9519,13 +9788,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107">
@@ -9539,7 +9808,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9548,13 +9817,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="108">
@@ -9568,7 +9837,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9577,13 +9846,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109">
@@ -9597,7 +9866,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9606,13 +9875,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110">
@@ -9626,7 +9895,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9635,13 +9904,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111">
@@ -9655,7 +9924,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9664,13 +9933,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112">
@@ -9684,7 +9953,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9693,13 +9962,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="113">
@@ -9713,22 +9982,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114">
@@ -9742,22 +10011,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115">
@@ -9771,22 +10040,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116">
@@ -9800,7 +10069,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -9809,13 +10078,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="117">
@@ -9829,22 +10098,22 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G117" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="118">
@@ -9858,7 +10127,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -9867,13 +10136,13 @@
         <v>11</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>287</v>
+        <v>298</v>
       </c>
     </row>
     <row r="119">
@@ -9887,22 +10156,22 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="120">
@@ -9916,7 +10185,7 @@
         <v>33</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>98</v>
@@ -9925,13 +10194,129 @@
         <v>11</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I120" t="s" s="0">
-        <v>290</v>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F121" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="G121" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="H121" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="I121" t="s" s="0">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F122" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="G122" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="H122" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="I122" t="s" s="0">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F123" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="G123" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="H123" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="I123" t="s" s="0">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F124" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G124" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="H124" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="I124" t="s" s="0">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -9941,179 +10326,188 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AW57"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>338</v>
+        <v>353</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>356</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>234</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
@@ -10218,51 +10612,60 @@
         <v>11</v>
       </c>
       <c r="AP2" t="s" s="0">
-        <v>171</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="s" s="0">
-        <v>174</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>174</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="AW2" t="s" s="0">
-        <v>185</v>
+        <v>127</v>
+      </c>
+      <c r="AX2" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="AY2" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="AZ2" t="s" s="0">
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
@@ -10382,147 +10785,156 @@
         <v>11</v>
       </c>
       <c r="AU3" t="s" s="0">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="s" s="0">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AX3" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="AY3" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="AZ3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>131</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AQ4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AR4" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AS4" t="s" s="0">
         <v>11</v>
@@ -10534,144 +10946,153 @@
         <v>11</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>171</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AX4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AY4" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="AZ4" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AS5" t="s" s="0">
         <v>11</v>
@@ -10683,159 +11104,177 @@
         <v>11</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AX5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="AZ5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>131</v>
+        <v>140</v>
+      </c>
+      <c r="AX6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AY6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="AZ6" t="s" s="0">
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -10843,18 +11282,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>339</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -10862,10 +11301,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -10873,10 +11312,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -10884,21 +11323,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>11</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -10906,21 +11345,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>11</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -10928,10 +11367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -10939,10 +11378,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -10950,10 +11389,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -10961,10 +11400,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -10972,10 +11411,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -10983,10 +11422,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -10994,10 +11433,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -11005,10 +11444,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -11016,10 +11455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -11027,10 +11466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -11038,10 +11477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -11049,10 +11488,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -11060,10 +11499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -11071,10 +11510,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -11082,10 +11521,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -11093,10 +11532,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -11104,10 +11543,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -11115,10 +11554,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -11126,10 +11565,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -11137,10 +11576,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -11148,10 +11587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -11159,10 +11598,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -11170,10 +11609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -11181,10 +11620,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -11192,10 +11631,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -11203,10 +11642,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -11214,10 +11653,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -11225,10 +11664,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -11236,10 +11675,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -11247,10 +11686,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -11258,10 +11697,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -11269,10 +11708,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -11280,10 +11719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -11291,10 +11730,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -11302,10 +11741,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -11313,10 +11752,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -11324,10 +11763,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -11335,10 +11774,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -11346,10 +11785,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -11357,10 +11796,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -11368,12 +11807,45 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C57" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>288</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s" s="0">
         <v>11</v>
       </c>
     </row>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="372">
   <si>
     <t>workstream</t>
   </si>
@@ -392,343 +392,358 @@
     <t>Add scope-graph transition diagnostics breakdown for continuation triage</t>
   </si>
   <si>
+    <t>Implemented scope-graph transition breakdown diagnostics (begin/end/underflow/final depth per scope) and validated interpreter coverage in unit tests. [github:committed]</t>
+  </si>
+  <si>
+    <t>Add deterministic ordering assertions for resource-depth tie cases across paint kinds</t>
+  </si>
+  <si>
+    <t>Added deterministic resource-depth tie paint-order assertions across image/graphic/text kinds in `AfpNativePdfRendererTest`. [github:committed]</t>
+  </si>
+  <si>
+    <t>Publish continuation diagnostics and next-step delta after slice validations</t>
+  </si>
+  <si>
+    <t>Published continuation diagnostics and refreshed next-step/report deltas after WS-2026-002 slice validations. [github:committed]</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>previous_status</t>
+  </si>
+  <si>
+    <t>new_status</t>
+  </si>
+  <si>
+    <t>previous_priority</t>
+  </si>
+  <si>
+    <t>new_priority</t>
+  </si>
+  <si>
+    <t>previous_percent</t>
+  </si>
+  <si>
+    <t>new_percent</t>
+  </si>
+  <si>
+    <t>csv_last_updated</t>
+  </si>
+  <si>
+    <t>2026-02-23T19:13:46Z</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
+  </si>
+  <si>
+    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
+  </si>
+  <si>
+    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
+  </si>
+  <si>
+    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
+  </si>
+  <si>
+    <t>Render and diagnostics flags exposed and documented.</t>
+  </si>
+  <si>
+    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>qualityGate and publishCiArtifacts are active and passing.</t>
+  </si>
+  <si>
+    <t>AfpPrintCentricTraceEngine established and integrated.</t>
+  </si>
+  <si>
+    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
+  </si>
+  <si>
+    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
+  </si>
+  <si>
+    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
+  </si>
+  <si>
+    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
+  </si>
+  <si>
+    <t>Realm naming and path references updated for policy/management/product semantics.</t>
+  </si>
+  <si>
+    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
+  </si>
+  <si>
+    <t>2026-02-23T20:57:10Z</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
+  </si>
+  <si>
+    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:05:19Z</t>
+  </si>
+  <si>
+    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
+  </si>
+  <si>
+    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
+  </si>
+  <si>
+    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:47:26Z</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
+  </si>
+  <si>
+    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
+  </si>
+  <si>
+    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
+  </si>
+  <si>
+    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
+  </si>
+  <si>
+    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:49:59Z</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
+  </si>
+  <si>
+    <t>2026-02-23T21:59:35Z</t>
+  </si>
+  <si>
+    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:25:04Z</t>
+  </si>
+  <si>
+    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:26:23Z</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:33:37Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T22:39:03Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:01:31Z</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
+  </si>
+  <si>
+    <t>Pending implementation after scope graph baseline.</t>
+  </si>
+  <si>
+    <t>Planned closeout task for first continuation slice.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:07:45Z</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:13:28Z</t>
+  </si>
+  <si>
+    <t>Active closeout task: publish continuation diagnostics and updated next-step deltas after slice-2 commit.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:22:39Z</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:29:45Z</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Slice 1 implementation underway to enrich scope-graph diagnostics for faster render-scope triage.</t>
+  </si>
+  <si>
+    <t>Pending after scope-graph diagnostics slice.</t>
+  </si>
+  <si>
+    <t>Closeout task for WS-2026-002.</t>
+  </si>
+  <si>
+    <t>2026-02-23T23:30:47Z</t>
+  </si>
+  <si>
     <t>Implemented scope-graph transition breakdown diagnostics (begin/end/underflow/final depth per scope) and validated interpreter coverage in unit tests. [github:not-committed]</t>
   </si>
   <si>
-    <t>Add deterministic ordering assertions for resource-depth tie cases across paint kinds</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Pending after scope-graph diagnostics slice.</t>
-  </si>
-  <si>
-    <t>Publish continuation diagnostics and next-step delta after slice validations</t>
-  </si>
-  <si>
-    <t>Closeout task for WS-2026-002.</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>previous_status</t>
-  </si>
-  <si>
-    <t>new_status</t>
-  </si>
-  <si>
-    <t>previous_priority</t>
-  </si>
-  <si>
-    <t>new_priority</t>
-  </si>
-  <si>
-    <t>previous_percent</t>
-  </si>
-  <si>
-    <t>new_percent</t>
-  </si>
-  <si>
-    <t>csv_last_updated</t>
-  </si>
-  <si>
-    <t>2026-02-23T19:13:46Z</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Implemented deterministic object model and scope tracking in native renderer.</t>
-  </si>
-  <si>
-    <t>Single ordered paint stream and base/overlay pass execution in place.</t>
-  </si>
-  <si>
-    <t>Core line/box primitives implemented; additional AFP graphics semantics still pending. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Orientation-aware transforms and clipping implemented; synthetic fallback removed, placeholders gated by image evidence, image-object counting tightened to BIM/EIM, embedded image resolution now requires explicit AFPLib token overlap between BIM and BOC/EOC resources, draw-path prefers resource-resolved images before raw decode, selection policy runs through ImageResolutionService, and render-time resource selection is now strict per-image-index (no cross-index fallback bleed). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Scoped CFI resolution implemented; sample path gaps remain due missing SCFL/CFI visibility. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Mixed run decode and mapping diagnostics implemented; further parity tuning required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Initial metric/spacing tuning added; still significant visual drift vs IBM sample. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Fallback narrowed substantially; low-signal run-level fallback retained only for guarded unresolved paths. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Common signature-based and raw fallback paths available; coverage not exhaustive. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Image decode confidence and fallback diagnostics emitted in meta/diag outputs; raw-candidate classification filters structured UTF-16-like payloads and now reports descriptor payload counts/resource hints.</t>
-  </si>
-  <si>
-    <t>Per-format tests added and image-heavy sample included; corpus expansion remains. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>RenderPolicy and DiagnosticsPolicy added and wired through conversion options.</t>
-  </si>
-  <si>
-    <t>Render and diagnostics flags exposed and documented.</t>
-  </si>
-  <si>
-    <t>Font/image/resource/print-centric trace diagnostics added; image binding diagnostics now include per-page BIM/candidate/overlap tokens plus candidate payload size and byte-prefix evidence, with explicit image render-path decisions (embedded/resource/raw/unresolved). Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Current corpus has limited coverage and needs broader document diversity. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Strong test base exists; additional parity-focused regression slices still required. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>qualityGate and publishCiArtifacts are active and passing.</t>
-  </si>
-  <si>
-    <t>AfpPrintCentricTraceEngine established and integrated.</t>
-  </si>
-  <si>
-    <t>Trace events, SF/PTX histograms, and byte histogram are emitted.</t>
-  </si>
-  <si>
-    <t>Added operand-level PDF text operator traces, normalized PTX/alias histograms, cross-exam inference hints, and BIM/BOC/EOC timeline slices with inferred binding pairs. Closed in single-cycle optimization pass.</t>
-  </si>
-  <si>
-    <t>Extended PTX alias normalization and image evidence diagnostics, filtered non-raster BIM payloads, switched to deterministic matching, surfaced token+payload binding evidence (sample shows JPEG candidate payload with zero BIM token overlap), implemented evidence-driven resource-first image selection with dedicated image-resolution policy service, and added confidence-aware embedded-resource matching (token/sequence/size heuristics) with strict per-object fallback behavior. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added dedicated project-state and boilerplate-state SQLite databases with Gradle task integration; workflow JSON/reporting outputs now route through pm-tools database tooling.</t>
-  </si>
-  <si>
-    <t>Governance alerts now emit from project-state SQLite and constitutional policy requires human-visible breach reporting plus trust-event logging through governance CSV/DB sync.</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added `enforceProjectBoundaries` and wired it into `qualityGate`; product modules now fail verification if they reference pm-tools classes or project-management state sources.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `tools/` or `pm-tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added SQL schema and upsert/link commands for decision_log and decision_dependency in realm DBs. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workflow and manifest wiring in progress to make decision state a first-class execution driver. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Pending initial population of decision records for renderer and boilerplate promotion actions. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added project-state knowledge tables and commands for entries/evidence/decision links. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added knowledgeBaseReport task and workflow wiring; now needs broader seeding coverage. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added intent-style report command, screen payload format, DB allowlist auth, and granular refresh options. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Added reasoning sync pipeline, dual reasoning DBs, and reasoning-drive report with workflow integration. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Workspace reorganized to canonical realm layout with compatibility handling.</t>
-  </si>
-  <si>
-    <t>Realm naming and path references updated for policy/management/product semantics.</t>
-  </si>
-  <si>
-    <t>Quality gate validation completed after migration fixes for artifact indexing, tooling guards, tests, and fidelity gate pathing.</t>
-  </si>
-  <si>
-    <t>2026-02-23T20:57:10Z</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Scope: finalize pzAiCore identity convergence, complete canonical core-&gt;project-&gt;product hierarchy/file-structure migration, and publish topology-drift baseline evidence.</t>
-  </si>
-  <si>
-    <t>Scope: replace critical hardcoded DB/path arguments with resolver-backed sources, enforce realm segmentation, implement owner-negotiation gate, and standardize deterministic default outputs.</t>
-  </si>
-  <si>
-    <t>Scope: promote report checks to strict gates (hardcoded critical paths, cross-realm writes, topology drift), execute full validation cycle, publish evidence pack, and close with handoff/backlog.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:05:19Z</t>
-  </si>
-  <si>
-    <t>Project-state SQLite now captures Git head/branch/dirty summary and per-path file discipline inventory; build publishes management/pm/reports/version-control-ledger.json for auditable governance workflows.</t>
-  </si>
-  <si>
-    <t>Added constitutional managed-tooling rule and `enforceManagedTooling` gate; untracked workflow tooling under `management/tools/` or `management/pm-management/tools/.../tools` now fails quality verification.</t>
-  </si>
-  <si>
-    <t>Added export command and Gradle decisionPriorityReport task for management/pm/reports/decision-priority-queue.json. Closed in single-pass closeout after full qualityGate/documentationManifest validation and cross-realm sync.</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json).</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts.</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:47:26Z</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scoped and activated as immediate execution driver after qualityGate failure in mixed-index branch state.</t>
-  </si>
-  <si>
-    <t>Target artifacts include .gradle/.idea metadata, sqlite wal/shm sidecars, .DS_Store, and transient authenticity staging files.</t>
-  </si>
-  <si>
-    <t>Reduce blast radius and make enforcement outcomes auditable per realm.</t>
-  </si>
-  <si>
-    <t>Align planning trackers with PM action-items and decision-priority queue current state.</t>
-  </si>
-  <si>
-    <t>Exit step for workstream closure once deterministic pass conditions are proven.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:49:59Z</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation.</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked.</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Stabilization guardrails are in place; next step is physically slicing the migration into auditable realm-specific change sets.</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Plan/progress next-step artifacts now point to WS-J; follow-up needed to align/refresh SQL action and decision records for WS-J scope.</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts.</t>
-  </si>
-  <si>
-    <t>2026-02-23T21:59:35Z</t>
-  </si>
-  <si>
-    <t>Published realm-slice evidence artifact (`management/pm/reports/workstream-j-slice-evidence.json`) with scope counts and next slice staging actions; physical commit slicing still pending.</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:25:04Z</t>
-  </si>
-  <si>
-    <t>Completed pzAiCore identity convergence and canonical hierarchy alignment with topology drift report baseline (management/pm/reports/topology-structure-drift.json). [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Completed managed tool inventory and critical path contract refactor with resolver-backed DB paths and governance tooling artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Enabled strict topology and hardcoded critical-path gates and validated full qualityGate pass with evidence pack outputs. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Updated `enforceBoilerplateRollupForFrameworkChanges` to union staged+unstaged+untracked paths and de-duplicate before trigger evaluation. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added scoped .gitignore for local IDE/cache artifacts, SQLite WAL/SHM sidecars, .DS_Store, and transient authenticity staging files; governed artifacts remain tracked. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Added WS-J decision/action records via StateDatabaseTool and confirmed visibility in `action-items.json` and `decision-priority-queue.json` after PM refresh. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>Ran `qualityGate` successfully and executed `pmWorkflowRun -PpmPhase=pm_refresh_and_reports` to refresh evidence artifacts. [github:not-committed]</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:26:23Z</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Automated slice manifests and git add pathspec commands now generated under `management/pm/reports/slice-manifests/`; remaining step is performing and validating actual per-slice commits.</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:33:37Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T22:39:03Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:01:31Z</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>New active internal workstream formalized with unique UID; presentation alias should appear as Workstream A.</t>
-  </si>
-  <si>
-    <t>Pending implementation after scope graph baseline.</t>
-  </si>
-  <si>
-    <t>Planned closeout task for first continuation slice.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:07:45Z</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Activated next slice after scope graph baseline completion; implementing targeted ordering assertions.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:13:28Z</t>
-  </si>
-  <si>
-    <t>Active closeout task: publish continuation diagnostics and updated next-step deltas after slice-2 commit.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:22:39Z</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:29:45Z</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Slice 1 implementation underway to enrich scope-graph diagnostics for faster render-scope triage.</t>
-  </si>
-  <si>
-    <t>2026-02-23T23:30:47Z</t>
+    <t>2026-02-24T16:24:26Z</t>
+  </si>
+  <si>
+    <t>2026-02-24T16:25:17Z</t>
   </si>
   <si>
     <t>iteration</t>
@@ -938,6 +953,12 @@
     <t>-@</t>
   </si>
   <si>
+    <t>35,100,100</t>
+  </si>
+  <si>
+    <t>-@@</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -1103,7 +1124,7 @@
     <t xml:space="preserve"> -@@@</t>
   </si>
   <si>
-    <t xml:space="preserve">     </t>
+    <t xml:space="preserve"> @@@@</t>
   </si>
   <si>
     <t>-@@@@</t>
@@ -1113,9 +1134,6 @@
   </si>
   <si>
     <t>+@@@@</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> @@@@</t>
   </si>
 </sst>
 </file>
@@ -2324,16 +2342,16 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
@@ -2341,22 +2359,22 @@
         <v>122</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2367,12 +2385,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2381,25 +2399,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="G1" t="s" s="0">
         <v>133</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>136</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>138</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2407,7 +2425,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2416,19 +2434,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2437,12 +2455,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2451,19 +2469,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2472,12 +2490,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2486,19 +2504,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2507,12 +2525,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2521,19 +2539,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2542,12 +2560,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2556,19 +2574,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2577,12 +2595,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2591,19 +2609,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2612,12 +2630,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2626,19 +2644,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2647,12 +2665,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2661,19 +2679,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2682,12 +2700,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2696,19 +2714,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2717,12 +2735,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2731,19 +2749,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2752,12 +2770,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2766,19 +2784,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2787,12 +2805,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2801,19 +2819,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2822,12 +2840,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2836,19 +2854,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2857,12 +2875,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2871,19 +2889,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2892,12 +2910,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2906,19 +2924,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2927,12 +2945,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2941,19 +2959,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2962,12 +2980,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2976,19 +2994,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -2997,12 +3015,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -3011,19 +3029,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -3032,12 +3050,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -3046,19 +3064,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -3067,12 +3085,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -3081,19 +3099,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -3102,12 +3120,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -3116,19 +3134,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -3137,12 +3155,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3151,19 +3169,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3172,12 +3190,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3186,19 +3204,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3207,12 +3225,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3221,19 +3239,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3242,12 +3260,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3256,19 +3274,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3277,12 +3295,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3291,19 +3309,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3312,12 +3330,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3326,19 +3344,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3347,12 +3365,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3361,19 +3379,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3382,12 +3400,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3396,19 +3414,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3417,12 +3435,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3431,19 +3449,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3452,12 +3470,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3466,19 +3484,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3487,12 +3505,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3501,19 +3519,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3522,12 +3540,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3536,19 +3554,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3557,12 +3575,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3571,19 +3589,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3592,12 +3610,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3606,19 +3624,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3627,12 +3645,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3641,19 +3659,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3662,12 +3680,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3676,19 +3694,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3697,12 +3715,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3711,33 +3729,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3746,22 +3764,22 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
@@ -3772,7 +3790,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3781,22 +3799,22 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
@@ -3921,7 +3939,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3933,7 +3951,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3956,7 +3974,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3968,7 +3986,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3991,7 +4009,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -4003,7 +4021,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -4026,19 +4044,19 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I48" t="s" s="0">
         <v>192</v>
@@ -4061,22 +4079,22 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
@@ -4096,22 +4114,22 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
@@ -4131,22 +4149,22 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
@@ -4166,22 +4184,22 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
@@ -4201,7 +4219,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4236,7 +4254,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4248,7 +4266,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4271,10 +4289,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4283,7 +4301,7 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I55" t="s" s="0">
         <v>201</v>
@@ -4306,10 +4324,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4318,7 +4336,7 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I56" t="s" s="0">
         <v>203</v>
@@ -4341,7 +4359,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4353,7 +4371,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4376,10 +4394,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4391,7 +4409,7 @@
         <v>201</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
@@ -4411,7 +4429,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -5986,10 +6004,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -5998,7 +6016,7 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I104" t="s" s="0">
         <v>218</v>
@@ -6091,7 +6109,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6301,19 +6319,19 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I113" t="s" s="0">
         <v>223</v>
@@ -6336,22 +6354,22 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
@@ -6371,22 +6389,22 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
@@ -6406,7 +6424,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6441,10 +6459,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6453,7 +6471,7 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I117" t="s" s="0">
         <v>228</v>
@@ -6476,7 +6494,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6511,10 +6529,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6523,7 +6541,7 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I119" t="s" s="0">
         <v>201</v>
@@ -6546,7 +6564,7 @@
         <v>120</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>10</v>
@@ -6581,19 +6599,19 @@
         <v>123</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I121" t="s" s="0">
         <v>234</v>
@@ -6616,28 +6634,28 @@
         <v>125</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G122" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K122" t="s" s="0">
-        <v>128</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123">
@@ -6648,36 +6666,36 @@
         <v>122</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="J123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K123" t="s" s="0">
-        <v>130</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B124" t="s" s="0">
         <v>122</v>
@@ -6686,7 +6704,7 @@
         <v>123</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>10</v>
@@ -6707,6 +6725,111 @@
         <v>98</v>
       </c>
       <c r="K124" t="s" s="0">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H125" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="I125" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J125" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K125" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E126" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F126" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G126" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H126" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="I126" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J126" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K126" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H127" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I127" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J127" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="K127" t="s" s="0">
         <v>124</v>
       </c>
     </row>
@@ -6717,7 +6840,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6731,25 +6854,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -6763,7 +6886,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6772,13 +6895,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -6792,7 +6915,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6801,13 +6924,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -6821,7 +6944,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6830,13 +6953,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
@@ -6850,7 +6973,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6859,13 +6982,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -6879,7 +7002,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -6888,13 +7011,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
@@ -6908,7 +7031,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -6917,13 +7040,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -6937,7 +7060,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -6946,13 +7069,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -6966,7 +7089,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -6975,13 +7098,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -6995,7 +7118,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -7004,13 +7127,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -7024,7 +7147,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -7033,13 +7156,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
@@ -7053,7 +7176,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -7062,13 +7185,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13">
@@ -7082,7 +7205,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -7091,13 +7214,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
@@ -7111,7 +7234,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -7120,13 +7243,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15">
@@ -7140,7 +7263,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -7149,13 +7272,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16">
@@ -7169,7 +7292,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -7178,13 +7301,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17">
@@ -7198,7 +7321,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -7207,13 +7330,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18">
@@ -7227,7 +7350,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -7236,13 +7359,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19">
@@ -7256,7 +7379,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -7265,13 +7388,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20">
@@ -7285,7 +7408,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -7294,13 +7417,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21">
@@ -7314,7 +7437,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -7323,13 +7446,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22">
@@ -7343,7 +7466,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -7352,13 +7475,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23">
@@ -7372,7 +7495,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -7381,13 +7504,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24">
@@ -7401,7 +7524,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7410,13 +7533,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25">
@@ -7430,7 +7553,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7439,13 +7562,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26">
@@ -7459,7 +7582,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7468,13 +7591,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27">
@@ -7488,7 +7611,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7497,13 +7620,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28">
@@ -7517,7 +7640,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7526,13 +7649,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29">
@@ -7546,7 +7669,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7555,13 +7678,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30">
@@ -7575,7 +7698,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7584,13 +7707,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31">
@@ -7604,7 +7727,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7613,13 +7736,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32">
@@ -7633,7 +7756,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7642,13 +7765,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33">
@@ -7662,7 +7785,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7671,13 +7794,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34">
@@ -7691,7 +7814,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7700,13 +7823,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35">
@@ -7720,7 +7843,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7729,13 +7852,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36">
@@ -7749,7 +7872,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7758,13 +7881,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37">
@@ -7778,7 +7901,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7787,13 +7910,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38">
@@ -7807,7 +7930,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7816,13 +7939,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39">
@@ -7836,22 +7959,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40">
@@ -7865,22 +7988,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41">
@@ -7894,22 +8017,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42">
@@ -7923,7 +8046,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -7932,13 +8055,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43">
@@ -7952,7 +8075,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -7961,13 +8084,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44">
@@ -7981,7 +8104,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -7990,13 +8113,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45">
@@ -8010,7 +8133,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -8019,13 +8142,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46">
@@ -8039,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -8051,10 +8174,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47">
@@ -8068,7 +8191,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -8080,10 +8203,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48">
@@ -8097,7 +8220,7 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
@@ -8106,13 +8229,13 @@
         <v>192</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H48" t="s" s="0">
         <v>192</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49">
@@ -8126,22 +8249,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50">
@@ -8155,22 +8278,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51">
@@ -8184,22 +8307,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52">
@@ -8213,22 +8336,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53">
@@ -8242,7 +8365,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -8251,13 +8374,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54">
@@ -8271,7 +8394,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -8283,10 +8406,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55">
@@ -8300,7 +8423,7 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
@@ -8312,10 +8435,10 @@
         <v>201</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56">
@@ -8329,7 +8452,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
@@ -8341,10 +8464,10 @@
         <v>203</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57">
@@ -8358,7 +8481,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -8370,10 +8493,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58">
@@ -8387,22 +8510,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59">
@@ -8416,7 +8539,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8425,13 +8548,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60">
@@ -8445,7 +8568,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8454,13 +8577,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="61">
@@ -8474,7 +8597,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8483,13 +8606,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62">
@@ -8503,7 +8626,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8512,13 +8635,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63">
@@ -8532,7 +8655,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8541,13 +8664,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64">
@@ -8561,7 +8684,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8570,13 +8693,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65">
@@ -8590,7 +8713,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8599,13 +8722,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66">
@@ -8619,7 +8742,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8628,13 +8751,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67">
@@ -8648,7 +8771,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8657,13 +8780,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68">
@@ -8677,7 +8800,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8686,13 +8809,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69">
@@ -8706,7 +8829,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8715,13 +8838,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70">
@@ -8735,7 +8858,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8744,13 +8867,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71">
@@ -8764,7 +8887,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8773,13 +8896,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72">
@@ -8793,7 +8916,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8802,13 +8925,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73">
@@ -8822,7 +8945,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8831,13 +8954,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74">
@@ -8851,7 +8974,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8860,13 +8983,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75">
@@ -8880,7 +9003,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -8889,13 +9012,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76">
@@ -8909,7 +9032,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -8918,13 +9041,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77">
@@ -8938,7 +9061,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -8947,13 +9070,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78">
@@ -8967,7 +9090,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -8976,13 +9099,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79">
@@ -8996,7 +9119,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -9005,13 +9128,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80">
@@ -9025,7 +9148,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -9034,13 +9157,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81">
@@ -9054,7 +9177,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -9063,13 +9186,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82">
@@ -9083,7 +9206,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -9092,13 +9215,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83">
@@ -9112,7 +9235,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -9121,13 +9244,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84">
@@ -9141,7 +9264,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -9150,13 +9273,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85">
@@ -9170,7 +9293,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -9179,13 +9302,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86">
@@ -9199,7 +9322,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -9208,13 +9331,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87">
@@ -9228,7 +9351,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -9237,13 +9360,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88">
@@ -9257,7 +9380,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -9266,13 +9389,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89">
@@ -9286,7 +9409,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -9295,13 +9418,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90">
@@ -9315,7 +9438,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -9324,13 +9447,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="91">
@@ -9344,7 +9467,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -9353,13 +9476,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92">
@@ -9373,7 +9496,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -9382,13 +9505,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93">
@@ -9402,7 +9525,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9411,13 +9534,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94">
@@ -9431,7 +9554,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9440,13 +9563,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95">
@@ -9460,7 +9583,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9469,13 +9592,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96">
@@ -9489,7 +9612,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9498,13 +9621,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97">
@@ -9518,7 +9641,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9527,13 +9650,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98">
@@ -9547,7 +9670,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9556,13 +9679,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="99">
@@ -9576,7 +9699,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9585,13 +9708,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100">
@@ -9605,7 +9728,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9614,13 +9737,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="101">
@@ -9634,7 +9757,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9643,13 +9766,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="102">
@@ -9663,7 +9786,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9672,13 +9795,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103">
@@ -9692,7 +9815,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9701,13 +9824,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104">
@@ -9721,7 +9844,7 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
@@ -9730,13 +9853,13 @@
         <v>218</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="105">
@@ -9750,7 +9873,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9759,13 +9882,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106">
@@ -9779,7 +9902,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9788,13 +9911,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107">
@@ -9808,7 +9931,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9820,10 +9943,10 @@
         <v>228</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108">
@@ -9837,7 +9960,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9846,13 +9969,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="109">
@@ -9866,7 +9989,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9875,13 +9998,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="110">
@@ -9895,7 +10018,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -9904,13 +10027,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="111">
@@ -9924,7 +10047,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -9933,13 +10056,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="112">
@@ -9953,7 +10076,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -9962,13 +10085,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113">
@@ -9982,7 +10105,7 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
@@ -9991,13 +10114,13 @@
         <v>223</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H113" t="s" s="0">
         <v>223</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="114">
@@ -10011,22 +10134,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115">
@@ -10040,22 +10163,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="116">
@@ -10069,7 +10192,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -10078,13 +10201,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="117">
@@ -10098,7 +10221,7 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
@@ -10110,10 +10233,10 @@
         <v>228</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="118">
@@ -10127,7 +10250,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -10139,10 +10262,10 @@
         <v>218</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="119">
@@ -10156,7 +10279,7 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
@@ -10168,10 +10291,10 @@
         <v>201</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120">
@@ -10185,7 +10308,7 @@
         <v>33</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>98</v>
@@ -10194,13 +10317,13 @@
         <v>11</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I120" t="s" s="0">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="121">
@@ -10214,7 +10337,7 @@
         <v>9</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E121" t="s" s="0">
         <v>98</v>
@@ -10223,13 +10346,13 @@
         <v>234</v>
       </c>
       <c r="G121" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H121" t="s" s="0">
         <v>234</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="122">
@@ -10243,22 +10366,22 @@
         <v>9</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="123">
@@ -10266,28 +10389,28 @@
         <v>122</v>
       </c>
       <c r="B123" t="s" s="0">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s" s="0">
         <v>33</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124">
@@ -10301,7 +10424,7 @@
         <v>9</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>98</v>
@@ -10310,13 +10433,100 @@
         <v>11</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="I124" t="s" s="0">
-        <v>305</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F125" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G125" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="H125" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="I125" t="s" s="0">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="E126" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F126" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G126" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="H126" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="I126" t="s" s="0">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F127" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G127" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="H127" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="I127" t="s" s="0">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -10331,183 +10541,183 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AX1" t="s" s="0">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AY1" t="s" s="0">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AZ1" t="s" s="0">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>223</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>234</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
@@ -10621,25 +10831,25 @@
         <v>11</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AW2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AX2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AY2" t="s" s="0">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="AZ2" t="s" s="0">
         <v>192</v>
@@ -10647,7 +10857,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>228</v>
@@ -10659,13 +10869,13 @@
         <v>201</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
@@ -10805,136 +11015,136 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="W4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AH4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AP4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AQ4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AR4" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AS4" t="s" s="0">
         <v>11</v>
@@ -10955,7 +11165,7 @@
         <v>11</v>
       </c>
       <c r="AY4" t="s" s="0">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AZ4" t="s" s="0">
         <v>11</v>
@@ -10963,136 +11173,136 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AS5" t="s" s="0">
         <v>11</v>
@@ -11121,151 +11331,151 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AX6" t="s" s="0">
         <v>11</v>
@@ -11274,7 +11484,7 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="s" s="0">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -11282,18 +11492,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -11301,10 +11511,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -11312,10 +11522,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -11323,21 +11533,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>127</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -11345,21 +11555,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>127</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -11367,10 +11577,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -11378,10 +11588,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -11389,10 +11599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -11400,10 +11610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -11411,10 +11621,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -11422,10 +11632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -11433,10 +11643,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -11444,10 +11654,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -11455,10 +11665,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -11466,10 +11676,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -11477,10 +11687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -11488,10 +11698,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -11499,10 +11709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -11510,10 +11720,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -11521,10 +11731,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -11532,10 +11742,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -11543,10 +11753,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -11554,10 +11764,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -11565,10 +11775,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -11576,10 +11786,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -11587,10 +11797,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -11598,10 +11808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -11609,10 +11819,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -11620,10 +11830,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -11631,10 +11841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -11642,10 +11852,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -11653,10 +11863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -11664,10 +11874,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -11675,10 +11885,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -11686,10 +11896,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -11697,10 +11907,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -11708,10 +11918,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -11719,10 +11929,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -11730,10 +11940,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -11741,10 +11951,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -11752,10 +11962,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -11763,10 +11973,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -11774,10 +11984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -11785,10 +11995,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -11796,10 +12006,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -11807,10 +12017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>
@@ -11818,10 +12028,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C58" t="s" s="0">
         <v>11</v>
@@ -11829,10 +12039,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C59" t="s" s="0">
         <v>11</v>
@@ -11840,10 +12050,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C60" t="s" s="0">
         <v>11</v>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Progress Graph" r:id="rId6" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3373" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="386">
   <si>
     <t>workstream</t>
   </si>
@@ -407,6 +407,30 @@
     <t>Published continuation diagnostics and refreshed next-step/report deltas after WS-2026-002 slice validations. [github:committed]</t>
   </si>
   <si>
+    <t>Realm Artifact Ringfencing 2026-02-24</t>
+  </si>
+  <si>
+    <t>Refactor CI artifact publishing to generate realm-ringfenced indices under parent management realm only</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>Replaced preview-copy CI artifact publishing with parent-level realm indices under `management/pm/reports/realm-artifacts/application|pm|boilerplate`. [github:committed]</t>
+  </si>
+  <si>
+    <t>Enforce PM/application boundary by blocking preview ci-artifacts leakage and removing legacy leaked bundle</t>
+  </si>
+  <si>
+    <t>Extended `enforcePmApplicationRealmSeparation` to fail on `product/afp-converter/preview/ci-artifacts` and removed legacy leaked preview bundle files. [github:committed]</t>
+  </si>
+  <si>
+    <t>Publish policy/doc updates and refreshed next-step guidance for post-ringfence continuation</t>
+  </si>
+  <si>
+    <t>Updated `AI-POLICY.md` and `README.md` artifact expectations and refreshed PM next-step guidance after ringfence validation. [github:committed]</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
@@ -746,6 +770,15 @@
     <t>2026-02-24T16:25:17Z</t>
   </si>
   <si>
+    <t>2026-02-24T16:41:11Z</t>
+  </si>
+  <si>
+    <t>Replaced preview-copy CI artifact publishing with parent-level realm indices under `management/pm/reports/realm-artifacts/{application</t>
+  </si>
+  <si>
+    <t>2026-02-24T16:43:25Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -959,6 +992,15 @@
     <t>-@@</t>
   </si>
   <si>
+    <t>Realm Artifact Ringfencing 2026-02-24 | Enforce PM/application boundary by blocking preview ci-artifacts leakage and removing legacy leaked bundle</t>
+  </si>
+  <si>
+    <t>Realm Artifact Ringfencing 2026-02-24 | Publish policy/doc updates and refreshed next-step guidance for post-ringfence continuation</t>
+  </si>
+  <si>
+    <t>Realm Artifact Ringfencing 2026-02-24 | Refactor CI artifact publishing to generate realm-ringfenced indices under parent management realm only</t>
+  </si>
+  <si>
     <t>Renderer Continuation 2026-02-23 | Add deterministic paint-order assertions for overlay/text/image interleave cases</t>
   </si>
   <si>
@@ -1115,6 +1157,9 @@
     <t>latest_percent</t>
   </si>
   <si>
+    <t>@@@@@</t>
+  </si>
+  <si>
     <t xml:space="preserve"> :@@@</t>
   </si>
   <si>
@@ -1128,9 +1173,6 @@
   </si>
   <si>
     <t>-@@@@</t>
-  </si>
-  <si>
-    <t>@@@@@</t>
   </si>
   <si>
     <t>+@@@@</t>
@@ -1178,7 +1220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2377,20 +2419,89 @@
         <v>128</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G52"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2399,25 +2510,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2425,7 +2536,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2434,19 +2545,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2455,12 +2566,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2469,19 +2580,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2490,12 +2601,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2504,19 +2615,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2525,12 +2636,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2539,19 +2650,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2560,12 +2671,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2574,19 +2685,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2595,12 +2706,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2609,19 +2720,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2630,12 +2741,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2644,19 +2755,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2665,12 +2776,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2679,19 +2790,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2700,12 +2811,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2714,19 +2825,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2735,12 +2846,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2749,19 +2860,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2770,12 +2881,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2784,19 +2895,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2805,12 +2916,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2819,19 +2930,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2840,12 +2951,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2854,19 +2965,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2875,12 +2986,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -2889,19 +3000,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -2910,12 +3021,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -2924,19 +3035,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -2945,12 +3056,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -2959,19 +3070,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -2980,12 +3091,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -2994,19 +3105,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -3015,12 +3126,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -3029,19 +3140,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -3050,12 +3161,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -3064,19 +3175,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -3085,12 +3196,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -3099,19 +3210,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -3120,12 +3231,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -3134,19 +3245,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -3155,12 +3266,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3169,19 +3280,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3190,12 +3301,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3204,19 +3315,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3225,12 +3336,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3239,19 +3350,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3260,12 +3371,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3274,19 +3385,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3295,12 +3406,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3309,19 +3420,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3330,12 +3441,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3344,19 +3455,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3365,12 +3476,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3379,19 +3490,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3400,12 +3511,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3414,19 +3525,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3435,12 +3546,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3449,19 +3560,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3470,12 +3581,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3484,19 +3595,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3505,12 +3616,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3519,19 +3630,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3540,12 +3651,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3554,19 +3665,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3575,12 +3686,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3589,19 +3700,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3610,12 +3721,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3624,19 +3735,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3645,12 +3756,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3659,19 +3770,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3680,12 +3791,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3694,19 +3805,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3715,12 +3826,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3729,33 +3840,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3764,33 +3875,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3799,33 +3910,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3855,12 +3966,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -3890,12 +4001,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -3925,12 +4036,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -3939,7 +4050,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -3951,7 +4062,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -3960,12 +4071,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -3974,7 +4085,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -3986,7 +4097,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -3995,12 +4106,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -4009,7 +4120,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -4021,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -4030,12 +4141,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -4044,33 +4155,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -4079,33 +4190,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -4114,33 +4225,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -4149,33 +4260,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -4184,33 +4295,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -4219,7 +4330,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4231,7 +4342,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -4240,12 +4351,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -4254,7 +4365,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4266,7 +4377,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4275,12 +4386,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -4289,10 +4400,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4301,21 +4412,21 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4324,10 +4435,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4336,21 +4447,21 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4359,7 +4470,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4371,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4380,12 +4491,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4394,10 +4505,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4406,21 +4517,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4429,7 +4540,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4441,7 +4552,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4450,12 +4561,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4490,7 +4601,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4525,7 +4636,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4560,7 +4671,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4595,7 +4706,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4630,7 +4741,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4665,7 +4776,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4700,7 +4811,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4735,7 +4846,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4770,7 +4881,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4805,7 +4916,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4840,7 +4951,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4875,7 +4986,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -4910,7 +5021,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -4945,7 +5056,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -4980,7 +5091,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -5015,7 +5126,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -5050,7 +5161,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -5085,7 +5196,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -5120,7 +5231,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -5155,7 +5266,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -5190,7 +5301,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -5225,7 +5336,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -5260,7 +5371,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -5295,7 +5406,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5330,7 +5441,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5365,7 +5476,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5400,7 +5511,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5435,7 +5546,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5470,7 +5581,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5505,7 +5616,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5540,7 +5651,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5575,7 +5686,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5610,7 +5721,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5645,7 +5756,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5680,7 +5791,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5715,7 +5826,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5750,7 +5861,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5780,12 +5891,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5815,12 +5926,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5850,12 +5961,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5885,12 +5996,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -5920,12 +6031,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -5955,12 +6066,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -5990,12 +6101,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -6004,10 +6115,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -6016,21 +6127,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -6065,7 +6176,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -6100,7 +6211,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -6109,7 +6220,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6121,7 +6232,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -6135,7 +6246,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -6170,7 +6281,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -6205,7 +6316,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -6240,7 +6351,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -6275,7 +6386,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -6310,7 +6421,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>115</v>
@@ -6319,33 +6430,33 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>115</v>
@@ -6354,33 +6465,33 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>115</v>
@@ -6389,33 +6500,33 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>115</v>
@@ -6424,7 +6535,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6436,7 +6547,7 @@
         <v>9</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I116" t="s" s="0">
         <v>11</v>
@@ -6450,7 +6561,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B117" t="s" s="0">
         <v>115</v>
@@ -6459,10 +6570,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6471,21 +6582,21 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="J117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K117" t="s" s="0">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>115</v>
@@ -6494,7 +6605,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6506,7 +6617,7 @@
         <v>9</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="I118" t="s" s="0">
         <v>11</v>
@@ -6520,7 +6631,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B119" t="s" s="0">
         <v>115</v>
@@ -6529,10 +6640,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6541,21 +6652,21 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>115</v>
@@ -6564,7 +6675,7 @@
         <v>120</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>10</v>
@@ -6576,7 +6687,7 @@
         <v>33</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="I120" t="s" s="0">
         <v>11</v>
@@ -6590,7 +6701,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B121" t="s" s="0">
         <v>122</v>
@@ -6599,33 +6710,33 @@
         <v>123</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K121" t="s" s="0">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B122" t="s" s="0">
         <v>122</v>
@@ -6634,33 +6745,33 @@
         <v>125</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G122" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K122" t="s" s="0">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B123" t="s" s="0">
         <v>122</v>
@@ -6669,33 +6780,33 @@
         <v>127</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="J123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K123" t="s" s="0">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B124" t="s" s="0">
         <v>122</v>
@@ -6704,7 +6815,7 @@
         <v>123</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>10</v>
@@ -6716,7 +6827,7 @@
         <v>9</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="I124" t="s" s="0">
         <v>11</v>
@@ -6725,12 +6836,12 @@
         <v>98</v>
       </c>
       <c r="K124" t="s" s="0">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B125" t="s" s="0">
         <v>122</v>
@@ -6739,7 +6850,7 @@
         <v>125</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>10</v>
@@ -6751,7 +6862,7 @@
         <v>9</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I125" t="s" s="0">
         <v>11</v>
@@ -6765,7 +6876,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B126" t="s" s="0">
         <v>122</v>
@@ -6774,7 +6885,7 @@
         <v>127</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>10</v>
@@ -6786,7 +6897,7 @@
         <v>33</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I126" t="s" s="0">
         <v>11</v>
@@ -6800,7 +6911,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B127" t="s" s="0">
         <v>122</v>
@@ -6831,6 +6942,146 @@
       </c>
       <c r="K127" t="s" s="0">
         <v>124</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F128" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="G128" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H128" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I128" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J128" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K128" t="s" s="0">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D129" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F129" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="G129" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H129" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I129" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J129" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K129" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="D130" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="E130" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F130" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="G130" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H130" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I130" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J130" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K130" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="D131" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E131" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F131" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G131" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H131" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I131" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J131" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K131" t="s" s="0">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -6840,7 +7091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6854,25 +7105,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
@@ -6886,7 +7137,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -6895,13 +7146,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
@@ -6915,7 +7166,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -6924,13 +7175,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -6944,7 +7195,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -6953,13 +7204,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -6973,7 +7224,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -6982,13 +7233,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
@@ -7002,7 +7253,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -7011,13 +7262,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
@@ -7031,7 +7282,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -7040,13 +7291,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -7060,7 +7311,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -7069,13 +7320,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +7340,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -7098,13 +7349,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -7118,7 +7369,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -7127,13 +7378,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -7147,7 +7398,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -7156,13 +7407,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -7176,7 +7427,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -7185,13 +7436,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13">
@@ -7205,7 +7456,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -7214,13 +7465,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
@@ -7234,7 +7485,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -7243,13 +7494,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +7514,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -7272,13 +7523,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16">
@@ -7292,7 +7543,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -7301,13 +7552,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
@@ -7321,7 +7572,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -7330,13 +7581,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18">
@@ -7350,7 +7601,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -7359,13 +7610,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19">
@@ -7379,7 +7630,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -7388,13 +7639,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20">
@@ -7408,7 +7659,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -7417,13 +7668,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21">
@@ -7437,7 +7688,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -7446,13 +7697,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22">
@@ -7466,7 +7717,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -7475,13 +7726,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23">
@@ -7495,7 +7746,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -7504,13 +7755,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24">
@@ -7524,7 +7775,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7533,13 +7784,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25">
@@ -7553,7 +7804,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7562,13 +7813,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26">
@@ -7582,7 +7833,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7591,13 +7842,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27">
@@ -7611,7 +7862,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7620,13 +7871,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28">
@@ -7640,7 +7891,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7649,13 +7900,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29">
@@ -7669,7 +7920,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7678,13 +7929,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30">
@@ -7698,7 +7949,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7707,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31">
@@ -7727,7 +7978,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7736,13 +7987,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32">
@@ -7756,7 +8007,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -7765,13 +8016,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33">
@@ -7785,7 +8036,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -7794,13 +8045,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34">
@@ -7814,7 +8065,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -7823,13 +8074,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35">
@@ -7843,7 +8094,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -7852,13 +8103,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36">
@@ -7872,7 +8123,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -7881,13 +8132,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37">
@@ -7901,7 +8152,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -7910,13 +8161,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38">
@@ -7930,7 +8181,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -7939,13 +8190,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39">
@@ -7959,22 +8210,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40">
@@ -7988,22 +8239,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41">
@@ -8017,22 +8268,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42">
@@ -8046,7 +8297,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -8055,13 +8306,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43">
@@ -8075,7 +8326,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -8084,13 +8335,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44">
@@ -8104,7 +8355,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -8113,13 +8364,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45">
@@ -8133,7 +8384,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -8142,13 +8393,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46">
@@ -8162,7 +8413,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -8174,10 +8425,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47">
@@ -8191,7 +8442,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -8203,10 +8454,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48">
@@ -8220,22 +8471,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49">
@@ -8249,22 +8500,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50">
@@ -8278,22 +8529,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51">
@@ -8307,22 +8558,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52">
@@ -8336,22 +8587,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53">
@@ -8365,7 +8616,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -8374,13 +8625,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54">
@@ -8394,7 +8645,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -8406,10 +8657,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55">
@@ -8423,22 +8674,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56">
@@ -8452,22 +8703,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57">
@@ -8481,7 +8732,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -8493,10 +8744,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58">
@@ -8510,22 +8761,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59">
@@ -8539,7 +8790,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8548,13 +8799,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60">
@@ -8568,7 +8819,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8577,13 +8828,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61">
@@ -8597,7 +8848,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8606,13 +8857,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62">
@@ -8626,7 +8877,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8635,13 +8886,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63">
@@ -8655,7 +8906,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8664,13 +8915,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64">
@@ -8684,7 +8935,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8693,13 +8944,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65">
@@ -8713,7 +8964,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8722,13 +8973,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66">
@@ -8742,7 +8993,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -8751,13 +9002,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67">
@@ -8771,7 +9022,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -8780,13 +9031,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68">
@@ -8800,7 +9051,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -8809,13 +9060,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="69">
@@ -8829,7 +9080,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -8838,13 +9089,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70">
@@ -8858,7 +9109,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -8867,13 +9118,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71">
@@ -8887,7 +9138,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -8896,13 +9147,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72">
@@ -8916,7 +9167,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -8925,13 +9176,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73">
@@ -8945,7 +9196,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -8954,13 +9205,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74">
@@ -8974,7 +9225,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -8983,13 +9234,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75">
@@ -9003,7 +9254,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -9012,13 +9263,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76">
@@ -9032,7 +9283,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -9041,13 +9292,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="77">
@@ -9061,7 +9312,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -9070,13 +9321,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78">
@@ -9090,7 +9341,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -9099,13 +9350,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79">
@@ -9119,7 +9370,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -9128,13 +9379,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="80">
@@ -9148,7 +9399,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -9157,13 +9408,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81">
@@ -9177,7 +9428,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -9186,13 +9437,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82">
@@ -9206,7 +9457,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -9215,13 +9466,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83">
@@ -9235,7 +9486,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -9244,13 +9495,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84">
@@ -9264,7 +9515,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -9273,13 +9524,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="85">
@@ -9293,7 +9544,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -9302,13 +9553,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86">
@@ -9322,7 +9573,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -9331,13 +9582,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -9351,7 +9602,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -9360,13 +9611,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88">
@@ -9380,7 +9631,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -9389,13 +9640,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89">
@@ -9409,7 +9660,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -9418,13 +9669,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -9438,7 +9689,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -9447,13 +9698,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="91">
@@ -9467,7 +9718,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -9476,13 +9727,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92">
@@ -9496,7 +9747,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -9505,13 +9756,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93">
@@ -9525,7 +9776,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9534,13 +9785,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94">
@@ -9554,7 +9805,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9563,13 +9814,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95">
@@ -9583,7 +9834,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9592,13 +9843,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96">
@@ -9612,7 +9863,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9621,13 +9872,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="97">
@@ -9641,7 +9892,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9650,13 +9901,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98">
@@ -9670,7 +9921,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9679,13 +9930,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99">
@@ -9699,7 +9950,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9708,13 +9959,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="100">
@@ -9728,7 +9979,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9737,13 +9988,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="101">
@@ -9757,7 +10008,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -9766,13 +10017,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102">
@@ -9786,7 +10037,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -9795,13 +10046,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103">
@@ -9815,7 +10066,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -9824,13 +10075,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="104">
@@ -9844,22 +10095,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="105">
@@ -9873,7 +10124,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -9882,13 +10133,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106">
@@ -9902,7 +10153,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -9911,13 +10162,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107">
@@ -9931,7 +10182,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -9940,13 +10191,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108">
@@ -9960,7 +10211,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -9969,13 +10220,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="109">
@@ -9989,7 +10240,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -9998,13 +10249,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="110">
@@ -10018,7 +10269,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -10027,13 +10278,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="111">
@@ -10047,7 +10298,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -10056,13 +10307,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="112">
@@ -10076,7 +10327,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -10085,13 +10336,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="113">
@@ -10105,22 +10356,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114">
@@ -10134,22 +10385,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115">
@@ -10163,22 +10414,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116">
@@ -10192,7 +10443,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -10201,13 +10452,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117">
@@ -10221,22 +10472,22 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G117" t="s" s="0">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118">
@@ -10250,7 +10501,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -10259,13 +10510,13 @@
         <v>11</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="119">
@@ -10279,22 +10530,22 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120">
@@ -10308,7 +10559,7 @@
         <v>33</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>98</v>
@@ -10317,13 +10568,13 @@
         <v>11</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="I120" t="s" s="0">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="121">
@@ -10337,22 +10588,22 @@
         <v>9</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G121" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="122">
@@ -10366,22 +10617,22 @@
         <v>9</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123">
@@ -10395,22 +10646,22 @@
         <v>33</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124">
@@ -10424,7 +10675,7 @@
         <v>9</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>98</v>
@@ -10433,13 +10684,13 @@
         <v>11</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="I124" t="s" s="0">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125">
@@ -10453,7 +10704,7 @@
         <v>9</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>98</v>
@@ -10465,10 +10716,10 @@
         <v>11</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I125" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126">
@@ -10482,7 +10733,7 @@
         <v>33</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>98</v>
@@ -10494,10 +10745,10 @@
         <v>11</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="I126" t="s" s="0">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127">
@@ -10511,7 +10762,7 @@
         <v>9</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>98</v>
@@ -10520,13 +10771,129 @@
         <v>11</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="I127" t="s" s="0">
-        <v>312</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F128" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G128" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="H128" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I128" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D129" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F129" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G129" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="H129" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I129" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D130" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="E130" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F130" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G130" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="H130" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I130" t="s" s="0">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D131" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="E131" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F131" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G131" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="H131" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="I131" t="s" s="0">
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -10536,197 +10903,206 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:BC63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AX1" t="s" s="0">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AY1" t="s" s="0">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="AZ1" t="s" s="0">
-        <v>363</v>
+        <v>374</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>11</v>
+        <v>189</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>11</v>
+        <v>242</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>11</v>
+        <v>189</v>
       </c>
       <c r="K2" t="s" s="0">
         <v>11</v>
@@ -10831,51 +11207,60 @@
         <v>11</v>
       </c>
       <c r="AS2" t="s" s="0">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AW2" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AX2" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AY2" t="s" s="0">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AZ2" t="s" s="0">
-        <v>192</v>
+        <v>189</v>
+      </c>
+      <c r="BA2" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="BB2" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="BC2" t="s" s="0">
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>201</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>11</v>
+        <v>209</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
@@ -11004,156 +11389,165 @@
         <v>11</v>
       </c>
       <c r="AX3" t="s" s="0">
-        <v>203</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="s" s="0">
-        <v>201</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BA3" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="BB3" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="BC3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AP4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AQ4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AR4" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AS4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AT4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AV4" t="s" s="0">
         <v>11</v>
@@ -11165,153 +11559,162 @@
         <v>11</v>
       </c>
       <c r="AY4" t="s" s="0">
-        <v>178</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BA4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="BC4" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AT5" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AV5" t="s" s="0">
         <v>11</v>
@@ -11323,168 +11726,186 @@
         <v>11</v>
       </c>
       <c r="AY5" t="s" s="0">
-        <v>218</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BA5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BB5" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="BC5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AX6" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AY6" t="s" s="0">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="AZ6" t="s" s="0">
-        <v>138</v>
+        <v>146</v>
+      </c>
+      <c r="BA6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BB6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="s" s="0">
+        <v>146</v>
       </c>
     </row>
     <row r="9">
@@ -11492,18 +11913,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -11511,10 +11932,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -11522,10 +11943,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -11533,10 +11954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -11544,10 +11965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -11555,10 +11976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -11566,10 +11987,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -11577,10 +11998,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -11588,10 +12009,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -11599,10 +12020,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -11610,10 +12031,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -11621,10 +12042,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -11632,10 +12053,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -11643,10 +12064,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -11654,10 +12075,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -11665,10 +12086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -11676,10 +12097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -11687,10 +12108,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -11698,10 +12119,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -11709,10 +12130,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -11720,10 +12141,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -11731,10 +12152,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -11742,10 +12163,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -11753,10 +12174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -11764,10 +12185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -11775,10 +12196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -11786,10 +12207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -11797,10 +12218,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -11808,10 +12229,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -11819,10 +12240,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -11830,10 +12251,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -11841,10 +12262,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -11852,10 +12273,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -11863,10 +12284,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -11874,10 +12295,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -11885,10 +12306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -11896,10 +12317,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -11907,10 +12328,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -11918,10 +12339,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -11929,10 +12350,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -11940,10 +12361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -11951,10 +12372,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -11962,10 +12383,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -11973,10 +12394,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -11984,10 +12405,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -11995,10 +12416,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -12006,10 +12427,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -12017,10 +12438,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>
@@ -12028,10 +12449,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="C58" t="s" s="0">
         <v>11</v>
@@ -12039,10 +12460,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>293</v>
+        <v>383</v>
       </c>
       <c r="C59" t="s" s="0">
         <v>11</v>
@@ -12050,12 +12471,45 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="C60" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="C63" t="s" s="0">
         <v>11</v>
       </c>
     </row>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Progress Graph" r:id="rId6" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3501" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3689" uniqueCount="403">
   <si>
     <t>workstream</t>
   </si>
@@ -431,6 +431,27 @@
     <t>Updated `AI-POLICY.md` and `README.md` artifact expectations and refreshed PM next-step guidance after ringfence validation. [github:committed]</t>
   </si>
   <si>
+    <t>Sample Baseline Protection 2026-02-24</t>
+  </si>
+  <si>
+    <t>Restore protected sampleOutput baseline artifacts and remove generated overwrite residue</t>
+  </si>
+  <si>
+    <t>Restored `sampleOutput` baseline files from pre-overwrite commit and removed generated sampleOutput overwrite residue to recover IBM comparison references. [github:committed]</t>
+  </si>
+  <si>
+    <t>Redirect build-time multi-sample generation to preview-only path and keep sampleOutput read-only</t>
+  </si>
+  <si>
+    <t>Updated `:afp-cli:generateSampleOutputs` to emit to `product/afp-converter/preview/generated-sample-output/` while preserving `product/afp-converter/sampleOutput/` for baseline comparison assets. [github:committed]</t>
+  </si>
+  <si>
+    <t>Add enforceable process guardrails for sample baseline integrity and publish policy/docs/process deltas</t>
+  </si>
+  <si>
+    <t>Added protected sample-output reference manifest plus `enforceSampleOutputReferenceIntegrity` in `qualityGate` and updated policy/docs/boilerplate rollup for the corrected process. [github:committed]</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
@@ -779,6 +800,27 @@
     <t>2026-02-24T16:43:25Z</t>
   </si>
   <si>
+    <t>2026-02-24T17:01:36Z</t>
+  </si>
+  <si>
+    <t>Restored `sampleOutput` baseline files from pre-overwrite commit and removed generated sampleOutput overwrite residue to recover IBM comparison references. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Updated `:afp-cli:generateSampleOutputs` to emit to `product/afp-converter/preview/generated-sample-output/` while preserving `product/afp-converter/sampleOutput/` for baseline comparison assets. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Added protected sample-output reference manifest plus `enforceSampleOutputReferenceIntegrity` in `qualityGate`</t>
+  </si>
+  <si>
+    <t>2026-02-24T17:02:27Z</t>
+  </si>
+  <si>
+    <t>Added protected sample-output reference manifest plus `enforceSampleOutputReferenceIntegrity` in `qualityGate` and updated policy/docs/boilerplate rollup for the corrected process. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>2026-02-24T17:03:45Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -1017,6 +1059,15 @@
   </si>
   <si>
     <t>Renderer Continuation 2026-02-23-B | Publish continuation diagnostics and next-step delta after slice validations</t>
+  </si>
+  <si>
+    <t>Sample Baseline Protection 2026-02-24 | Add enforceable process guardrails for sample baseline integrity and publish policy/docs/process deltas</t>
+  </si>
+  <si>
+    <t>Sample Baseline Protection 2026-02-24 | Redirect build-time multi-sample generation to preview-only path and keep sampleOutput read-only</t>
+  </si>
+  <si>
+    <t>Sample Baseline Protection 2026-02-24 | Restore protected sampleOutput baseline artifacts and remove generated overwrite residue</t>
   </si>
   <si>
     <t>Workstream A | complete graphics object rendering beyond placeholders (rules, boxes, strokes/fills)</t>
@@ -1220,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2488,20 +2539,89 @@
         <v>136</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F56" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G56" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F57" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G57" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F58" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G58" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G58"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2510,25 +2630,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2536,7 +2656,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2545,19 +2665,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2566,12 +2686,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2580,19 +2700,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2601,12 +2721,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2615,19 +2735,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2636,12 +2756,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2650,19 +2770,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2671,12 +2791,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2685,19 +2805,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2706,12 +2826,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2720,19 +2840,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2741,12 +2861,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2755,19 +2875,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2776,12 +2896,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2790,19 +2910,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2811,12 +2931,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2825,19 +2945,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2846,12 +2966,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2860,19 +2980,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -2881,12 +3001,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -2895,19 +3015,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -2916,12 +3036,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -2930,19 +3050,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -2951,12 +3071,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -2965,19 +3085,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -2986,12 +3106,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -3000,19 +3120,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -3021,12 +3141,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -3035,19 +3155,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -3056,12 +3176,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -3070,19 +3190,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -3091,12 +3211,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -3105,19 +3225,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -3126,12 +3246,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -3140,19 +3260,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -3161,12 +3281,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -3175,19 +3295,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -3196,12 +3316,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -3210,19 +3330,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -3231,12 +3351,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -3245,19 +3365,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -3266,12 +3386,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3280,19 +3400,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3301,12 +3421,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3315,19 +3435,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3336,12 +3456,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3350,19 +3470,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3371,12 +3491,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3385,19 +3505,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3406,12 +3526,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3420,19 +3540,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3441,12 +3561,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3455,19 +3575,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3476,12 +3596,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3490,19 +3610,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3511,12 +3631,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3525,19 +3645,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3546,12 +3666,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3560,19 +3680,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3581,12 +3701,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3595,19 +3715,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3616,12 +3736,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3630,19 +3750,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3651,12 +3771,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3665,19 +3785,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3686,12 +3806,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3700,19 +3820,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3721,12 +3841,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3735,19 +3855,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3756,12 +3876,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3770,19 +3890,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3791,12 +3911,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3805,19 +3925,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3826,12 +3946,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3840,33 +3960,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3875,33 +3995,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -3910,33 +4030,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -3966,12 +4086,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -4001,12 +4121,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -4036,12 +4156,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -4050,7 +4170,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -4062,7 +4182,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -4071,12 +4191,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -4085,7 +4205,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -4097,7 +4217,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -4106,12 +4226,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -4120,7 +4240,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -4132,7 +4252,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -4141,12 +4261,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -4155,33 +4275,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -4190,33 +4310,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -4225,33 +4345,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -4260,33 +4380,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -4295,33 +4415,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -4330,7 +4450,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4342,7 +4462,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -4351,12 +4471,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -4365,7 +4485,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4377,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4386,12 +4506,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -4400,10 +4520,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4412,21 +4532,21 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4435,10 +4555,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4447,21 +4567,21 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4470,7 +4590,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4482,7 +4602,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4491,12 +4611,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4505,10 +4625,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4517,21 +4637,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4540,7 +4660,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4552,7 +4672,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4561,12 +4681,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4601,7 +4721,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4636,7 +4756,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4671,7 +4791,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4706,7 +4826,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4741,7 +4861,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4776,7 +4896,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4811,7 +4931,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4846,7 +4966,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -4881,7 +5001,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -4916,7 +5036,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -4951,7 +5071,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -4986,7 +5106,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -5021,7 +5141,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -5056,7 +5176,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -5091,7 +5211,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -5126,7 +5246,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -5161,7 +5281,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -5196,7 +5316,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -5231,7 +5351,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -5266,7 +5386,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -5301,7 +5421,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -5336,7 +5456,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -5371,7 +5491,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -5406,7 +5526,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5441,7 +5561,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5476,7 +5596,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5511,7 +5631,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5546,7 +5666,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5581,7 +5701,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5616,7 +5736,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5651,7 +5771,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5686,7 +5806,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5721,7 +5841,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5756,7 +5876,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5791,7 +5911,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5826,7 +5946,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5861,7 +5981,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -5891,12 +6011,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -5926,12 +6046,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -5961,12 +6081,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -5996,12 +6116,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -6031,12 +6151,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -6066,12 +6186,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -6101,12 +6221,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -6115,10 +6235,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -6127,21 +6247,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -6176,7 +6296,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -6211,7 +6331,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -6220,7 +6340,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6232,7 +6352,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -6246,7 +6366,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -6281,7 +6401,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -6316,7 +6436,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -6351,7 +6471,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -6386,7 +6506,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -6421,7 +6541,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>115</v>
@@ -6430,33 +6550,33 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>115</v>
@@ -6465,33 +6585,33 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>115</v>
@@ -6500,33 +6620,33 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>115</v>
@@ -6535,7 +6655,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6547,7 +6667,7 @@
         <v>9</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I116" t="s" s="0">
         <v>11</v>
@@ -6561,7 +6681,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B117" t="s" s="0">
         <v>115</v>
@@ -6570,10 +6690,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6582,21 +6702,21 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="J117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K117" t="s" s="0">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>115</v>
@@ -6605,7 +6725,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6617,7 +6737,7 @@
         <v>9</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I118" t="s" s="0">
         <v>11</v>
@@ -6631,7 +6751,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B119" t="s" s="0">
         <v>115</v>
@@ -6640,10 +6760,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6652,21 +6772,21 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="J119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>115</v>
@@ -6675,7 +6795,7 @@
         <v>120</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>10</v>
@@ -6687,7 +6807,7 @@
         <v>33</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I120" t="s" s="0">
         <v>11</v>
@@ -6701,7 +6821,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B121" t="s" s="0">
         <v>122</v>
@@ -6710,33 +6830,33 @@
         <v>123</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="J121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K121" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B122" t="s" s="0">
         <v>122</v>
@@ -6745,33 +6865,33 @@
         <v>125</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G122" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K122" t="s" s="0">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B123" t="s" s="0">
         <v>122</v>
@@ -6780,33 +6900,33 @@
         <v>127</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K123" t="s" s="0">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B124" t="s" s="0">
         <v>122</v>
@@ -6815,7 +6935,7 @@
         <v>123</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>10</v>
@@ -6827,7 +6947,7 @@
         <v>9</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="I124" t="s" s="0">
         <v>11</v>
@@ -6836,12 +6956,12 @@
         <v>98</v>
       </c>
       <c r="K124" t="s" s="0">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B125" t="s" s="0">
         <v>122</v>
@@ -6850,7 +6970,7 @@
         <v>125</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>10</v>
@@ -6862,7 +6982,7 @@
         <v>9</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I125" t="s" s="0">
         <v>11</v>
@@ -6876,7 +6996,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B126" t="s" s="0">
         <v>122</v>
@@ -6885,7 +7005,7 @@
         <v>127</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>10</v>
@@ -6897,7 +7017,7 @@
         <v>33</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I126" t="s" s="0">
         <v>11</v>
@@ -6911,7 +7031,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B127" t="s" s="0">
         <v>122</v>
@@ -6946,7 +7066,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B128" t="s" s="0">
         <v>129</v>
@@ -6955,19 +7075,19 @@
         <v>130</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E128" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G128" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H128" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I128" t="s" s="0">
         <v>11</v>
@@ -6976,12 +7096,12 @@
         <v>131</v>
       </c>
       <c r="K128" t="s" s="0">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B129" t="s" s="0">
         <v>129</v>
@@ -6990,19 +7110,19 @@
         <v>133</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G129" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H129" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I129" t="s" s="0">
         <v>11</v>
@@ -7016,7 +7136,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B130" t="s" s="0">
         <v>129</v>
@@ -7025,19 +7145,19 @@
         <v>135</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G130" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H130" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I130" t="s" s="0">
         <v>11</v>
@@ -7051,7 +7171,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s" s="0">
         <v>129</v>
@@ -7082,6 +7202,251 @@
       </c>
       <c r="K131" t="s" s="0">
         <v>132</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="D132" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="E132" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F132" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G132" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H132" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="I132" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J132" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K132" t="s" s="0">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="D133" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F133" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G133" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H133" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="I133" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J133" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K133" t="s" s="0">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D134" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="E134" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F134" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="G134" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H134" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="I134" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J134" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K134" t="s" s="0">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F135" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G135" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H135" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I135" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J135" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K135" t="s" s="0">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="D136" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E136" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F136" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G136" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H136" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I136" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J136" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K136" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G137" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H137" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I137" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J137" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K137" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D138" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E138" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F138" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G138" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H138" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I138" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J138" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K138" t="s" s="0">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -7091,7 +7456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7105,25 +7470,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>257</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2">
@@ -7137,7 +7502,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -7146,13 +7511,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3">
@@ -7166,7 +7531,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -7175,13 +7540,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4">
@@ -7195,7 +7560,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -7204,13 +7569,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
@@ -7224,7 +7589,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -7233,13 +7598,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6">
@@ -7253,7 +7618,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -7262,13 +7627,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7">
@@ -7282,7 +7647,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -7291,13 +7656,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8">
@@ -7311,7 +7676,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -7320,13 +7685,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9">
@@ -7340,7 +7705,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -7349,13 +7714,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -7369,7 +7734,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -7378,13 +7743,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -7398,7 +7763,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -7407,13 +7772,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
@@ -7427,7 +7792,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -7436,13 +7801,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
@@ -7456,7 +7821,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -7465,13 +7830,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
@@ -7485,7 +7850,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -7494,13 +7859,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
@@ -7514,7 +7879,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -7523,13 +7888,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16">
@@ -7543,7 +7908,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -7552,13 +7917,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17">
@@ -7572,7 +7937,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -7581,13 +7946,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18">
@@ -7601,7 +7966,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -7610,13 +7975,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19">
@@ -7630,7 +7995,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -7639,13 +8004,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20">
@@ -7659,7 +8024,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -7668,13 +8033,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21">
@@ -7688,7 +8053,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -7697,13 +8062,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22">
@@ -7717,7 +8082,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -7726,13 +8091,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23">
@@ -7746,7 +8111,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -7755,13 +8120,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24">
@@ -7775,7 +8140,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -7784,13 +8149,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25">
@@ -7804,7 +8169,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -7813,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26">
@@ -7833,7 +8198,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -7842,13 +8207,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27">
@@ -7862,7 +8227,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -7871,13 +8236,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28">
@@ -7891,7 +8256,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -7900,13 +8265,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29">
@@ -7920,7 +8285,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -7929,13 +8294,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30">
@@ -7949,7 +8314,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -7958,13 +8323,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31">
@@ -7978,7 +8343,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -7987,13 +8352,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32">
@@ -8007,7 +8372,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -8016,13 +8381,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33">
@@ -8036,7 +8401,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -8045,13 +8410,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34">
@@ -8065,7 +8430,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -8074,13 +8439,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35">
@@ -8094,7 +8459,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -8103,13 +8468,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36">
@@ -8123,7 +8488,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -8132,13 +8497,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37">
@@ -8152,7 +8517,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -8161,13 +8526,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38">
@@ -8181,7 +8546,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -8190,13 +8555,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39">
@@ -8210,22 +8575,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40">
@@ -8239,22 +8604,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41">
@@ -8268,22 +8633,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42">
@@ -8297,7 +8662,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -8306,13 +8671,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43">
@@ -8326,7 +8691,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -8335,13 +8700,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44">
@@ -8355,7 +8720,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -8364,13 +8729,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45">
@@ -8384,7 +8749,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -8393,13 +8758,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46">
@@ -8413,7 +8778,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -8425,10 +8790,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="47">
@@ -8442,7 +8807,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -8454,10 +8819,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48">
@@ -8471,22 +8836,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49">
@@ -8500,22 +8865,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50">
@@ -8529,22 +8894,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51">
@@ -8558,22 +8923,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52">
@@ -8587,22 +8952,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53">
@@ -8616,7 +8981,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -8625,13 +8990,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54">
@@ -8645,7 +9010,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -8657,10 +9022,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="55">
@@ -8674,22 +9039,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56">
@@ -8703,22 +9068,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>277</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57">
@@ -8732,7 +9097,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -8744,10 +9109,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58">
@@ -8761,22 +9126,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59">
@@ -8790,7 +9155,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -8799,13 +9164,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60">
@@ -8819,7 +9184,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -8828,13 +9193,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="61">
@@ -8848,7 +9213,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -8857,13 +9222,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62">
@@ -8877,7 +9242,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -8886,13 +9251,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63">
@@ -8906,7 +9271,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -8915,13 +9280,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="64">
@@ -8935,7 +9300,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -8944,13 +9309,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65">
@@ -8964,7 +9329,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -8973,13 +9338,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66">
@@ -8993,7 +9358,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -9002,13 +9367,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="67">
@@ -9022,7 +9387,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -9031,13 +9396,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="68">
@@ -9051,7 +9416,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -9060,13 +9425,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69">
@@ -9080,7 +9445,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -9089,13 +9454,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70">
@@ -9109,7 +9474,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -9118,13 +9483,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71">
@@ -9138,7 +9503,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -9147,13 +9512,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72">
@@ -9167,7 +9532,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -9176,13 +9541,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73">
@@ -9196,7 +9561,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -9205,13 +9570,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74">
@@ -9225,7 +9590,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -9234,13 +9599,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75">
@@ -9254,7 +9619,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -9263,13 +9628,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76">
@@ -9283,7 +9648,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -9292,13 +9657,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="77">
@@ -9312,7 +9677,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -9321,13 +9686,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78">
@@ -9341,7 +9706,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -9350,13 +9715,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79">
@@ -9370,7 +9735,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -9379,13 +9744,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80">
@@ -9399,7 +9764,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -9408,13 +9773,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81">
@@ -9428,7 +9793,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -9437,13 +9802,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82">
@@ -9457,7 +9822,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -9466,13 +9831,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83">
@@ -9486,7 +9851,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -9495,13 +9860,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84">
@@ -9515,7 +9880,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -9524,13 +9889,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="85">
@@ -9544,7 +9909,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -9553,13 +9918,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86">
@@ -9573,7 +9938,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -9582,13 +9947,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87">
@@ -9602,7 +9967,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -9611,13 +9976,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88">
@@ -9631,7 +9996,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -9640,13 +10005,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="89">
@@ -9660,7 +10025,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -9669,13 +10034,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="90">
@@ -9689,7 +10054,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -9698,13 +10063,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91">
@@ -9718,7 +10083,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -9727,13 +10092,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="92">
@@ -9747,7 +10112,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -9756,13 +10121,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93">
@@ -9776,7 +10141,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -9785,13 +10150,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94">
@@ -9805,7 +10170,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -9814,13 +10179,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95">
@@ -9834,7 +10199,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -9843,13 +10208,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="96">
@@ -9863,7 +10228,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -9872,13 +10237,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97">
@@ -9892,7 +10257,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -9901,13 +10266,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98">
@@ -9921,7 +10286,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -9930,13 +10295,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99">
@@ -9950,7 +10315,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -9959,13 +10324,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100">
@@ -9979,7 +10344,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -9988,13 +10353,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101">
@@ -10008,7 +10373,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -10017,13 +10382,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102">
@@ -10037,7 +10402,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -10046,13 +10411,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>295</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103">
@@ -10066,7 +10431,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -10075,13 +10440,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104">
@@ -10095,22 +10460,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>297</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105">
@@ -10124,7 +10489,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -10133,13 +10498,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>299</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106">
@@ -10153,7 +10518,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -10162,13 +10527,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107">
@@ -10182,7 +10547,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -10191,13 +10556,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>304</v>
+        <v>318</v>
       </c>
     </row>
     <row r="108">
@@ -10211,7 +10576,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -10220,13 +10585,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109">
@@ -10240,7 +10605,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -10249,13 +10614,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110">
@@ -10269,7 +10634,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -10278,13 +10643,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="111">
@@ -10298,7 +10663,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -10307,13 +10672,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112">
@@ -10327,7 +10692,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -10336,13 +10701,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>301</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113">
@@ -10356,22 +10721,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114">
@@ -10385,22 +10750,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115">
@@ -10414,22 +10779,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116">
@@ -10443,7 +10808,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -10452,13 +10817,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117">
@@ -10472,22 +10837,22 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="G117" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="118">
@@ -10501,7 +10866,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -10510,13 +10875,13 @@
         <v>11</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="119">
@@ -10530,22 +10895,22 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120">
@@ -10559,7 +10924,7 @@
         <v>33</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>98</v>
@@ -10568,13 +10933,13 @@
         <v>11</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="I120" t="s" s="0">
-        <v>317</v>
+        <v>331</v>
       </c>
     </row>
     <row r="121">
@@ -10588,22 +10953,22 @@
         <v>9</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G121" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="122">
@@ -10617,22 +10982,22 @@
         <v>9</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="123">
@@ -10646,22 +11011,22 @@
         <v>33</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="124">
@@ -10675,7 +11040,7 @@
         <v>9</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>98</v>
@@ -10684,13 +11049,13 @@
         <v>11</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I124" t="s" s="0">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="125">
@@ -10704,7 +11069,7 @@
         <v>9</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>98</v>
@@ -10716,10 +11081,10 @@
         <v>11</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I125" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="126">
@@ -10733,7 +11098,7 @@
         <v>33</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>98</v>
@@ -10745,10 +11110,10 @@
         <v>11</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="I126" t="s" s="0">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127">
@@ -10762,7 +11127,7 @@
         <v>9</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>98</v>
@@ -10771,13 +11136,13 @@
         <v>11</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="I127" t="s" s="0">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="128">
@@ -10791,7 +11156,7 @@
         <v>9</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E128" t="s" s="0">
         <v>131</v>
@@ -10800,13 +11165,13 @@
         <v>11</v>
       </c>
       <c r="G128" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H128" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129">
@@ -10820,7 +11185,7 @@
         <v>9</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>131</v>
@@ -10829,13 +11194,13 @@
         <v>11</v>
       </c>
       <c r="G129" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H129" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130">
@@ -10849,7 +11214,7 @@
         <v>33</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>131</v>
@@ -10858,13 +11223,13 @@
         <v>11</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H130" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I130" t="s" s="0">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131">
@@ -10878,7 +11243,7 @@
         <v>9</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E131" t="s" s="0">
         <v>131</v>
@@ -10887,13 +11252,216 @@
         <v>11</v>
       </c>
       <c r="G131" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H131" t="s" s="0">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>264</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D132" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="E132" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F132" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G132" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="H132" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I132" t="s" s="0">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D133" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F133" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G133" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="H133" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I133" t="s" s="0">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D134" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="E134" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F134" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G134" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="H134" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I134" t="s" s="0">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F135" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G135" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="H135" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="I135" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D136" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="E136" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F136" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G136" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="H136" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="I136" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F137" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G137" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="H137" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="I137" t="s" s="0">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D138" t="s" s="0">
+        <v>292</v>
+      </c>
+      <c r="E138" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F138" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G138" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="H138" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="I138" t="s" s="0">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -10903,179 +11471,188 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BC63"/>
+  <dimension ref="A1:BF66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="AX1" t="s" s="0">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="AY1" t="s" s="0">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="AZ1" t="s" s="0">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="BA1" t="s" s="0">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="BB1" t="s" s="0">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="BC1" t="s" s="0">
-        <v>377</v>
+        <v>391</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>11</v>
@@ -11087,22 +11664,22 @@
         <v>11</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K2" t="s" s="0">
         <v>11</v>
@@ -11216,51 +11793,60 @@
         <v>11</v>
       </c>
       <c r="AV2" t="s" s="0">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="s" s="0">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="s" s="0">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="s" s="0">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AZ2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="BA2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="BB2" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="BC2" t="s" s="0">
-        <v>200</v>
+        <v>196</v>
+      </c>
+      <c r="BD2" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="BE2" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="BF2" t="s" s="0">
+        <v>207</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
@@ -11398,165 +11984,174 @@
         <v>11</v>
       </c>
       <c r="BA3" t="s" s="0">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="s" s="0">
-        <v>209</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BD3" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="BE3" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="BF3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AP4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AQ4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AR4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AS4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AT4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AW4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AX4" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AY4" t="s" s="0">
         <v>11</v>
@@ -11568,162 +12163,171 @@
         <v>11</v>
       </c>
       <c r="BB4" t="s" s="0">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BD4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="s" s="0">
+        <v>193</v>
+      </c>
+      <c r="BF4" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AT5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AW5" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AX5" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AY5" t="s" s="0">
         <v>11</v>
@@ -11735,177 +12339,195 @@
         <v>11</v>
       </c>
       <c r="BB5" t="s" s="0">
-        <v>226</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BD5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BE5" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="BF5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AX6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AY6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AZ6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="BA6" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="BB6" t="s" s="0">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="BC6" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
+      </c>
+      <c r="BD6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BE6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BF6" t="s" s="0">
+        <v>153</v>
       </c>
     </row>
     <row r="9">
@@ -11913,18 +12535,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>378</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -11932,10 +12554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -11943,10 +12565,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -11954,10 +12576,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -11965,10 +12587,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -11976,10 +12598,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -11987,10 +12609,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -11998,10 +12620,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -12009,10 +12631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -12020,10 +12642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -12031,10 +12653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -12042,10 +12664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -12053,10 +12675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -12064,10 +12686,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -12075,10 +12697,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -12086,10 +12708,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -12097,10 +12719,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -12108,10 +12730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -12119,10 +12741,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -12130,10 +12752,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -12141,10 +12763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -12152,10 +12774,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -12163,10 +12785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -12174,10 +12796,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -12185,10 +12807,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -12196,10 +12818,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -12207,10 +12829,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -12218,10 +12840,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -12229,10 +12851,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -12240,10 +12862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -12251,10 +12873,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -12262,10 +12884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -12273,10 +12895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -12284,10 +12906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -12295,10 +12917,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -12306,10 +12928,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -12317,10 +12939,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -12328,10 +12950,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -12339,10 +12961,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -12350,10 +12972,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -12361,10 +12983,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -12372,10 +12994,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -12383,10 +13005,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -12394,10 +13016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -12405,10 +13027,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -12416,10 +13038,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -12427,10 +13049,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -12438,10 +13060,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>
@@ -12449,10 +13071,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C58" t="s" s="0">
         <v>11</v>
@@ -12460,10 +13082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C59" t="s" s="0">
         <v>11</v>
@@ -12471,10 +13093,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C60" t="s" s="0">
         <v>11</v>
@@ -12482,10 +13104,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="C61" t="s" s="0">
         <v>11</v>
@@ -12493,10 +13115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>304</v>
+        <v>400</v>
       </c>
       <c r="C62" t="s" s="0">
         <v>11</v>
@@ -12504,12 +13126,45 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C63" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>392</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>318</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>394</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>398</v>
+      </c>
+      <c r="C66" t="s" s="0">
         <v>11</v>
       </c>
     </row>

--- a/management/docs/project-plan-progress.xlsx
+++ b/management/docs/project-plan-progress.xlsx
@@ -12,13 +12,13 @@
     <sheet name="Progress Graph" r:id="rId6" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Current Progress'!$A$1:$G$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3689" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3797" uniqueCount="414">
   <si>
     <t>workstream</t>
   </si>
@@ -452,6 +452,27 @@
     <t>Added protected sample-output reference manifest plus `enforceSampleOutputReferenceIntegrity` in `qualityGate` and updated policy/docs/boilerplate rollup for the corrected process. [github:committed]</t>
   </si>
   <si>
+    <t>Renderer Output De-Templating 2026-02-24</t>
+  </si>
+  <si>
+    <t>Remove forced semantic template rendering from default HTML sample generation path</t>
+  </si>
+  <si>
+    <t>Updated `AfpHtmlRenderer` default behavior to render raw extracted AFP text preview; semantic template mode is now explicit opt-in only. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Prevent template table injection in DOM diagnostics unless semantic template mode is explicitly enabled</t>
+  </si>
+  <si>
+    <t>Guarded `FakeEngineOutputGenerator` layout-table DOM injection behind the same semantic-template opt-in flag. [github:not-committed]</t>
+  </si>
+  <si>
+    <t>Validate non-normalized sample outputs across all AFP fixtures in preview generated output</t>
+  </si>
+  <si>
+    <t>Executed `:afp-engine:test` and `:afp-cli:generateSampleOutputs`; regenerated distinct sample HTML/PDF artifacts under `preview/generated-sample-output`. [github:not-committed]</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
@@ -821,6 +842,9 @@
     <t>2026-02-24T17:03:45Z</t>
   </si>
   <si>
+    <t>2026-02-24T23:11:03Z</t>
+  </si>
+  <si>
     <t>iteration</t>
   </si>
   <si>
@@ -1059,6 +1083,15 @@
   </si>
   <si>
     <t>Renderer Continuation 2026-02-23-B | Publish continuation diagnostics and next-step delta after slice validations</t>
+  </si>
+  <si>
+    <t>Renderer Output De-Templating 2026-02-24 | Prevent template table injection in DOM diagnostics unless semantic template mode is explicitly enabled</t>
+  </si>
+  <si>
+    <t>Renderer Output De-Templating 2026-02-24 | Remove forced semantic template rendering from default HTML sample generation path</t>
+  </si>
+  <si>
+    <t>Renderer Output De-Templating 2026-02-24 | Validate non-normalized sample outputs across all AFP fixtures in preview generated output</t>
   </si>
   <si>
     <t>Sample Baseline Protection 2026-02-24 | Add enforceable process guardrails for sample baseline integrity and publish policy/docs/process deltas</t>
@@ -1271,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2608,20 +2641,89 @@
         <v>143</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F59" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G59" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F60" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G60" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F61" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="G61" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G58"/>
+  <autoFilter ref="A1:G61"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -2630,25 +2732,25 @@
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K1" t="s" s="0">
         <v>6</v>
@@ -2656,7 +2758,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>7</v>
@@ -2665,19 +2767,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>11</v>
@@ -2686,12 +2788,12 @@
         <v>12</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>7</v>
@@ -2700,19 +2802,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>11</v>
@@ -2721,12 +2823,12 @@
         <v>12</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>7</v>
@@ -2735,19 +2837,19 @@
         <v>16</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
@@ -2756,12 +2858,12 @@
         <v>17</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>7</v>
@@ -2770,19 +2872,19 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>11</v>
@@ -2791,12 +2893,12 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>22</v>
@@ -2805,19 +2907,19 @@
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>11</v>
@@ -2826,12 +2928,12 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>22</v>
@@ -2840,19 +2942,19 @@
         <v>25</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>11</v>
@@ -2861,12 +2963,12 @@
         <v>17</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>22</v>
@@ -2875,19 +2977,19 @@
         <v>27</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G8" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>11</v>
@@ -2896,12 +2998,12 @@
         <v>17</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>22</v>
@@ -2910,19 +3012,19 @@
         <v>29</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>11</v>
@@ -2931,12 +3033,12 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>31</v>
@@ -2945,19 +3047,19 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G10" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>11</v>
@@ -2966,12 +3068,12 @@
         <v>17</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>31</v>
@@ -2980,19 +3082,19 @@
         <v>35</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>11</v>
@@ -3001,12 +3103,12 @@
         <v>12</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="0">
         <v>31</v>
@@ -3015,19 +3117,19 @@
         <v>37</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>11</v>
@@ -3036,12 +3138,12 @@
         <v>17</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="0">
         <v>39</v>
@@ -3050,19 +3152,19 @@
         <v>40</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>11</v>
@@ -3071,12 +3173,12 @@
         <v>12</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="0">
         <v>39</v>
@@ -3085,19 +3187,19 @@
         <v>42</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G14" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>11</v>
@@ -3106,12 +3208,12 @@
         <v>12</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>39</v>
@@ -3120,19 +3222,19 @@
         <v>44</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>11</v>
@@ -3141,12 +3243,12 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="0">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>46</v>
@@ -3155,19 +3257,19 @@
         <v>47</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G16" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>11</v>
@@ -3176,12 +3278,12 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>46</v>
@@ -3190,19 +3292,19 @@
         <v>49</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G17" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>11</v>
@@ -3211,12 +3313,12 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="0">
         <v>46</v>
@@ -3225,19 +3327,19 @@
         <v>51</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>11</v>
@@ -3246,12 +3348,12 @@
         <v>12</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s" s="0">
         <v>53</v>
@@ -3260,19 +3362,19 @@
         <v>54</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>11</v>
@@ -3281,12 +3383,12 @@
         <v>12</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>53</v>
@@ -3295,19 +3397,19 @@
         <v>56</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>11</v>
@@ -3316,12 +3418,12 @@
         <v>12</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s" s="0">
         <v>53</v>
@@ -3330,19 +3432,19 @@
         <v>58</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G21" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I21" t="s" s="0">
         <v>11</v>
@@ -3351,12 +3453,12 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>53</v>
@@ -3365,19 +3467,19 @@
         <v>60</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I22" t="s" s="0">
         <v>11</v>
@@ -3386,12 +3488,12 @@
         <v>17</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="0">
         <v>46</v>
@@ -3400,19 +3502,19 @@
         <v>62</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G23" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I23" t="s" s="0">
         <v>11</v>
@@ -3421,12 +3523,12 @@
         <v>12</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s" s="0">
         <v>46</v>
@@ -3435,19 +3537,19 @@
         <v>64</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G24" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I24" t="s" s="0">
         <v>11</v>
@@ -3456,12 +3558,12 @@
         <v>12</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>46</v>
@@ -3470,19 +3572,19 @@
         <v>66</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I25" t="s" s="0">
         <v>11</v>
@@ -3491,12 +3593,12 @@
         <v>12</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="0">
         <v>46</v>
@@ -3505,19 +3607,19 @@
         <v>68</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I26" t="s" s="0">
         <v>11</v>
@@ -3526,12 +3628,12 @@
         <v>12</v>
       </c>
       <c r="K26" t="s" s="0">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>46</v>
@@ -3540,19 +3642,19 @@
         <v>70</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="0">
         <v>11</v>
@@ -3561,12 +3663,12 @@
         <v>12</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s" s="0">
         <v>72</v>
@@ -3575,19 +3677,19 @@
         <v>73</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G28" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="0">
         <v>11</v>
@@ -3596,12 +3698,12 @@
         <v>17</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="0">
         <v>72</v>
@@ -3610,19 +3712,19 @@
         <v>75</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G29" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I29" t="s" s="0">
         <v>11</v>
@@ -3631,12 +3733,12 @@
         <v>17</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s" s="0">
         <v>72</v>
@@ -3645,19 +3747,19 @@
         <v>77</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G30" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s" s="0">
         <v>11</v>
@@ -3666,12 +3768,12 @@
         <v>17</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B31" t="s" s="0">
         <v>72</v>
@@ -3680,19 +3782,19 @@
         <v>79</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G31" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I31" t="s" s="0">
         <v>11</v>
@@ -3701,12 +3803,12 @@
         <v>17</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s" s="0">
         <v>72</v>
@@ -3715,19 +3817,19 @@
         <v>81</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s" s="0">
         <v>11</v>
@@ -3736,12 +3838,12 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s" s="0">
         <v>72</v>
@@ -3750,19 +3852,19 @@
         <v>83</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="0">
         <v>11</v>
@@ -3771,12 +3873,12 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="0">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>72</v>
@@ -3785,19 +3887,19 @@
         <v>85</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I34" t="s" s="0">
         <v>11</v>
@@ -3806,12 +3908,12 @@
         <v>17</v>
       </c>
       <c r="K34" t="s" s="0">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B35" t="s" s="0">
         <v>72</v>
@@ -3820,19 +3922,19 @@
         <v>87</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G35" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I35" t="s" s="0">
         <v>11</v>
@@ -3841,12 +3943,12 @@
         <v>17</v>
       </c>
       <c r="K35" t="s" s="0">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B36" t="s" s="0">
         <v>89</v>
@@ -3855,19 +3957,19 @@
         <v>90</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G36" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I36" t="s" s="0">
         <v>11</v>
@@ -3876,12 +3978,12 @@
         <v>17</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s" s="0">
         <v>89</v>
@@ -3890,19 +3992,19 @@
         <v>92</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G37" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="0">
         <v>11</v>
@@ -3911,12 +4013,12 @@
         <v>17</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s" s="0">
         <v>89</v>
@@ -3925,19 +4027,19 @@
         <v>94</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G38" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="0">
         <v>11</v>
@@ -3946,12 +4048,12 @@
         <v>17</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s" s="0">
         <v>96</v>
@@ -3960,33 +4062,33 @@
         <v>97</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G39" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="0">
         <v>96</v>
@@ -3995,33 +4097,33 @@
         <v>100</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s" s="0">
         <v>96</v>
@@ -4030,33 +4132,33 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G41" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s" s="0">
         <v>46</v>
@@ -4086,12 +4188,12 @@
         <v>12</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>46</v>
@@ -4121,12 +4223,12 @@
         <v>12</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s" s="0">
         <v>72</v>
@@ -4156,12 +4258,12 @@
         <v>17</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s" s="0">
         <v>96</v>
@@ -4170,7 +4272,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>10</v>
@@ -4182,7 +4284,7 @@
         <v>9</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I45" t="s" s="0">
         <v>11</v>
@@ -4191,12 +4293,12 @@
         <v>98</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s" s="0">
         <v>96</v>
@@ -4205,7 +4307,7 @@
         <v>100</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>10</v>
@@ -4217,7 +4319,7 @@
         <v>9</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I46" t="s" s="0">
         <v>11</v>
@@ -4226,12 +4328,12 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="0">
         <v>96</v>
@@ -4240,7 +4342,7 @@
         <v>102</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>10</v>
@@ -4252,7 +4354,7 @@
         <v>9</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s" s="0">
         <v>11</v>
@@ -4261,12 +4363,12 @@
         <v>98</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s" s="0">
         <v>104</v>
@@ -4275,33 +4377,33 @@
         <v>105</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G48" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="J48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s" s="0">
         <v>104</v>
@@ -4310,33 +4412,33 @@
         <v>107</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G49" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s" s="0">
         <v>104</v>
@@ -4345,33 +4447,33 @@
         <v>109</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G50" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s" s="0">
         <v>104</v>
@@ -4380,33 +4482,33 @@
         <v>111</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E51" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G51" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>104</v>
@@ -4415,33 +4517,33 @@
         <v>113</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E52" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G52" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s" s="0">
         <v>104</v>
@@ -4450,7 +4552,7 @@
         <v>105</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>10</v>
@@ -4462,7 +4564,7 @@
         <v>9</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>11</v>
@@ -4471,12 +4573,12 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s" s="0">
         <v>104</v>
@@ -4485,7 +4587,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>10</v>
@@ -4497,7 +4599,7 @@
         <v>9</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I54" t="s" s="0">
         <v>11</v>
@@ -4506,12 +4608,12 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B55" t="s" s="0">
         <v>104</v>
@@ -4520,10 +4622,10 @@
         <v>109</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F55" t="s" s="0">
         <v>9</v>
@@ -4532,21 +4634,21 @@
         <v>9</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s" s="0">
         <v>104</v>
@@ -4555,10 +4657,10 @@
         <v>111</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E56" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F56" t="s" s="0">
         <v>9</v>
@@ -4567,21 +4669,21 @@
         <v>9</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K56" t="s" s="0">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s" s="0">
         <v>104</v>
@@ -4590,7 +4692,7 @@
         <v>113</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>10</v>
@@ -4602,7 +4704,7 @@
         <v>9</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I57" t="s" s="0">
         <v>11</v>
@@ -4611,12 +4713,12 @@
         <v>98</v>
       </c>
       <c r="K57" t="s" s="0">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s" s="0">
         <v>104</v>
@@ -4625,10 +4727,10 @@
         <v>109</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F58" t="s" s="0">
         <v>9</v>
@@ -4637,21 +4739,21 @@
         <v>9</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K58" t="s" s="0">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B59" t="s" s="0">
         <v>104</v>
@@ -4660,7 +4762,7 @@
         <v>111</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>10</v>
@@ -4672,7 +4774,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="I59" t="s" s="0">
         <v>11</v>
@@ -4681,12 +4783,12 @@
         <v>98</v>
       </c>
       <c r="K59" t="s" s="0">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B60" t="s" s="0">
         <v>7</v>
@@ -4721,7 +4823,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s" s="0">
         <v>7</v>
@@ -4756,7 +4858,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B62" t="s" s="0">
         <v>7</v>
@@ -4791,7 +4893,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B63" t="s" s="0">
         <v>7</v>
@@ -4826,7 +4928,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B64" t="s" s="0">
         <v>22</v>
@@ -4861,7 +4963,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B65" t="s" s="0">
         <v>22</v>
@@ -4896,7 +4998,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B66" t="s" s="0">
         <v>22</v>
@@ -4931,7 +5033,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>22</v>
@@ -4966,7 +5068,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s" s="0">
         <v>31</v>
@@ -5001,7 +5103,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s" s="0">
         <v>31</v>
@@ -5036,7 +5138,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s" s="0">
         <v>31</v>
@@ -5071,7 +5173,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s" s="0">
         <v>39</v>
@@ -5106,7 +5208,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B72" t="s" s="0">
         <v>39</v>
@@ -5141,7 +5243,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B73" t="s" s="0">
         <v>39</v>
@@ -5176,7 +5278,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s" s="0">
         <v>46</v>
@@ -5211,7 +5313,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>46</v>
@@ -5246,7 +5348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B76" t="s" s="0">
         <v>46</v>
@@ -5281,7 +5383,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s" s="0">
         <v>53</v>
@@ -5316,7 +5418,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s" s="0">
         <v>53</v>
@@ -5351,7 +5453,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B79" t="s" s="0">
         <v>53</v>
@@ -5386,7 +5488,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B80" t="s" s="0">
         <v>53</v>
@@ -5421,7 +5523,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B81" t="s" s="0">
         <v>46</v>
@@ -5456,7 +5558,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B82" t="s" s="0">
         <v>46</v>
@@ -5491,7 +5593,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>46</v>
@@ -5526,7 +5628,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B84" t="s" s="0">
         <v>46</v>
@@ -5561,7 +5663,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B85" t="s" s="0">
         <v>46</v>
@@ -5596,7 +5698,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>72</v>
@@ -5631,7 +5733,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B87" t="s" s="0">
         <v>72</v>
@@ -5666,7 +5768,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B88" t="s" s="0">
         <v>72</v>
@@ -5701,7 +5803,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B89" t="s" s="0">
         <v>72</v>
@@ -5736,7 +5838,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B90" t="s" s="0">
         <v>72</v>
@@ -5771,7 +5873,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s" s="0">
         <v>72</v>
@@ -5806,7 +5908,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B92" t="s" s="0">
         <v>72</v>
@@ -5841,7 +5943,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B93" t="s" s="0">
         <v>72</v>
@@ -5876,7 +5978,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B94" t="s" s="0">
         <v>89</v>
@@ -5911,7 +6013,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B95" t="s" s="0">
         <v>89</v>
@@ -5946,7 +6048,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B96" t="s" s="0">
         <v>89</v>
@@ -5981,7 +6083,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B97" t="s" s="0">
         <v>96</v>
@@ -6011,12 +6113,12 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="0">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B98" t="s" s="0">
         <v>96</v>
@@ -6046,12 +6148,12 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="0">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B99" t="s" s="0">
         <v>96</v>
@@ -6081,12 +6183,12 @@
         <v>98</v>
       </c>
       <c r="K99" t="s" s="0">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B100" t="s" s="0">
         <v>104</v>
@@ -6116,12 +6218,12 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="0">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B101" t="s" s="0">
         <v>104</v>
@@ -6151,12 +6253,12 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="0">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B102" t="s" s="0">
         <v>104</v>
@@ -6186,12 +6288,12 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B103" t="s" s="0">
         <v>104</v>
@@ -6221,12 +6323,12 @@
         <v>98</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B104" t="s" s="0">
         <v>104</v>
@@ -6235,10 +6337,10 @@
         <v>109</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E104" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F104" t="s" s="0">
         <v>9</v>
@@ -6247,21 +6349,21 @@
         <v>9</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="J104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B105" t="s" s="0">
         <v>104</v>
@@ -6296,7 +6398,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B106" t="s" s="0">
         <v>104</v>
@@ -6331,7 +6433,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B107" t="s" s="0">
         <v>104</v>
@@ -6340,7 +6442,7 @@
         <v>109</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>10</v>
@@ -6352,7 +6454,7 @@
         <v>9</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I107" t="s" s="0">
         <v>11</v>
@@ -6366,7 +6468,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s" s="0">
         <v>104</v>
@@ -6401,7 +6503,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s" s="0">
         <v>104</v>
@@ -6436,7 +6538,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B110" t="s" s="0">
         <v>96</v>
@@ -6471,7 +6573,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B111" t="s" s="0">
         <v>96</v>
@@ -6506,7 +6608,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B112" t="s" s="0">
         <v>96</v>
@@ -6541,7 +6643,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B113" t="s" s="0">
         <v>115</v>
@@ -6550,33 +6652,33 @@
         <v>116</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G113" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="J113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K113" t="s" s="0">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B114" t="s" s="0">
         <v>115</v>
@@ -6585,33 +6687,33 @@
         <v>118</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G114" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K114" t="s" s="0">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B115" t="s" s="0">
         <v>115</v>
@@ -6620,33 +6722,33 @@
         <v>120</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G115" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K115" t="s" s="0">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B116" t="s" s="0">
         <v>115</v>
@@ -6655,7 +6757,7 @@
         <v>116</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>10</v>
@@ -6667,7 +6769,7 @@
         <v>9</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I116" t="s" s="0">
         <v>11</v>
@@ -6681,7 +6783,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s" s="0">
         <v>115</v>
@@ -6690,10 +6792,10 @@
         <v>118</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F117" t="s" s="0">
         <v>9</v>
@@ -6702,21 +6804,21 @@
         <v>9</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="J117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K117" t="s" s="0">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B118" t="s" s="0">
         <v>115</v>
@@ -6725,7 +6827,7 @@
         <v>118</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>10</v>
@@ -6737,7 +6839,7 @@
         <v>9</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I118" t="s" s="0">
         <v>11</v>
@@ -6751,7 +6853,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B119" t="s" s="0">
         <v>115</v>
@@ -6760,10 +6862,10 @@
         <v>120</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E119" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F119" t="s" s="0">
         <v>33</v>
@@ -6772,21 +6874,21 @@
         <v>33</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K119" t="s" s="0">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B120" t="s" s="0">
         <v>115</v>
@@ -6795,7 +6897,7 @@
         <v>120</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>10</v>
@@ -6807,7 +6909,7 @@
         <v>33</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="I120" t="s" s="0">
         <v>11</v>
@@ -6821,7 +6923,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B121" t="s" s="0">
         <v>122</v>
@@ -6830,33 +6932,33 @@
         <v>123</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G121" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="J121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K121" t="s" s="0">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B122" t="s" s="0">
         <v>122</v>
@@ -6865,33 +6967,33 @@
         <v>125</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G122" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K122" t="s" s="0">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B123" t="s" s="0">
         <v>122</v>
@@ -6900,33 +7002,33 @@
         <v>127</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G123" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="K123" t="s" s="0">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B124" t="s" s="0">
         <v>122</v>
@@ -6935,7 +7037,7 @@
         <v>123</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>10</v>
@@ -6947,7 +7049,7 @@
         <v>9</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I124" t="s" s="0">
         <v>11</v>
@@ -6956,12 +7058,12 @@
         <v>98</v>
       </c>
       <c r="K124" t="s" s="0">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B125" t="s" s="0">
         <v>122</v>
@@ -6970,7 +7072,7 @@
         <v>125</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>10</v>
@@ -6982,7 +7084,7 @@
         <v>9</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I125" t="s" s="0">
         <v>11</v>
@@ -6996,7 +7098,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B126" t="s" s="0">
         <v>122</v>
@@ -7005,7 +7107,7 @@
         <v>127</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>10</v>
@@ -7017,7 +7119,7 @@
         <v>33</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I126" t="s" s="0">
         <v>11</v>
@@ -7031,7 +7133,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B127" t="s" s="0">
         <v>122</v>
@@ -7066,7 +7168,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B128" t="s" s="0">
         <v>129</v>
@@ -7075,19 +7177,19 @@
         <v>130</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E128" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G128" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H128" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I128" t="s" s="0">
         <v>11</v>
@@ -7096,12 +7198,12 @@
         <v>131</v>
       </c>
       <c r="K128" t="s" s="0">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B129" t="s" s="0">
         <v>129</v>
@@ -7110,19 +7212,19 @@
         <v>133</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G129" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H129" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I129" t="s" s="0">
         <v>11</v>
@@ -7136,7 +7238,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B130" t="s" s="0">
         <v>129</v>
@@ -7145,19 +7247,19 @@
         <v>135</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G130" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H130" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I130" t="s" s="0">
         <v>11</v>
@@ -7171,7 +7273,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B131" t="s" s="0">
         <v>129</v>
@@ -7206,7 +7308,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s" s="0">
         <v>137</v>
@@ -7215,19 +7317,19 @@
         <v>138</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G132" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H132" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I132" t="s" s="0">
         <v>11</v>
@@ -7236,12 +7338,12 @@
         <v>131</v>
       </c>
       <c r="K132" t="s" s="0">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B133" t="s" s="0">
         <v>137</v>
@@ -7250,19 +7352,19 @@
         <v>140</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E133" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F133" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G133" t="s" s="0">
         <v>9</v>
       </c>
       <c r="H133" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I133" t="s" s="0">
         <v>11</v>
@@ -7271,12 +7373,12 @@
         <v>131</v>
       </c>
       <c r="K133" t="s" s="0">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B134" t="s" s="0">
         <v>137</v>
@@ -7285,19 +7387,19 @@
         <v>142</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E134" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G134" t="s" s="0">
         <v>33</v>
       </c>
       <c r="H134" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I134" t="s" s="0">
         <v>11</v>
@@ -7306,12 +7408,12 @@
         <v>131</v>
       </c>
       <c r="K134" t="s" s="0">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B135" t="s" s="0">
         <v>137</v>
@@ -7341,12 +7443,12 @@
         <v>131</v>
       </c>
       <c r="K135" t="s" s="0">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B136" t="s" s="0">
         <v>137</v>
@@ -7381,7 +7483,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B137" t="s" s="0">
         <v>137</v>
@@ -7416,7 +7518,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B138" t="s" s="0">
         <v>137</v>
@@ -7447,6 +7549,111 @@
       </c>
       <c r="K138" t="s" s="0">
         <v>143</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D139" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E139" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F139" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="G139" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H139" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="I139" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J139" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K139" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C140" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D140" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E140" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F140" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="G140" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H140" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="I140" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J140" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K140" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F141" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="G141" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="H141" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="I141" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="J141" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="K141" t="s" s="0">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -7456,7 +7663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7470,25 +7677,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
@@ -7502,7 +7709,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>12</v>
@@ -7511,13 +7718,13 @@
         <v>11</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -7531,7 +7738,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>12</v>
@@ -7540,13 +7747,13 @@
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -7560,7 +7767,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>17</v>
@@ -7569,13 +7776,13 @@
         <v>11</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -7589,7 +7796,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>20</v>
@@ -7598,13 +7805,13 @@
         <v>11</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
@@ -7618,7 +7825,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>17</v>
@@ -7627,13 +7834,13 @@
         <v>11</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -7647,7 +7854,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>17</v>
@@ -7656,13 +7863,13 @@
         <v>11</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H7" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
@@ -7676,7 +7883,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>17</v>
@@ -7685,13 +7892,13 @@
         <v>11</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H8" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9">
@@ -7705,7 +7912,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>20</v>
@@ -7714,13 +7921,13 @@
         <v>11</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H9" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -7734,7 +7941,7 @@
         <v>33</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E10" t="s" s="0">
         <v>17</v>
@@ -7743,13 +7950,13 @@
         <v>11</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -7763,7 +7970,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>12</v>
@@ -7772,13 +7979,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H11" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
@@ -7792,7 +7999,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>17</v>
@@ -7801,13 +8008,13 @@
         <v>11</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H12" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
@@ -7821,7 +8028,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>12</v>
@@ -7830,13 +8037,13 @@
         <v>11</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H13" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
@@ -7850,7 +8057,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>12</v>
@@ -7859,13 +8066,13 @@
         <v>11</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H14" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15">
@@ -7879,7 +8086,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>20</v>
@@ -7888,13 +8095,13 @@
         <v>11</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H15" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16">
@@ -7908,7 +8115,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>17</v>
@@ -7917,13 +8124,13 @@
         <v>11</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H16" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
@@ -7937,7 +8144,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>17</v>
@@ -7946,13 +8153,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18">
@@ -7966,7 +8173,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>12</v>
@@ -7975,13 +8182,13 @@
         <v>11</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19">
@@ -7995,7 +8202,7 @@
         <v>9</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>12</v>
@@ -8004,13 +8211,13 @@
         <v>11</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H19" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20">
@@ -8024,7 +8231,7 @@
         <v>9</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E20" t="s" s="0">
         <v>12</v>
@@ -8033,13 +8240,13 @@
         <v>11</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H20" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21">
@@ -8053,7 +8260,7 @@
         <v>9</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E21" t="s" s="0">
         <v>20</v>
@@ -8062,13 +8269,13 @@
         <v>11</v>
       </c>
       <c r="G21" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H21" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22">
@@ -8082,7 +8289,7 @@
         <v>9</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E22" t="s" s="0">
         <v>17</v>
@@ -8091,13 +8298,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H22" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23">
@@ -8111,7 +8318,7 @@
         <v>9</v>
       </c>
       <c r="D23" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s" s="0">
         <v>12</v>
@@ -8120,13 +8327,13 @@
         <v>11</v>
       </c>
       <c r="G23" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H23" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24">
@@ -8140,7 +8347,7 @@
         <v>9</v>
       </c>
       <c r="D24" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E24" t="s" s="0">
         <v>12</v>
@@ -8149,13 +8356,13 @@
         <v>11</v>
       </c>
       <c r="G24" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25">
@@ -8169,7 +8376,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E25" t="s" s="0">
         <v>12</v>
@@ -8178,13 +8385,13 @@
         <v>11</v>
       </c>
       <c r="G25" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H25" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26">
@@ -8198,7 +8405,7 @@
         <v>9</v>
       </c>
       <c r="D26" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>12</v>
@@ -8207,13 +8414,13 @@
         <v>11</v>
       </c>
       <c r="G26" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H26" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I26" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27">
@@ -8227,7 +8434,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E27" t="s" s="0">
         <v>12</v>
@@ -8236,13 +8443,13 @@
         <v>11</v>
       </c>
       <c r="G27" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28">
@@ -8256,7 +8463,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E28" t="s" s="0">
         <v>17</v>
@@ -8265,13 +8472,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H28" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29">
@@ -8285,7 +8492,7 @@
         <v>9</v>
       </c>
       <c r="D29" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E29" t="s" s="0">
         <v>17</v>
@@ -8294,13 +8501,13 @@
         <v>11</v>
       </c>
       <c r="G29" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H29" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I29" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
@@ -8314,7 +8521,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E30" t="s" s="0">
         <v>17</v>
@@ -8323,13 +8530,13 @@
         <v>11</v>
       </c>
       <c r="G30" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H30" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31">
@@ -8343,7 +8550,7 @@
         <v>9</v>
       </c>
       <c r="D31" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
@@ -8352,13 +8559,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32">
@@ -8372,7 +8579,7 @@
         <v>9</v>
       </c>
       <c r="D32" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
@@ -8381,13 +8588,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H32" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
@@ -8401,7 +8608,7 @@
         <v>9</v>
       </c>
       <c r="D33" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
@@ -8410,13 +8617,13 @@
         <v>11</v>
       </c>
       <c r="G33" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H33" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I33" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34">
@@ -8430,7 +8637,7 @@
         <v>9</v>
       </c>
       <c r="D34" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
@@ -8439,13 +8646,13 @@
         <v>11</v>
       </c>
       <c r="G34" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H34" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I34" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35">
@@ -8459,7 +8666,7 @@
         <v>9</v>
       </c>
       <c r="D35" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E35" t="s" s="0">
         <v>17</v>
@@ -8468,13 +8675,13 @@
         <v>11</v>
       </c>
       <c r="G35" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H35" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I35" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36">
@@ -8488,7 +8695,7 @@
         <v>9</v>
       </c>
       <c r="D36" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E36" t="s" s="0">
         <v>17</v>
@@ -8497,13 +8704,13 @@
         <v>11</v>
       </c>
       <c r="G36" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H36" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37">
@@ -8517,7 +8724,7 @@
         <v>9</v>
       </c>
       <c r="D37" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E37" t="s" s="0">
         <v>17</v>
@@ -8526,13 +8733,13 @@
         <v>11</v>
       </c>
       <c r="G37" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H37" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38">
@@ -8546,7 +8753,7 @@
         <v>9</v>
       </c>
       <c r="D38" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
@@ -8555,13 +8762,13 @@
         <v>11</v>
       </c>
       <c r="G38" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H38" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39">
@@ -8575,22 +8782,22 @@
         <v>9</v>
       </c>
       <c r="D39" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E39" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40">
@@ -8604,22 +8811,22 @@
         <v>9</v>
       </c>
       <c r="D40" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E40" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G40" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41">
@@ -8633,22 +8840,22 @@
         <v>9</v>
       </c>
       <c r="D41" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E41" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G41" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42">
@@ -8662,7 +8869,7 @@
         <v>9</v>
       </c>
       <c r="D42" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E42" t="s" s="0">
         <v>12</v>
@@ -8671,13 +8878,13 @@
         <v>11</v>
       </c>
       <c r="G42" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43">
@@ -8691,7 +8898,7 @@
         <v>9</v>
       </c>
       <c r="D43" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E43" t="s" s="0">
         <v>12</v>
@@ -8700,13 +8907,13 @@
         <v>11</v>
       </c>
       <c r="G43" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H43" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44">
@@ -8720,7 +8927,7 @@
         <v>9</v>
       </c>
       <c r="D44" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E44" t="s" s="0">
         <v>17</v>
@@ -8729,13 +8936,13 @@
         <v>11</v>
       </c>
       <c r="G44" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H44" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45">
@@ -8749,7 +8956,7 @@
         <v>9</v>
       </c>
       <c r="D45" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>98</v>
@@ -8758,13 +8965,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s" s="0">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="H45" t="s" s="0">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46">
@@ -8778,7 +8985,7 @@
         <v>9</v>
       </c>
       <c r="D46" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E46" t="s" s="0">
         <v>98</v>
@@ -8790,10 +8997,10 @@
         <v>11</v>
       </c>
       <c r="H46" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47">
@@ -8807,7 +9014,7 @@
         <v>9</v>
       </c>
       <c r="D47" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E47" t="s" s="0">
         <v>98</v>
@@ -8819,10 +9026,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48">
@@ -8836,22 +9043,22 @@
         <v>9</v>
       </c>
       <c r="D48" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E48" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="G48" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H48" t="s" s="0">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49">
@@ -8865,22 +9072,22 @@
         <v>9</v>
       </c>
       <c r="D49" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E49" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G49" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H49" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50">
@@ -8894,22 +9101,22 @@
         <v>9</v>
       </c>
       <c r="D50" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E50" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G50" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H50" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51">
@@ -8923,22 +9130,22 @@
         <v>9</v>
       </c>
       <c r="D51" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G51" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H51" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52">
@@ -8952,22 +9159,22 @@
         <v>9</v>
       </c>
       <c r="D52" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G52" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H52" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53">
@@ -8981,7 +9188,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>98</v>
@@ -8990,13 +9197,13 @@
         <v>11</v>
       </c>
       <c r="G53" t="s" s="0">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="H53" t="s" s="0">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54">
@@ -9010,7 +9217,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>98</v>
@@ -9022,10 +9229,10 @@
         <v>11</v>
       </c>
       <c r="H54" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I54" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55">
@@ -9039,22 +9246,22 @@
         <v>9</v>
       </c>
       <c r="D55" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E55" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G55" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H55" t="s" s="0">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56">
@@ -9068,22 +9275,22 @@
         <v>9</v>
       </c>
       <c r="D56" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="G56" t="s" s="0">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H56" t="s" s="0">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I56" t="s" s="0">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="57">
@@ -9097,7 +9304,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>98</v>
@@ -9109,10 +9316,10 @@
         <v>11</v>
       </c>
       <c r="H57" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I57" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58">
@@ -9126,22 +9333,22 @@
         <v>9</v>
       </c>
       <c r="D58" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E58" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G58" t="s" s="0">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H58" t="s" s="0">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I58" t="s" s="0">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59">
@@ -9155,7 +9362,7 @@
         <v>9</v>
       </c>
       <c r="D59" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E59" t="s" s="0">
         <v>98</v>
@@ -9164,13 +9371,13 @@
         <v>11</v>
       </c>
       <c r="G59" t="s" s="0">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="H59" t="s" s="0">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="I59" t="s" s="0">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60">
@@ -9184,7 +9391,7 @@
         <v>9</v>
       </c>
       <c r="D60" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E60" t="s" s="0">
         <v>12</v>
@@ -9193,13 +9400,13 @@
         <v>11</v>
       </c>
       <c r="G60" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H60" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61">
@@ -9213,7 +9420,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E61" t="s" s="0">
         <v>12</v>
@@ -9222,13 +9429,13 @@
         <v>11</v>
       </c>
       <c r="G61" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H61" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62">
@@ -9242,7 +9449,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E62" t="s" s="0">
         <v>17</v>
@@ -9251,13 +9458,13 @@
         <v>11</v>
       </c>
       <c r="G62" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H62" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="63">
@@ -9271,7 +9478,7 @@
         <v>9</v>
       </c>
       <c r="D63" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E63" t="s" s="0">
         <v>20</v>
@@ -9280,13 +9487,13 @@
         <v>11</v>
       </c>
       <c r="G63" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H63" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64">
@@ -9300,7 +9507,7 @@
         <v>9</v>
       </c>
       <c r="D64" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E64" t="s" s="0">
         <v>17</v>
@@ -9309,13 +9516,13 @@
         <v>11</v>
       </c>
       <c r="G64" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H64" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65">
@@ -9329,7 +9536,7 @@
         <v>9</v>
       </c>
       <c r="D65" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E65" t="s" s="0">
         <v>17</v>
@@ -9338,13 +9545,13 @@
         <v>11</v>
       </c>
       <c r="G65" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H65" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66">
@@ -9358,7 +9565,7 @@
         <v>9</v>
       </c>
       <c r="D66" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E66" t="s" s="0">
         <v>17</v>
@@ -9367,13 +9574,13 @@
         <v>11</v>
       </c>
       <c r="G66" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H66" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67">
@@ -9387,7 +9594,7 @@
         <v>9</v>
       </c>
       <c r="D67" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E67" t="s" s="0">
         <v>20</v>
@@ -9396,13 +9603,13 @@
         <v>11</v>
       </c>
       <c r="G67" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H67" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="68">
@@ -9416,7 +9623,7 @@
         <v>33</v>
       </c>
       <c r="D68" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E68" t="s" s="0">
         <v>17</v>
@@ -9425,13 +9632,13 @@
         <v>11</v>
       </c>
       <c r="G68" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H68" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69">
@@ -9445,7 +9652,7 @@
         <v>33</v>
       </c>
       <c r="D69" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>12</v>
@@ -9454,13 +9661,13 @@
         <v>11</v>
       </c>
       <c r="G69" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H69" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70">
@@ -9474,7 +9681,7 @@
         <v>33</v>
       </c>
       <c r="D70" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E70" t="s" s="0">
         <v>17</v>
@@ -9483,13 +9690,13 @@
         <v>11</v>
       </c>
       <c r="G70" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H70" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71">
@@ -9503,7 +9710,7 @@
         <v>33</v>
       </c>
       <c r="D71" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E71" t="s" s="0">
         <v>12</v>
@@ -9512,13 +9719,13 @@
         <v>11</v>
       </c>
       <c r="G71" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H71" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="72">
@@ -9532,7 +9739,7 @@
         <v>33</v>
       </c>
       <c r="D72" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E72" t="s" s="0">
         <v>12</v>
@@ -9541,13 +9748,13 @@
         <v>11</v>
       </c>
       <c r="G72" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H72" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73">
@@ -9561,7 +9768,7 @@
         <v>33</v>
       </c>
       <c r="D73" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E73" t="s" s="0">
         <v>20</v>
@@ -9570,13 +9777,13 @@
         <v>11</v>
       </c>
       <c r="G73" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H73" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="74">
@@ -9590,7 +9797,7 @@
         <v>33</v>
       </c>
       <c r="D74" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
@@ -9599,13 +9806,13 @@
         <v>11</v>
       </c>
       <c r="G74" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H74" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="75">
@@ -9619,7 +9826,7 @@
         <v>33</v>
       </c>
       <c r="D75" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
@@ -9628,13 +9835,13 @@
         <v>11</v>
       </c>
       <c r="G75" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H75" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="76">
@@ -9648,7 +9855,7 @@
         <v>33</v>
       </c>
       <c r="D76" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E76" t="s" s="0">
         <v>12</v>
@@ -9657,13 +9864,13 @@
         <v>11</v>
       </c>
       <c r="G76" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H76" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="77">
@@ -9677,7 +9884,7 @@
         <v>9</v>
       </c>
       <c r="D77" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>12</v>
@@ -9686,13 +9893,13 @@
         <v>11</v>
       </c>
       <c r="G77" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H77" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9913,7 @@
         <v>9</v>
       </c>
       <c r="D78" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E78" t="s" s="0">
         <v>12</v>
@@ -9715,13 +9922,13 @@
         <v>11</v>
       </c>
       <c r="G78" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H78" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I78" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="79">
@@ -9735,7 +9942,7 @@
         <v>9</v>
       </c>
       <c r="D79" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>20</v>
@@ -9744,13 +9951,13 @@
         <v>11</v>
       </c>
       <c r="G79" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H79" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="80">
@@ -9764,7 +9971,7 @@
         <v>9</v>
       </c>
       <c r="D80" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E80" t="s" s="0">
         <v>17</v>
@@ -9773,13 +9980,13 @@
         <v>11</v>
       </c>
       <c r="G80" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H80" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="81">
@@ -9793,7 +10000,7 @@
         <v>9</v>
       </c>
       <c r="D81" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>12</v>
@@ -9802,13 +10009,13 @@
         <v>11</v>
       </c>
       <c r="G81" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H81" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="82">
@@ -9822,7 +10029,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>12</v>
@@ -9831,13 +10038,13 @@
         <v>11</v>
       </c>
       <c r="G82" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H82" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="83">
@@ -9851,7 +10058,7 @@
         <v>9</v>
       </c>
       <c r="D83" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E83" t="s" s="0">
         <v>12</v>
@@ -9860,13 +10067,13 @@
         <v>11</v>
       </c>
       <c r="G83" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H83" t="s" s="0">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="84">
@@ -9880,7 +10087,7 @@
         <v>9</v>
       </c>
       <c r="D84" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E84" t="s" s="0">
         <v>12</v>
@@ -9889,13 +10096,13 @@
         <v>11</v>
       </c>
       <c r="G84" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H84" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="85">
@@ -9909,7 +10116,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>12</v>
@@ -9918,13 +10125,13 @@
         <v>11</v>
       </c>
       <c r="G85" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H85" t="s" s="0">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I85" t="s" s="0">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86">
@@ -9938,7 +10145,7 @@
         <v>9</v>
       </c>
       <c r="D86" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E86" t="s" s="0">
         <v>17</v>
@@ -9947,13 +10154,13 @@
         <v>11</v>
       </c>
       <c r="G86" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H86" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="87">
@@ -9967,7 +10174,7 @@
         <v>9</v>
       </c>
       <c r="D87" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E87" t="s" s="0">
         <v>17</v>
@@ -9976,13 +10183,13 @@
         <v>11</v>
       </c>
       <c r="G87" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H87" t="s" s="0">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="88">
@@ -9996,7 +10203,7 @@
         <v>9</v>
       </c>
       <c r="D88" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E88" t="s" s="0">
         <v>17</v>
@@ -10005,13 +10212,13 @@
         <v>11</v>
       </c>
       <c r="G88" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H88" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="89">
@@ -10025,7 +10232,7 @@
         <v>9</v>
       </c>
       <c r="D89" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
@@ -10034,13 +10241,13 @@
         <v>11</v>
       </c>
       <c r="G89" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H89" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90">
@@ -10054,7 +10261,7 @@
         <v>9</v>
       </c>
       <c r="D90" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E90" t="s" s="0">
         <v>17</v>
@@ -10063,13 +10270,13 @@
         <v>11</v>
       </c>
       <c r="G90" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H90" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="91">
@@ -10083,7 +10290,7 @@
         <v>9</v>
       </c>
       <c r="D91" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E91" t="s" s="0">
         <v>17</v>
@@ -10092,13 +10299,13 @@
         <v>11</v>
       </c>
       <c r="G91" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H91" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="92">
@@ -10112,7 +10319,7 @@
         <v>9</v>
       </c>
       <c r="D92" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E92" t="s" s="0">
         <v>17</v>
@@ -10121,13 +10328,13 @@
         <v>11</v>
       </c>
       <c r="G92" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H92" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="93">
@@ -10141,7 +10348,7 @@
         <v>9</v>
       </c>
       <c r="D93" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E93" t="s" s="0">
         <v>17</v>
@@ -10150,13 +10357,13 @@
         <v>11</v>
       </c>
       <c r="G93" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H93" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="94">
@@ -10170,7 +10377,7 @@
         <v>9</v>
       </c>
       <c r="D94" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E94" t="s" s="0">
         <v>17</v>
@@ -10179,13 +10386,13 @@
         <v>11</v>
       </c>
       <c r="G94" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H94" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95">
@@ -10199,7 +10406,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E95" t="s" s="0">
         <v>17</v>
@@ -10208,13 +10415,13 @@
         <v>11</v>
       </c>
       <c r="G95" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H95" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="96">
@@ -10228,7 +10435,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
@@ -10237,13 +10444,13 @@
         <v>11</v>
       </c>
       <c r="G96" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H96" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I96" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97">
@@ -10257,7 +10464,7 @@
         <v>9</v>
       </c>
       <c r="D97" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E97" t="s" s="0">
         <v>98</v>
@@ -10266,13 +10473,13 @@
         <v>11</v>
       </c>
       <c r="G97" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H97" t="s" s="0">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="I97" t="s" s="0">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98">
@@ -10286,7 +10493,7 @@
         <v>9</v>
       </c>
       <c r="D98" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E98" t="s" s="0">
         <v>98</v>
@@ -10295,13 +10502,13 @@
         <v>11</v>
       </c>
       <c r="G98" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H98" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I98" t="s" s="0">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99">
@@ -10315,7 +10522,7 @@
         <v>9</v>
       </c>
       <c r="D99" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>98</v>
@@ -10324,13 +10531,13 @@
         <v>11</v>
       </c>
       <c r="G99" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H99" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I99" t="s" s="0">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100">
@@ -10344,7 +10551,7 @@
         <v>9</v>
       </c>
       <c r="D100" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E100" t="s" s="0">
         <v>98</v>
@@ -10353,13 +10560,13 @@
         <v>11</v>
       </c>
       <c r="G100" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H100" t="s" s="0">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I100" t="s" s="0">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101">
@@ -10373,7 +10580,7 @@
         <v>9</v>
       </c>
       <c r="D101" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E101" t="s" s="0">
         <v>98</v>
@@ -10382,13 +10589,13 @@
         <v>11</v>
       </c>
       <c r="G101" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H101" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I101" t="s" s="0">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102">
@@ -10402,7 +10609,7 @@
         <v>9</v>
       </c>
       <c r="D102" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E102" t="s" s="0">
         <v>98</v>
@@ -10411,13 +10618,13 @@
         <v>11</v>
       </c>
       <c r="G102" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H102" t="s" s="0">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103">
@@ -10431,7 +10638,7 @@
         <v>9</v>
       </c>
       <c r="D103" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E103" t="s" s="0">
         <v>98</v>
@@ -10440,13 +10647,13 @@
         <v>11</v>
       </c>
       <c r="G103" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H103" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104">
@@ -10460,22 +10667,22 @@
         <v>9</v>
       </c>
       <c r="D104" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G104" t="s" s="0">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H104" t="s" s="0">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105">
@@ -10489,7 +10696,7 @@
         <v>9</v>
       </c>
       <c r="D105" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E105" t="s" s="0">
         <v>98</v>
@@ -10498,13 +10705,13 @@
         <v>11</v>
       </c>
       <c r="G105" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H105" t="s" s="0">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I105" t="s" s="0">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="106">
@@ -10518,7 +10725,7 @@
         <v>9</v>
       </c>
       <c r="D106" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>98</v>
@@ -10527,13 +10734,13 @@
         <v>11</v>
       </c>
       <c r="G106" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H106" t="s" s="0">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107">
@@ -10547,7 +10754,7 @@
         <v>9</v>
       </c>
       <c r="D107" t="s" s="0">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E107" t="s" s="0">
         <v>98</v>
@@ -10556,13 +10763,13 @@
         <v>11</v>
       </c>
       <c r="G107" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H107" t="s" s="0">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="I107" t="s" s="0">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108">
@@ -10576,7 +10783,7 @@
         <v>9</v>
       </c>
       <c r="D108" t="s" s="0">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E108" t="s" s="0">
         <v>98</v>
@@ -10585,13 +10792,13 @@
         <v>11</v>
       </c>
       <c r="G108" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H108" t="s" s="0">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I108" t="s" s="0">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109">
@@ -10605,7 +10812,7 @@
         <v>9</v>
       </c>
       <c r="D109" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E109" t="s" s="0">
         <v>98</v>
@@ -10614,13 +10821,13 @@
         <v>11</v>
       </c>
       <c r="G109" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H109" t="s" s="0">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I109" t="s" s="0">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="110">
@@ -10634,7 +10841,7 @@
         <v>9</v>
       </c>
       <c r="D110" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E110" t="s" s="0">
         <v>98</v>
@@ -10643,13 +10850,13 @@
         <v>11</v>
       </c>
       <c r="G110" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H110" t="s" s="0">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="I110" t="s" s="0">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="111">
@@ -10663,7 +10870,7 @@
         <v>9</v>
       </c>
       <c r="D111" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E111" t="s" s="0">
         <v>98</v>
@@ -10672,13 +10879,13 @@
         <v>11</v>
       </c>
       <c r="G111" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H111" t="s" s="0">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I111" t="s" s="0">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="112">
@@ -10692,7 +10899,7 @@
         <v>9</v>
       </c>
       <c r="D112" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E112" t="s" s="0">
         <v>98</v>
@@ -10701,13 +10908,13 @@
         <v>11</v>
       </c>
       <c r="G112" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H112" t="s" s="0">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="I112" t="s" s="0">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="113">
@@ -10721,22 +10928,22 @@
         <v>9</v>
       </c>
       <c r="D113" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E113" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G113" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H113" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I113" t="s" s="0">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="114">
@@ -10750,22 +10957,22 @@
         <v>9</v>
       </c>
       <c r="D114" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E114" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G114" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H114" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I114" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="115">
@@ -10779,22 +10986,22 @@
         <v>33</v>
       </c>
       <c r="D115" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E115" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G115" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H115" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I115" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="116">
@@ -10808,7 +11015,7 @@
         <v>9</v>
       </c>
       <c r="D116" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>98</v>
@@ -10817,13 +11024,13 @@
         <v>11</v>
       </c>
       <c r="G116" t="s" s="0">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H116" t="s" s="0">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="I116" t="s" s="0">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117">
@@ -10837,22 +11044,22 @@
         <v>9</v>
       </c>
       <c r="D117" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E117" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="G117" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H117" t="s" s="0">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I117" t="s" s="0">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="118">
@@ -10866,7 +11073,7 @@
         <v>9</v>
       </c>
       <c r="D118" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E118" t="s" s="0">
         <v>98</v>
@@ -10875,13 +11082,13 @@
         <v>11</v>
       </c>
       <c r="G118" t="s" s="0">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="H118" t="s" s="0">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="I118" t="s" s="0">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="119">
@@ -10895,22 +11102,22 @@
         <v>33</v>
       </c>
       <c r="D119" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G119" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H119" t="s" s="0">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="I119" t="s" s="0">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="120">
@@ -10924,7 +11131,7 @@
         <v>33</v>
       </c>
       <c r="D120" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E120" t="s" s="0">
         <v>98</v>
@@ -10933,13 +11140,13 @@
         <v>11</v>
       </c>
       <c r="G120" t="s" s="0">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="H120" t="s" s="0">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="I120" t="s" s="0">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="121">
@@ -10953,22 +11160,22 @@
         <v>9</v>
       </c>
       <c r="D121" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E121" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G121" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H121" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I121" t="s" s="0">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="122">
@@ -10982,22 +11189,22 @@
         <v>9</v>
       </c>
       <c r="D122" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E122" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G122" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H122" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I122" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123">
@@ -11011,22 +11218,22 @@
         <v>33</v>
       </c>
       <c r="D123" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E123" t="s" s="0">
         <v>98</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G123" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H123" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I123" t="s" s="0">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124">
@@ -11040,7 +11247,7 @@
         <v>9</v>
       </c>
       <c r="D124" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E124" t="s" s="0">
         <v>98</v>
@@ -11049,13 +11256,13 @@
         <v>11</v>
       </c>
       <c r="G124" t="s" s="0">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="H124" t="s" s="0">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="I124" t="s" s="0">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125">
@@ -11069,7 +11276,7 @@
         <v>9</v>
       </c>
       <c r="D125" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E125" t="s" s="0">
         <v>98</v>
@@ -11081,10 +11288,10 @@
         <v>11</v>
       </c>
       <c r="H125" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I125" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126">
@@ -11098,7 +11305,7 @@
         <v>33</v>
       </c>
       <c r="D126" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>98</v>
@@ -11110,10 +11317,10 @@
         <v>11</v>
       </c>
       <c r="H126" t="s" s="0">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="I126" t="s" s="0">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127">
@@ -11127,7 +11334,7 @@
         <v>9</v>
       </c>
       <c r="D127" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>98</v>
@@ -11136,13 +11343,13 @@
         <v>11</v>
       </c>
       <c r="G127" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H127" t="s" s="0">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I127" t="s" s="0">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="128">
@@ -11156,7 +11363,7 @@
         <v>9</v>
       </c>
       <c r="D128" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E128" t="s" s="0">
         <v>131</v>
@@ -11165,13 +11372,13 @@
         <v>11</v>
       </c>
       <c r="G128" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H128" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="129">
@@ -11185,7 +11392,7 @@
         <v>9</v>
       </c>
       <c r="D129" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E129" t="s" s="0">
         <v>131</v>
@@ -11194,13 +11401,13 @@
         <v>11</v>
       </c>
       <c r="G129" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H129" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="130">
@@ -11214,7 +11421,7 @@
         <v>33</v>
       </c>
       <c r="D130" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E130" t="s" s="0">
         <v>131</v>
@@ -11223,13 +11430,13 @@
         <v>11</v>
       </c>
       <c r="G130" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H130" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I130" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="131">
@@ -11243,7 +11450,7 @@
         <v>9</v>
       </c>
       <c r="D131" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E131" t="s" s="0">
         <v>131</v>
@@ -11252,13 +11459,13 @@
         <v>11</v>
       </c>
       <c r="G131" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H131" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="132">
@@ -11272,7 +11479,7 @@
         <v>9</v>
       </c>
       <c r="D132" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>131</v>
@@ -11281,13 +11488,13 @@
         <v>11</v>
       </c>
       <c r="G132" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H132" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="133">
@@ -11301,7 +11508,7 @@
         <v>9</v>
       </c>
       <c r="D133" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E133" t="s" s="0">
         <v>131</v>
@@ -11310,13 +11517,13 @@
         <v>11</v>
       </c>
       <c r="G133" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H133" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="134">
@@ -11330,7 +11537,7 @@
         <v>33</v>
       </c>
       <c r="D134" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E134" t="s" s="0">
         <v>131</v>
@@ -11339,13 +11546,13 @@
         <v>11</v>
       </c>
       <c r="G134" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H134" t="s" s="0">
         <v>11</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135">
@@ -11359,7 +11566,7 @@
         <v>33</v>
       </c>
       <c r="D135" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E135" t="s" s="0">
         <v>131</v>
@@ -11368,13 +11575,13 @@
         <v>11</v>
       </c>
       <c r="G135" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H135" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I135" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="136">
@@ -11388,7 +11595,7 @@
         <v>9</v>
       </c>
       <c r="D136" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E136" t="s" s="0">
         <v>131</v>
@@ -11397,13 +11604,13 @@
         <v>11</v>
       </c>
       <c r="G136" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H136" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137">
@@ -11417,7 +11624,7 @@
         <v>9</v>
       </c>
       <c r="D137" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E137" t="s" s="0">
         <v>131</v>
@@ -11426,13 +11633,13 @@
         <v>11</v>
       </c>
       <c r="G137" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H137" t="s" s="0">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I137" t="s" s="0">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="138">
@@ -11446,7 +11653,7 @@
         <v>33</v>
       </c>
       <c r="D138" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E138" t="s" s="0">
         <v>131</v>
@@ -11455,13 +11662,100 @@
         <v>11</v>
       </c>
       <c r="G138" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H138" t="s" s="0">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="I138" t="s" s="0">
-        <v>300</v>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D139" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="E139" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F139" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G139" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="H139" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I139" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C140" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D140" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="E140" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F140" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G140" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="H140" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I140" t="s" s="0">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C141" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="F141" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G141" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="H141" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I141" t="s" s="0">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -11471,188 +11765,197 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BF66"/>
+  <dimension ref="A1:BI69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="N1" t="s" s="0">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="P1" t="s" s="0">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Q1" t="s" s="0">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="S1" t="s" s="0">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="T1" t="s" s="0">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U1" t="s" s="0">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="X1" t="s" s="0">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y1" t="s" s="0">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z1" t="s" s="0">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA1" t="s" s="0">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AB1" t="s" s="0">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AC1" t="s" s="0">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AD1" t="s" s="0">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AE1" t="s" s="0">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AF1" t="s" s="0">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AG1" t="s" s="0">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AH1" t="s" s="0">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AI1" t="s" s="0">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ1" t="s" s="0">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AK1" t="s" s="0">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AL1" t="s" s="0">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AM1" t="s" s="0">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AN1" t="s" s="0">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AO1" t="s" s="0">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AP1" t="s" s="0">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AQ1" t="s" s="0">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AR1" t="s" s="0">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AS1" t="s" s="0">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AT1" t="s" s="0">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AU1" t="s" s="0">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AV1" t="s" s="0">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AW1" t="s" s="0">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AX1" t="s" s="0">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AY1" t="s" s="0">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AZ1" t="s" s="0">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="BA1" t="s" s="0">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="BB1" t="s" s="0">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="BC1" t="s" s="0">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="BD1" t="s" s="0">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="BE1" t="s" s="0">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="BF1" t="s" s="0">
-        <v>394</v>
+        <v>402</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>11</v>
@@ -11664,22 +11967,22 @@
         <v>11</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="K2" t="s" s="0">
         <v>11</v>
@@ -11802,51 +12105,60 @@
         <v>11</v>
       </c>
       <c r="AY2" t="s" s="0">
-        <v>193</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="s" s="0">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="BA2" t="s" s="0">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="s" s="0">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="BC2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="BD2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="BE2" t="s" s="0">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="BF2" t="s" s="0">
-        <v>207</v>
+        <v>203</v>
+      </c>
+      <c r="BG2" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="BH2" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="BI2" t="s" s="0">
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="H3" t="s" s="0">
         <v>11</v>
@@ -11858,13 +12170,13 @@
         <v>11</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>11</v>
@@ -11993,174 +12305,183 @@
         <v>11</v>
       </c>
       <c r="BD3" t="s" s="0">
-        <v>218</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="s" s="0">
-        <v>216</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BG3" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="BH3" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="BI3" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="R4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="S4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="T4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="U4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="V4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="W4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="X4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Y4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Z4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AA4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="AD4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AE4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="s" s="0">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AI4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="s" s="0">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AL4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AP4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AQ4" t="s" s="0">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AS4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AT4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AW4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AX4" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AY4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="AZ4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BA4" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BB4" t="s" s="0">
         <v>11</v>
@@ -12172,171 +12493,180 @@
         <v>11</v>
       </c>
       <c r="BE4" t="s" s="0">
-        <v>193</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BG4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BH4" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="BI4" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="P5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="R5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="S5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="T5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="U5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="V5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="W5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="X5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Y5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Z5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AC5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AD5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AE5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AI5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AK5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AO5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AQ5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AR5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AS5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AT5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AU5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AV5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AW5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AX5" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AY5" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="AZ5" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BA5" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BB5" t="s" s="0">
         <v>11</v>
@@ -12348,186 +12678,204 @@
         <v>11</v>
       </c>
       <c r="BE5" t="s" s="0">
-        <v>233</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BG5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BH5" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="BI5" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="R6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="S6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="T6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="U6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="V6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="W6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="X6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Y6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Z6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AC6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AD6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AE6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AI6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AL6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AM6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AO6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AP6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AQ6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AR6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AS6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AT6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AU6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AV6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AW6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AX6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AY6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AZ6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="BA6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="BB6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="BC6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="BD6" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BE6" t="s" s="0">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="BF6" t="s" s="0">
-        <v>153</v>
+        <v>160</v>
+      </c>
+      <c r="BG6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BH6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="BI6" t="s" s="0">
+        <v>160</v>
       </c>
     </row>
     <row r="9">
@@ -12535,18 +12883,18 @@
         <v>1</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>11</v>
@@ -12554,10 +12902,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C11" t="s" s="0">
         <v>11</v>
@@ -12565,10 +12913,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>11</v>
@@ -12576,10 +12924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>11</v>
@@ -12587,10 +12935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>11</v>
@@ -12598,10 +12946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>11</v>
@@ -12609,10 +12957,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>11</v>
@@ -12620,10 +12968,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>11</v>
@@ -12631,10 +12979,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>11</v>
@@ -12642,10 +12990,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C19" t="s" s="0">
         <v>11</v>
@@ -12653,10 +13001,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>11</v>
@@ -12664,10 +13012,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C21" t="s" s="0">
         <v>11</v>
@@ -12675,10 +13023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C22" t="s" s="0">
         <v>11</v>
@@ -12686,10 +13034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C23" t="s" s="0">
         <v>11</v>
@@ -12697,10 +13045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C24" t="s" s="0">
         <v>11</v>
@@ -12708,10 +13056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C25" t="s" s="0">
         <v>11</v>
@@ -12719,10 +13067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C26" t="s" s="0">
         <v>11</v>
@@ -12730,10 +13078,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C27" t="s" s="0">
         <v>11</v>
@@ -12741,10 +13089,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C28" t="s" s="0">
         <v>11</v>
@@ -12752,10 +13100,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C29" t="s" s="0">
         <v>11</v>
@@ -12763,10 +13111,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>11</v>
@@ -12774,10 +13122,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C31" t="s" s="0">
         <v>11</v>
@@ -12785,10 +13133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C32" t="s" s="0">
         <v>11</v>
@@ -12796,10 +13144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s" s="0">
         <v>11</v>
@@ -12807,10 +13155,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C34" t="s" s="0">
         <v>11</v>
@@ -12818,10 +13166,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C35" t="s" s="0">
         <v>11</v>
@@ -12829,10 +13177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C36" t="s" s="0">
         <v>11</v>
@@ -12840,10 +13188,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C37" t="s" s="0">
         <v>11</v>
@@ -12851,10 +13199,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C38" t="s" s="0">
         <v>11</v>
@@ -12862,10 +13210,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C39" t="s" s="0">
         <v>11</v>
@@ -12873,10 +13221,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C40" t="s" s="0">
         <v>11</v>
@@ -12884,10 +13232,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C41" t="s" s="0">
         <v>11</v>
@@ -12895,10 +13243,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C42" t="s" s="0">
         <v>11</v>
@@ -12906,10 +13254,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C43" t="s" s="0">
         <v>11</v>
@@ -12917,10 +13265,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C44" t="s" s="0">
         <v>11</v>
@@ -12928,10 +13276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C45" t="s" s="0">
         <v>11</v>
@@ -12939,10 +13287,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C46" t="s" s="0">
         <v>11</v>
@@ -12950,10 +13298,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C47" t="s" s="0">
         <v>11</v>
@@ -12961,10 +13309,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C48" t="s" s="0">
         <v>11</v>
@@ -12972,10 +13320,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C49" t="s" s="0">
         <v>11</v>
@@ -12983,10 +13331,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C50" t="s" s="0">
         <v>11</v>
@@ -12994,10 +13342,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C51" t="s" s="0">
         <v>11</v>
@@ -13005,10 +13353,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C52" t="s" s="0">
         <v>11</v>
@@ -13016,10 +13364,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C53" t="s" s="0">
         <v>11</v>
@@ -13027,10 +13375,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C54" t="s" s="0">
         <v>11</v>
@@ -13038,10 +13386,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C55" t="s" s="0">
         <v>11</v>
@@ -13049,10 +13397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C56" t="s" s="0">
         <v>11</v>
@@ -13060,10 +13408,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C57" t="s" s="0">
         <v>11</v>
@@ -13071,10 +13419,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="0">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C58" t="s" s="0">
         <v>11</v>
@@ -13082,10 +13430,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C59" t="s" s="0">
         <v>11</v>
@@ -13093,10 +13441,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B60" t="s" s="0">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C60" t="s" s="0">
         <v>11</v>
@@ -13104,10 +13452,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="0">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C61" t="s" s="0">
         <v>11</v>
@@ -13115,10 +13463,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="0">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C62" t="s" s="0">
         <v>11</v>
@@ -13126,10 +13474,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C63" t="s" s="0">
         <v>11</v>
@@ -13137,10 +13485,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B64" t="s" s="0">
-        <v>320</v>
+        <v>411</v>
       </c>
       <c r="C64" t="s" s="0">
         <v>11</v>
@@ -13148,10 +13496,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B65" t="s" s="0">
-        <v>318</v>
+        <v>411</v>
       </c>
       <c r="C65" t="s" s="0">
         <v>11</v>
@@ -13159,12 +13507,45 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="0">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C66" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>403</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="C69" t="s" s="0">
         <v>11</v>
       </c>
     </row>
